--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hotat\OneDrive\デスクトップ\GCP\DecoBom\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oskit-my.sharepoint.com/personal/e1q23083_oit_ac_jp/Documents/ゲーム作るやつ/rtbs_C/Assets/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3DB4F9-3A28-4B76-AC52-CE1DA0ABB6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{0A3DB4F9-3A28-4B76-AC52-CE1DA0ABB6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A088F843-C9EF-4AAF-80BD-740188983E7A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
+    <workbookView minimized="1" xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
   <sheets>
     <sheet name="stage1" sheetId="3" r:id="rId1"/>
     <sheet name="stage2" sheetId="1" r:id="rId2"/>
+    <sheet name="stage3" sheetId="4" r:id="rId3"/>
+    <sheet name="stage4" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +36,19 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+  <si>
+    <t>W</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>:</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -85,7 +100,133 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -534,15 +675,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B4B7A3-2A67-49C0-8CF3-3D0110D1C797}">
   <dimension ref="A1:U49"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>100</v>
       </c>
@@ -607,7 +748,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>100</v>
       </c>
@@ -672,7 +813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>100</v>
       </c>
@@ -737,7 +878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>100</v>
       </c>
@@ -802,7 +943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>10</v>
       </c>
@@ -867,7 +1008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>10</v>
       </c>
@@ -932,7 +1073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -997,7 +1138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>10</v>
       </c>
@@ -1062,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>10</v>
       </c>
@@ -1127,7 +1268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>10</v>
       </c>
@@ -1192,7 +1333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1257,7 +1398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1322,7 +1463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1387,7 +1528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1452,7 +1593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>10</v>
       </c>
@@ -1517,7 +1658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>10</v>
       </c>
@@ -1582,7 +1723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>10</v>
       </c>
@@ -1647,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>10</v>
       </c>
@@ -1712,7 +1853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>10</v>
       </c>
@@ -1777,7 +1918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>10</v>
       </c>
@@ -1842,7 +1983,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>10</v>
       </c>
@@ -1907,7 +2048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1972,7 +2113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2037,7 +2178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>10</v>
       </c>
@@ -2102,7 +2243,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>10</v>
       </c>
@@ -2167,7 +2308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>10</v>
       </c>
@@ -2232,7 +2373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2297,7 +2438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2362,7 +2503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>10</v>
       </c>
@@ -2427,7 +2568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>10</v>
       </c>
@@ -2492,7 +2633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>10</v>
       </c>
@@ -2557,7 +2698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>10</v>
       </c>
@@ -2622,7 +2763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>10</v>
       </c>
@@ -2687,7 +2828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>10</v>
       </c>
@@ -2752,7 +2893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>10</v>
       </c>
@@ -2817,7 +2958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>10</v>
       </c>
@@ -2882,7 +3023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>10</v>
       </c>
@@ -2947,7 +3088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>10</v>
       </c>
@@ -3012,7 +3153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>10</v>
       </c>
@@ -3077,7 +3218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>10</v>
       </c>
@@ -3142,7 +3283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>10</v>
       </c>
@@ -3207,7 +3348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>10</v>
       </c>
@@ -3272,7 +3413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>10</v>
       </c>
@@ -3337,7 +3478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>10</v>
       </c>
@@ -3402,7 +3543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>10</v>
       </c>
@@ -3467,7 +3608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>100</v>
       </c>
@@ -3532,7 +3673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>100</v>
       </c>
@@ -3597,7 +3738,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>100</v>
       </c>
@@ -3662,7 +3803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>100</v>
       </c>
@@ -3730,27 +3871,27 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:G8 O1:U8 V1:XFD49 H2:N8 A9:U49 A50:XFD1048576">
-    <cfRule type="expression" dxfId="15" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="4" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="5" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="6" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="7" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="29" priority="1">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="2" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="3" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3761,14 +3902,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA832E2E-F317-49D4-B89F-5814654F6E87}">
   <dimension ref="A1:AO49"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>100</v>
       </c>
@@ -3893,7 +4034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>100</v>
       </c>
@@ -4018,7 +4159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>100</v>
       </c>
@@ -4143,7 +4284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>100</v>
       </c>
@@ -4268,7 +4409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>100</v>
       </c>
@@ -4393,7 +4534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>100</v>
       </c>
@@ -4518,7 +4659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>100</v>
       </c>
@@ -4643,7 +4784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>100</v>
       </c>
@@ -4768,7 +4909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>100</v>
       </c>
@@ -4893,7 +5034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>100</v>
       </c>
@@ -5018,7 +5159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>100</v>
       </c>
@@ -5143,7 +5284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>100</v>
       </c>
@@ -5268,7 +5409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>100</v>
       </c>
@@ -5393,7 +5534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>100</v>
       </c>
@@ -5518,7 +5659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>100</v>
       </c>
@@ -5643,7 +5784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>100</v>
       </c>
@@ -5768,7 +5909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>10</v>
       </c>
@@ -5893,7 +6034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>10</v>
       </c>
@@ -6018,7 +6159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>10</v>
       </c>
@@ -6143,7 +6284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>10</v>
       </c>
@@ -6268,7 +6409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>10</v>
       </c>
@@ -6393,7 +6534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>10</v>
       </c>
@@ -6518,7 +6659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>10</v>
       </c>
@@ -6643,7 +6784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>10</v>
       </c>
@@ -6768,7 +6909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>10</v>
       </c>
@@ -6893,7 +7034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>10</v>
       </c>
@@ -7018,7 +7159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>10</v>
       </c>
@@ -7143,7 +7284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>10</v>
       </c>
@@ -7268,7 +7409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>10</v>
       </c>
@@ -7393,7 +7534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>10</v>
       </c>
@@ -7518,7 +7659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>10</v>
       </c>
@@ -7643,7 +7784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>10</v>
       </c>
@@ -7768,7 +7909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>10</v>
       </c>
@@ -7893,7 +8034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>100</v>
       </c>
@@ -8018,7 +8159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>100</v>
       </c>
@@ -8143,7 +8284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>100</v>
       </c>
@@ -8268,7 +8409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>100</v>
       </c>
@@ -8393,7 +8534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>100</v>
       </c>
@@ -8518,7 +8659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>100</v>
       </c>
@@ -8643,7 +8784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>100</v>
       </c>
@@ -8768,7 +8909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>100</v>
       </c>
@@ -8893,7 +9034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>100</v>
       </c>
@@ -9018,7 +9159,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>100</v>
       </c>
@@ -9143,7 +9284,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>100</v>
       </c>
@@ -9268,7 +9409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>100</v>
       </c>
@@ -9393,7 +9534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>100</v>
       </c>
@@ -9518,7 +9659,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>100</v>
       </c>
@@ -9643,7 +9784,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>100</v>
       </c>
@@ -9768,7 +9909,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>100</v>
       </c>
@@ -9891,6 +10032,6341 @@
       </c>
       <c r="AO49">
         <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="expression" dxfId="26" priority="1">
+      <formula>A1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="2">
+      <formula>A1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="3">
+      <formula>A1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="4" stopIfTrue="1">
+      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="5" stopIfTrue="1">
+      <formula>A1=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO16 K16:P16 Q16:AE34 A17:P23 AE17:AO33 A24:K26 L24:P34 K27:K34 A27:J49 AF34:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
+    <cfRule type="expression" dxfId="21" priority="6" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="7" stopIfTrue="1">
+      <formula>A1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="8" stopIfTrue="1">
+      <formula>A1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="9" stopIfTrue="1">
+      <formula>A1=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B5306A-7794-4650-A46E-0976E8D9B4A4}">
+  <dimension ref="A1:AI35"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A1">
+        <v>100</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+      <c r="C1">
+        <v>100</v>
+      </c>
+      <c r="D1">
+        <v>100</v>
+      </c>
+      <c r="E1">
+        <v>100</v>
+      </c>
+      <c r="F1">
+        <v>100</v>
+      </c>
+      <c r="G1">
+        <v>100</v>
+      </c>
+      <c r="H1">
+        <v>100</v>
+      </c>
+      <c r="I1">
+        <v>100</v>
+      </c>
+      <c r="J1">
+        <v>100</v>
+      </c>
+      <c r="K1">
+        <v>100</v>
+      </c>
+      <c r="L1">
+        <v>10</v>
+      </c>
+      <c r="M1">
+        <v>10</v>
+      </c>
+      <c r="N1">
+        <v>10</v>
+      </c>
+      <c r="O1">
+        <v>10</v>
+      </c>
+      <c r="P1">
+        <v>10</v>
+      </c>
+      <c r="Q1">
+        <v>10</v>
+      </c>
+      <c r="R1">
+        <v>10</v>
+      </c>
+      <c r="S1">
+        <v>100</v>
+      </c>
+      <c r="T1">
+        <v>100</v>
+      </c>
+      <c r="U1">
+        <v>100</v>
+      </c>
+      <c r="V1">
+        <v>100</v>
+      </c>
+      <c r="W1">
+        <v>100</v>
+      </c>
+      <c r="X1">
+        <v>100</v>
+      </c>
+      <c r="Y1">
+        <v>100</v>
+      </c>
+      <c r="Z1">
+        <v>100</v>
+      </c>
+      <c r="AA1">
+        <v>100</v>
+      </c>
+      <c r="AB1">
+        <v>100</v>
+      </c>
+      <c r="AC1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>99</v>
+      </c>
+      <c r="N2">
+        <v>99</v>
+      </c>
+      <c r="O2">
+        <v>99</v>
+      </c>
+      <c r="P2">
+        <v>99</v>
+      </c>
+      <c r="Q2">
+        <v>99</v>
+      </c>
+      <c r="R2">
+        <v>10</v>
+      </c>
+      <c r="S2">
+        <v>100</v>
+      </c>
+      <c r="T2">
+        <v>100</v>
+      </c>
+      <c r="U2">
+        <v>100</v>
+      </c>
+      <c r="V2">
+        <v>100</v>
+      </c>
+      <c r="W2">
+        <v>100</v>
+      </c>
+      <c r="X2">
+        <v>100</v>
+      </c>
+      <c r="Y2">
+        <v>100</v>
+      </c>
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>100</v>
+      </c>
+      <c r="AC2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>99</v>
+      </c>
+      <c r="N3">
+        <v>91</v>
+      </c>
+      <c r="O3">
+        <v>99</v>
+      </c>
+      <c r="P3">
+        <v>92</v>
+      </c>
+      <c r="Q3">
+        <v>99</v>
+      </c>
+      <c r="R3">
+        <v>10</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+      <c r="T3">
+        <v>100</v>
+      </c>
+      <c r="U3">
+        <v>100</v>
+      </c>
+      <c r="V3">
+        <v>100</v>
+      </c>
+      <c r="W3">
+        <v>100</v>
+      </c>
+      <c r="X3">
+        <v>100</v>
+      </c>
+      <c r="Y3">
+        <v>100</v>
+      </c>
+      <c r="Z3">
+        <v>100</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>100</v>
+      </c>
+      <c r="AC3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+      <c r="N4">
+        <v>99</v>
+      </c>
+      <c r="O4">
+        <v>99</v>
+      </c>
+      <c r="P4">
+        <v>99</v>
+      </c>
+      <c r="Q4">
+        <v>99</v>
+      </c>
+      <c r="R4">
+        <v>10</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <v>100</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AB4">
+        <v>100</v>
+      </c>
+      <c r="AC4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>95</v>
+      </c>
+      <c r="N5">
+        <v>95</v>
+      </c>
+      <c r="O5">
+        <v>95</v>
+      </c>
+      <c r="P5">
+        <v>95</v>
+      </c>
+      <c r="Q5">
+        <v>95</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="T5">
+        <v>10</v>
+      </c>
+      <c r="U5">
+        <v>10</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+      <c r="Z5">
+        <v>100</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <v>100</v>
+      </c>
+      <c r="AC5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>10</v>
+      </c>
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>100</v>
+      </c>
+      <c r="Z6">
+        <v>100</v>
+      </c>
+      <c r="AA6">
+        <v>100</v>
+      </c>
+      <c r="AB6">
+        <v>100</v>
+      </c>
+      <c r="AC6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7">
+        <v>20</v>
+      </c>
+      <c r="U7">
+        <v>10</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>10</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+      <c r="Z7">
+        <v>100</v>
+      </c>
+      <c r="AA7">
+        <v>100</v>
+      </c>
+      <c r="AB7">
+        <v>100</v>
+      </c>
+      <c r="AC7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>100</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>20</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8">
+        <v>20</v>
+      </c>
+      <c r="U8">
+        <v>20</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>10</v>
+      </c>
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+      <c r="Z8">
+        <v>100</v>
+      </c>
+      <c r="AA8">
+        <v>100</v>
+      </c>
+      <c r="AB8">
+        <v>100</v>
+      </c>
+      <c r="AC8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>10</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>10</v>
+      </c>
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+      <c r="Z9">
+        <v>100</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9">
+        <v>100</v>
+      </c>
+      <c r="AC9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>100</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>10</v>
+      </c>
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+      <c r="Z10">
+        <v>100</v>
+      </c>
+      <c r="AA10">
+        <v>100</v>
+      </c>
+      <c r="AB10">
+        <v>100</v>
+      </c>
+      <c r="AC10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>20</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>10</v>
+      </c>
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+      <c r="Z11">
+        <v>100</v>
+      </c>
+      <c r="AA11">
+        <v>100</v>
+      </c>
+      <c r="AB11">
+        <v>100</v>
+      </c>
+      <c r="AC11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>80</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+      <c r="N12">
+        <v>80</v>
+      </c>
+      <c r="O12">
+        <v>80</v>
+      </c>
+      <c r="P12">
+        <v>80</v>
+      </c>
+      <c r="Q12">
+        <v>80</v>
+      </c>
+      <c r="R12">
+        <v>80</v>
+      </c>
+      <c r="S12">
+        <v>10</v>
+      </c>
+      <c r="T12">
+        <v>20</v>
+      </c>
+      <c r="U12">
+        <v>20</v>
+      </c>
+      <c r="V12">
+        <v>20</v>
+      </c>
+      <c r="W12">
+        <v>10</v>
+      </c>
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>100</v>
+      </c>
+      <c r="Z12">
+        <v>100</v>
+      </c>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>100</v>
+      </c>
+      <c r="AC12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>80</v>
+      </c>
+      <c r="N13">
+        <v>80</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="P13">
+        <v>80</v>
+      </c>
+      <c r="Q13">
+        <v>80</v>
+      </c>
+      <c r="R13">
+        <v>80</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>10</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13">
+        <v>10</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>80</v>
+      </c>
+      <c r="O14">
+        <v>80</v>
+      </c>
+      <c r="P14">
+        <v>80</v>
+      </c>
+      <c r="Q14">
+        <v>80</v>
+      </c>
+      <c r="R14">
+        <v>80</v>
+      </c>
+      <c r="S14">
+        <v>10</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>10</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>80</v>
+      </c>
+      <c r="N15">
+        <v>80</v>
+      </c>
+      <c r="O15">
+        <v>80</v>
+      </c>
+      <c r="P15">
+        <v>80</v>
+      </c>
+      <c r="Q15">
+        <v>80</v>
+      </c>
+      <c r="R15">
+        <v>80</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>10</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>80</v>
+      </c>
+      <c r="M16">
+        <v>80</v>
+      </c>
+      <c r="N16">
+        <v>80</v>
+      </c>
+      <c r="O16">
+        <v>80</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>80</v>
+      </c>
+      <c r="R16">
+        <v>80</v>
+      </c>
+      <c r="S16">
+        <v>10</v>
+      </c>
+      <c r="T16">
+        <v>20</v>
+      </c>
+      <c r="U16">
+        <v>10</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
+      <c r="X16">
+        <v>10</v>
+      </c>
+      <c r="Y16">
+        <v>10</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>80</v>
+      </c>
+      <c r="M17">
+        <v>80</v>
+      </c>
+      <c r="N17">
+        <v>80</v>
+      </c>
+      <c r="O17">
+        <v>80</v>
+      </c>
+      <c r="P17">
+        <v>80</v>
+      </c>
+      <c r="Q17">
+        <v>80</v>
+      </c>
+      <c r="R17">
+        <v>80</v>
+      </c>
+      <c r="S17">
+        <v>20</v>
+      </c>
+      <c r="T17">
+        <v>20</v>
+      </c>
+      <c r="U17">
+        <v>20</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>20</v>
+      </c>
+      <c r="X17">
+        <v>20</v>
+      </c>
+      <c r="Y17">
+        <v>20</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>71</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>20</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>80</v>
+      </c>
+      <c r="M18">
+        <v>80</v>
+      </c>
+      <c r="N18">
+        <v>80</v>
+      </c>
+      <c r="O18">
+        <v>80</v>
+      </c>
+      <c r="P18">
+        <v>80</v>
+      </c>
+      <c r="Q18">
+        <v>80</v>
+      </c>
+      <c r="R18">
+        <v>80</v>
+      </c>
+      <c r="S18">
+        <v>20</v>
+      </c>
+      <c r="T18">
+        <v>20</v>
+      </c>
+      <c r="U18">
+        <v>20</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>20</v>
+      </c>
+      <c r="X18">
+        <v>20</v>
+      </c>
+      <c r="Y18">
+        <v>20</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>72</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>20</v>
+      </c>
+      <c r="L19">
+        <v>80</v>
+      </c>
+      <c r="M19">
+        <v>80</v>
+      </c>
+      <c r="N19">
+        <v>80</v>
+      </c>
+      <c r="O19">
+        <v>80</v>
+      </c>
+      <c r="P19">
+        <v>80</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
+      </c>
+      <c r="R19">
+        <v>80</v>
+      </c>
+      <c r="S19">
+        <v>20</v>
+      </c>
+      <c r="T19">
+        <v>20</v>
+      </c>
+      <c r="U19">
+        <v>20</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>20</v>
+      </c>
+      <c r="X19">
+        <v>20</v>
+      </c>
+      <c r="Y19">
+        <v>20</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>80</v>
+      </c>
+      <c r="M20">
+        <v>80</v>
+      </c>
+      <c r="N20">
+        <v>80</v>
+      </c>
+      <c r="O20">
+        <v>80</v>
+      </c>
+      <c r="P20">
+        <v>80</v>
+      </c>
+      <c r="Q20">
+        <v>80</v>
+      </c>
+      <c r="R20">
+        <v>80</v>
+      </c>
+      <c r="S20">
+        <v>10</v>
+      </c>
+      <c r="T20">
+        <v>20</v>
+      </c>
+      <c r="U20">
+        <v>10</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>10</v>
+      </c>
+      <c r="X20">
+        <v>10</v>
+      </c>
+      <c r="Y20">
+        <v>10</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>80</v>
+      </c>
+      <c r="M21">
+        <v>80</v>
+      </c>
+      <c r="N21">
+        <v>80</v>
+      </c>
+      <c r="O21">
+        <v>80</v>
+      </c>
+      <c r="P21">
+        <v>80</v>
+      </c>
+      <c r="Q21">
+        <v>80</v>
+      </c>
+      <c r="R21">
+        <v>80</v>
+      </c>
+      <c r="S21">
+        <v>10</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>10</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>80</v>
+      </c>
+      <c r="M22">
+        <v>80</v>
+      </c>
+      <c r="N22">
+        <v>80</v>
+      </c>
+      <c r="O22">
+        <v>80</v>
+      </c>
+      <c r="P22">
+        <v>80</v>
+      </c>
+      <c r="Q22">
+        <v>80</v>
+      </c>
+      <c r="R22">
+        <v>80</v>
+      </c>
+      <c r="S22">
+        <v>10</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>10</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>80</v>
+      </c>
+      <c r="M23">
+        <v>80</v>
+      </c>
+      <c r="N23">
+        <v>80</v>
+      </c>
+      <c r="O23">
+        <v>80</v>
+      </c>
+      <c r="P23">
+        <v>80</v>
+      </c>
+      <c r="Q23">
+        <v>80</v>
+      </c>
+      <c r="R23">
+        <v>80</v>
+      </c>
+      <c r="S23">
+        <v>10</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>10</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>10</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
+        <v>10</v>
+      </c>
+      <c r="Z23">
+        <v>10</v>
+      </c>
+      <c r="AA23">
+        <v>10</v>
+      </c>
+      <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>100</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="H24">
+        <v>20</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+      <c r="L24">
+        <v>80</v>
+      </c>
+      <c r="M24">
+        <v>80</v>
+      </c>
+      <c r="N24">
+        <v>80</v>
+      </c>
+      <c r="O24">
+        <v>80</v>
+      </c>
+      <c r="P24">
+        <v>80</v>
+      </c>
+      <c r="Q24">
+        <v>80</v>
+      </c>
+      <c r="R24">
+        <v>80</v>
+      </c>
+      <c r="S24">
+        <v>10</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>10</v>
+      </c>
+      <c r="X24">
+        <v>100</v>
+      </c>
+      <c r="Y24">
+        <v>100</v>
+      </c>
+      <c r="Z24">
+        <v>100</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
+      </c>
+      <c r="AB24">
+        <v>100</v>
+      </c>
+      <c r="AC24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>100</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>20</v>
+      </c>
+      <c r="O25">
+        <v>20</v>
+      </c>
+      <c r="P25">
+        <v>20</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
+        <v>10</v>
+      </c>
+      <c r="S25">
+        <v>10</v>
+      </c>
+      <c r="T25">
+        <v>20</v>
+      </c>
+      <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>10</v>
+      </c>
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+      <c r="Z25">
+        <v>100</v>
+      </c>
+      <c r="AA25">
+        <v>100</v>
+      </c>
+      <c r="AB25">
+        <v>100</v>
+      </c>
+      <c r="AC25">
+        <v>100</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>100</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>20</v>
+      </c>
+      <c r="O26">
+        <v>20</v>
+      </c>
+      <c r="P26">
+        <v>20</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>20</v>
+      </c>
+      <c r="T26">
+        <v>20</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>10</v>
+      </c>
+      <c r="X26">
+        <v>100</v>
+      </c>
+      <c r="Y26">
+        <v>100</v>
+      </c>
+      <c r="Z26">
+        <v>100</v>
+      </c>
+      <c r="AA26">
+        <v>100</v>
+      </c>
+      <c r="AB26">
+        <v>100</v>
+      </c>
+      <c r="AC26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>100</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>100</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>10</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>10</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>10</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>10</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>10</v>
+      </c>
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+      <c r="Z27">
+        <v>100</v>
+      </c>
+      <c r="AA27">
+        <v>100</v>
+      </c>
+      <c r="AB27">
+        <v>100</v>
+      </c>
+      <c r="AC27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>100</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+      <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <v>20</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>20</v>
+      </c>
+      <c r="P28">
+        <v>20</v>
+      </c>
+      <c r="Q28">
+        <v>20</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>20</v>
+      </c>
+      <c r="U28">
+        <v>20</v>
+      </c>
+      <c r="V28">
+        <v>20</v>
+      </c>
+      <c r="W28">
+        <v>10</v>
+      </c>
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>100</v>
+      </c>
+      <c r="Z28">
+        <v>100</v>
+      </c>
+      <c r="AA28">
+        <v>100</v>
+      </c>
+      <c r="AB28">
+        <v>100</v>
+      </c>
+      <c r="AC28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>100</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <v>20</v>
+      </c>
+      <c r="K29">
+        <v>10</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
+        <v>20</v>
+      </c>
+      <c r="Q29">
+        <v>10</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>10</v>
+      </c>
+      <c r="T29">
+        <v>20</v>
+      </c>
+      <c r="U29">
+        <v>10</v>
+      </c>
+      <c r="V29">
+        <v>20</v>
+      </c>
+      <c r="W29">
+        <v>10</v>
+      </c>
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+      <c r="Z29">
+        <v>100</v>
+      </c>
+      <c r="AA29">
+        <v>100</v>
+      </c>
+      <c r="AB29">
+        <v>100</v>
+      </c>
+      <c r="AC29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>20</v>
+      </c>
+      <c r="K30">
+        <v>20</v>
+      </c>
+      <c r="L30">
+        <v>20</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>20</v>
+      </c>
+      <c r="U30">
+        <v>20</v>
+      </c>
+      <c r="V30">
+        <v>20</v>
+      </c>
+      <c r="W30">
+        <v>10</v>
+      </c>
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+      <c r="Z30">
+        <v>100</v>
+      </c>
+      <c r="AA30">
+        <v>100</v>
+      </c>
+      <c r="AB30">
+        <v>100</v>
+      </c>
+      <c r="AC30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>100</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
+        <v>10</v>
+      </c>
+      <c r="L31">
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>95</v>
+      </c>
+      <c r="N31">
+        <v>95</v>
+      </c>
+      <c r="O31">
+        <v>95</v>
+      </c>
+      <c r="P31">
+        <v>95</v>
+      </c>
+      <c r="Q31">
+        <v>95</v>
+      </c>
+      <c r="R31">
+        <v>10</v>
+      </c>
+      <c r="S31">
+        <v>10</v>
+      </c>
+      <c r="T31">
+        <v>10</v>
+      </c>
+      <c r="U31">
+        <v>10</v>
+      </c>
+      <c r="V31">
+        <v>10</v>
+      </c>
+      <c r="W31">
+        <v>10</v>
+      </c>
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+      <c r="Z31">
+        <v>100</v>
+      </c>
+      <c r="AA31">
+        <v>100</v>
+      </c>
+      <c r="AB31">
+        <v>100</v>
+      </c>
+      <c r="AC31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>100</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>10</v>
+      </c>
+      <c r="M32">
+        <v>99</v>
+      </c>
+      <c r="N32">
+        <v>99</v>
+      </c>
+      <c r="O32">
+        <v>99</v>
+      </c>
+      <c r="P32">
+        <v>99</v>
+      </c>
+      <c r="Q32">
+        <v>99</v>
+      </c>
+      <c r="R32">
+        <v>10</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+      <c r="W32">
+        <v>100</v>
+      </c>
+      <c r="X32">
+        <v>100</v>
+      </c>
+      <c r="Y32">
+        <v>100</v>
+      </c>
+      <c r="Z32">
+        <v>100</v>
+      </c>
+      <c r="AA32">
+        <v>100</v>
+      </c>
+      <c r="AB32">
+        <v>100</v>
+      </c>
+      <c r="AC32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>100</v>
+      </c>
+      <c r="B33">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>10</v>
+      </c>
+      <c r="M33">
+        <v>99</v>
+      </c>
+      <c r="N33">
+        <v>93</v>
+      </c>
+      <c r="O33">
+        <v>99</v>
+      </c>
+      <c r="P33">
+        <v>94</v>
+      </c>
+      <c r="Q33">
+        <v>99</v>
+      </c>
+      <c r="R33">
+        <v>10</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
+        <v>100</v>
+      </c>
+      <c r="X33">
+        <v>100</v>
+      </c>
+      <c r="Y33">
+        <v>100</v>
+      </c>
+      <c r="Z33">
+        <v>100</v>
+      </c>
+      <c r="AA33">
+        <v>100</v>
+      </c>
+      <c r="AB33">
+        <v>100</v>
+      </c>
+      <c r="AC33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>100</v>
+      </c>
+      <c r="B34">
+        <v>100</v>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>100</v>
+      </c>
+      <c r="E34">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <v>99</v>
+      </c>
+      <c r="N34">
+        <v>99</v>
+      </c>
+      <c r="O34">
+        <v>99</v>
+      </c>
+      <c r="P34">
+        <v>99</v>
+      </c>
+      <c r="Q34">
+        <v>99</v>
+      </c>
+      <c r="R34">
+        <v>10</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
+        <v>100</v>
+      </c>
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
+        <v>100</v>
+      </c>
+      <c r="X34">
+        <v>100</v>
+      </c>
+      <c r="Y34">
+        <v>100</v>
+      </c>
+      <c r="Z34">
+        <v>100</v>
+      </c>
+      <c r="AA34">
+        <v>100</v>
+      </c>
+      <c r="AB34">
+        <v>100</v>
+      </c>
+      <c r="AC34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35">
+        <v>100</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>10</v>
+      </c>
+      <c r="M35">
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <v>10</v>
+      </c>
+      <c r="P35">
+        <v>10</v>
+      </c>
+      <c r="Q35">
+        <v>10</v>
+      </c>
+      <c r="R35">
+        <v>10</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+      <c r="Z35">
+        <v>100</v>
+      </c>
+      <c r="AA35">
+        <v>100</v>
+      </c>
+      <c r="AB35">
+        <v>100</v>
+      </c>
+      <c r="AC35">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>A1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>A1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="3">
+      <formula>A1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="4" stopIfTrue="1">
+      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="5" stopIfTrue="1">
+      <formula>A1=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 AF9:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
+    <cfRule type="expression" dxfId="12" priority="6" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="7" stopIfTrue="1">
+      <formula>A1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
+      <formula>A1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
+      <formula>A1=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A64FA3-C0B1-40B6-B9C2-665C3D824C39}">
+  <dimension ref="A1:AI39"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A1">
+        <v>100</v>
+      </c>
+      <c r="B1">
+        <v>100</v>
+      </c>
+      <c r="C1">
+        <v>100</v>
+      </c>
+      <c r="D1">
+        <v>100</v>
+      </c>
+      <c r="E1">
+        <v>100</v>
+      </c>
+      <c r="F1">
+        <v>100</v>
+      </c>
+      <c r="G1">
+        <v>100</v>
+      </c>
+      <c r="H1">
+        <v>100</v>
+      </c>
+      <c r="I1">
+        <v>100</v>
+      </c>
+      <c r="J1">
+        <v>100</v>
+      </c>
+      <c r="K1">
+        <v>100</v>
+      </c>
+      <c r="L1">
+        <v>10</v>
+      </c>
+      <c r="M1">
+        <v>10</v>
+      </c>
+      <c r="N1">
+        <v>10</v>
+      </c>
+      <c r="O1">
+        <v>10</v>
+      </c>
+      <c r="P1">
+        <v>10</v>
+      </c>
+      <c r="Q1">
+        <v>10</v>
+      </c>
+      <c r="R1">
+        <v>10</v>
+      </c>
+      <c r="S1">
+        <v>100</v>
+      </c>
+      <c r="T1">
+        <v>100</v>
+      </c>
+      <c r="U1">
+        <v>100</v>
+      </c>
+      <c r="V1">
+        <v>100</v>
+      </c>
+      <c r="W1">
+        <v>100</v>
+      </c>
+      <c r="X1">
+        <v>100</v>
+      </c>
+      <c r="Y1">
+        <v>100</v>
+      </c>
+      <c r="Z1">
+        <v>100</v>
+      </c>
+      <c r="AA1">
+        <v>100</v>
+      </c>
+      <c r="AB1">
+        <v>100</v>
+      </c>
+      <c r="AC1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>99</v>
+      </c>
+      <c r="N2">
+        <v>99</v>
+      </c>
+      <c r="O2">
+        <v>99</v>
+      </c>
+      <c r="P2">
+        <v>99</v>
+      </c>
+      <c r="Q2">
+        <v>99</v>
+      </c>
+      <c r="R2">
+        <v>10</v>
+      </c>
+      <c r="S2">
+        <v>100</v>
+      </c>
+      <c r="T2">
+        <v>100</v>
+      </c>
+      <c r="U2">
+        <v>100</v>
+      </c>
+      <c r="V2">
+        <v>100</v>
+      </c>
+      <c r="W2">
+        <v>100</v>
+      </c>
+      <c r="X2">
+        <v>100</v>
+      </c>
+      <c r="Y2">
+        <v>100</v>
+      </c>
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>100</v>
+      </c>
+      <c r="AC2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>99</v>
+      </c>
+      <c r="N3">
+        <v>91</v>
+      </c>
+      <c r="O3">
+        <v>99</v>
+      </c>
+      <c r="P3">
+        <v>92</v>
+      </c>
+      <c r="Q3">
+        <v>99</v>
+      </c>
+      <c r="R3">
+        <v>10</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+      <c r="T3">
+        <v>100</v>
+      </c>
+      <c r="U3">
+        <v>100</v>
+      </c>
+      <c r="V3">
+        <v>100</v>
+      </c>
+      <c r="W3">
+        <v>100</v>
+      </c>
+      <c r="X3">
+        <v>100</v>
+      </c>
+      <c r="Y3">
+        <v>100</v>
+      </c>
+      <c r="Z3">
+        <v>100</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>100</v>
+      </c>
+      <c r="AC3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+      <c r="N4">
+        <v>99</v>
+      </c>
+      <c r="O4">
+        <v>99</v>
+      </c>
+      <c r="P4">
+        <v>99</v>
+      </c>
+      <c r="Q4">
+        <v>99</v>
+      </c>
+      <c r="R4">
+        <v>10</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <v>100</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AB4">
+        <v>100</v>
+      </c>
+      <c r="AC4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>95</v>
+      </c>
+      <c r="N5">
+        <v>95</v>
+      </c>
+      <c r="O5">
+        <v>95</v>
+      </c>
+      <c r="P5">
+        <v>95</v>
+      </c>
+      <c r="Q5">
+        <v>95</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="T5">
+        <v>10</v>
+      </c>
+      <c r="U5">
+        <v>10</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+      <c r="Z5">
+        <v>100</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <v>100</v>
+      </c>
+      <c r="AC5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+      <c r="T6">
+        <v>20</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>10</v>
+      </c>
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>100</v>
+      </c>
+      <c r="Z6">
+        <v>100</v>
+      </c>
+      <c r="AA6">
+        <v>100</v>
+      </c>
+      <c r="AB6">
+        <v>100</v>
+      </c>
+      <c r="AC6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7">
+        <v>20</v>
+      </c>
+      <c r="U7">
+        <v>10</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>10</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+      <c r="Z7">
+        <v>100</v>
+      </c>
+      <c r="AA7">
+        <v>100</v>
+      </c>
+      <c r="AB7">
+        <v>100</v>
+      </c>
+      <c r="AC7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>100</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>20</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>20</v>
+      </c>
+      <c r="O8">
+        <v>20</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8">
+        <v>20</v>
+      </c>
+      <c r="U8">
+        <v>20</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>10</v>
+      </c>
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+      <c r="Z8">
+        <v>100</v>
+      </c>
+      <c r="AA8">
+        <v>100</v>
+      </c>
+      <c r="AB8">
+        <v>100</v>
+      </c>
+      <c r="AC8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>10</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>10</v>
+      </c>
+      <c r="T9">
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>10</v>
+      </c>
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+      <c r="Z9">
+        <v>100</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9">
+        <v>100</v>
+      </c>
+      <c r="AC9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>100</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>10</v>
+      </c>
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+      <c r="Z10">
+        <v>100</v>
+      </c>
+      <c r="AA10">
+        <v>100</v>
+      </c>
+      <c r="AB10">
+        <v>100</v>
+      </c>
+      <c r="AC10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>20</v>
+      </c>
+      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>10</v>
+      </c>
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+      <c r="Z11">
+        <v>100</v>
+      </c>
+      <c r="AA11">
+        <v>100</v>
+      </c>
+      <c r="AB11">
+        <v>100</v>
+      </c>
+      <c r="AC11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>80</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+      <c r="N12">
+        <v>80</v>
+      </c>
+      <c r="O12">
+        <v>80</v>
+      </c>
+      <c r="P12">
+        <v>80</v>
+      </c>
+      <c r="Q12">
+        <v>80</v>
+      </c>
+      <c r="R12">
+        <v>80</v>
+      </c>
+      <c r="S12">
+        <v>10</v>
+      </c>
+      <c r="T12">
+        <v>20</v>
+      </c>
+      <c r="U12">
+        <v>20</v>
+      </c>
+      <c r="V12">
+        <v>20</v>
+      </c>
+      <c r="W12">
+        <v>10</v>
+      </c>
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>100</v>
+      </c>
+      <c r="Z12">
+        <v>100</v>
+      </c>
+      <c r="AA12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
+        <v>100</v>
+      </c>
+      <c r="AC12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>80</v>
+      </c>
+      <c r="N13">
+        <v>80</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="P13">
+        <v>80</v>
+      </c>
+      <c r="Q13">
+        <v>80</v>
+      </c>
+      <c r="R13">
+        <v>80</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>10</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13">
+        <v>10</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>80</v>
+      </c>
+      <c r="O14">
+        <v>80</v>
+      </c>
+      <c r="P14">
+        <v>80</v>
+      </c>
+      <c r="Q14">
+        <v>80</v>
+      </c>
+      <c r="R14">
+        <v>80</v>
+      </c>
+      <c r="S14">
+        <v>10</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>10</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>80</v>
+      </c>
+      <c r="N15">
+        <v>80</v>
+      </c>
+      <c r="O15">
+        <v>80</v>
+      </c>
+      <c r="P15">
+        <v>80</v>
+      </c>
+      <c r="Q15">
+        <v>80</v>
+      </c>
+      <c r="R15">
+        <v>80</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>10</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>80</v>
+      </c>
+      <c r="M16">
+        <v>80</v>
+      </c>
+      <c r="N16">
+        <v>80</v>
+      </c>
+      <c r="O16">
+        <v>80</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>80</v>
+      </c>
+      <c r="R16">
+        <v>80</v>
+      </c>
+      <c r="S16">
+        <v>10</v>
+      </c>
+      <c r="T16">
+        <v>20</v>
+      </c>
+      <c r="U16">
+        <v>10</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
+      <c r="X16">
+        <v>10</v>
+      </c>
+      <c r="Y16">
+        <v>10</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>80</v>
+      </c>
+      <c r="M17">
+        <v>80</v>
+      </c>
+      <c r="N17">
+        <v>80</v>
+      </c>
+      <c r="O17">
+        <v>80</v>
+      </c>
+      <c r="P17">
+        <v>80</v>
+      </c>
+      <c r="Q17">
+        <v>80</v>
+      </c>
+      <c r="R17">
+        <v>80</v>
+      </c>
+      <c r="S17">
+        <v>20</v>
+      </c>
+      <c r="T17">
+        <v>20</v>
+      </c>
+      <c r="U17">
+        <v>20</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>20</v>
+      </c>
+      <c r="X17">
+        <v>20</v>
+      </c>
+      <c r="Y17">
+        <v>20</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>71</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <v>20</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>20</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>80</v>
+      </c>
+      <c r="M18">
+        <v>80</v>
+      </c>
+      <c r="N18">
+        <v>80</v>
+      </c>
+      <c r="O18">
+        <v>80</v>
+      </c>
+      <c r="P18">
+        <v>80</v>
+      </c>
+      <c r="Q18">
+        <v>80</v>
+      </c>
+      <c r="R18">
+        <v>80</v>
+      </c>
+      <c r="S18">
+        <v>20</v>
+      </c>
+      <c r="T18">
+        <v>20</v>
+      </c>
+      <c r="U18">
+        <v>20</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>20</v>
+      </c>
+      <c r="X18">
+        <v>20</v>
+      </c>
+      <c r="Y18">
+        <v>20</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>72</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>20</v>
+      </c>
+      <c r="L19">
+        <v>80</v>
+      </c>
+      <c r="M19">
+        <v>80</v>
+      </c>
+      <c r="N19">
+        <v>80</v>
+      </c>
+      <c r="O19">
+        <v>80</v>
+      </c>
+      <c r="P19">
+        <v>80</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
+      </c>
+      <c r="R19">
+        <v>80</v>
+      </c>
+      <c r="S19">
+        <v>20</v>
+      </c>
+      <c r="T19">
+        <v>20</v>
+      </c>
+      <c r="U19">
+        <v>20</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>20</v>
+      </c>
+      <c r="X19">
+        <v>20</v>
+      </c>
+      <c r="Y19">
+        <v>20</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>80</v>
+      </c>
+      <c r="M20">
+        <v>80</v>
+      </c>
+      <c r="N20">
+        <v>80</v>
+      </c>
+      <c r="O20">
+        <v>80</v>
+      </c>
+      <c r="P20">
+        <v>80</v>
+      </c>
+      <c r="Q20">
+        <v>80</v>
+      </c>
+      <c r="R20">
+        <v>80</v>
+      </c>
+      <c r="S20">
+        <v>10</v>
+      </c>
+      <c r="T20">
+        <v>20</v>
+      </c>
+      <c r="U20">
+        <v>10</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>10</v>
+      </c>
+      <c r="X20">
+        <v>10</v>
+      </c>
+      <c r="Y20">
+        <v>10</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>80</v>
+      </c>
+      <c r="M21">
+        <v>80</v>
+      </c>
+      <c r="N21">
+        <v>80</v>
+      </c>
+      <c r="O21">
+        <v>80</v>
+      </c>
+      <c r="P21">
+        <v>80</v>
+      </c>
+      <c r="Q21">
+        <v>80</v>
+      </c>
+      <c r="R21">
+        <v>80</v>
+      </c>
+      <c r="S21">
+        <v>10</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>10</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>80</v>
+      </c>
+      <c r="M22">
+        <v>80</v>
+      </c>
+      <c r="N22">
+        <v>80</v>
+      </c>
+      <c r="O22">
+        <v>80</v>
+      </c>
+      <c r="P22">
+        <v>80</v>
+      </c>
+      <c r="Q22">
+        <v>80</v>
+      </c>
+      <c r="R22">
+        <v>80</v>
+      </c>
+      <c r="S22">
+        <v>10</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>10</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>80</v>
+      </c>
+      <c r="M23">
+        <v>80</v>
+      </c>
+      <c r="N23">
+        <v>80</v>
+      </c>
+      <c r="O23">
+        <v>80</v>
+      </c>
+      <c r="P23">
+        <v>80</v>
+      </c>
+      <c r="Q23">
+        <v>80</v>
+      </c>
+      <c r="R23">
+        <v>80</v>
+      </c>
+      <c r="S23">
+        <v>10</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>10</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>10</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
+        <v>10</v>
+      </c>
+      <c r="Z23">
+        <v>10</v>
+      </c>
+      <c r="AA23">
+        <v>10</v>
+      </c>
+      <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>100</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="H24">
+        <v>20</v>
+      </c>
+      <c r="I24">
+        <v>20</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+      <c r="L24">
+        <v>80</v>
+      </c>
+      <c r="M24">
+        <v>80</v>
+      </c>
+      <c r="N24">
+        <v>80</v>
+      </c>
+      <c r="O24">
+        <v>80</v>
+      </c>
+      <c r="P24">
+        <v>80</v>
+      </c>
+      <c r="Q24">
+        <v>80</v>
+      </c>
+      <c r="R24">
+        <v>80</v>
+      </c>
+      <c r="S24">
+        <v>10</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>10</v>
+      </c>
+      <c r="X24">
+        <v>100</v>
+      </c>
+      <c r="Y24">
+        <v>100</v>
+      </c>
+      <c r="Z24">
+        <v>100</v>
+      </c>
+      <c r="AA24">
+        <v>100</v>
+      </c>
+      <c r="AB24">
+        <v>100</v>
+      </c>
+      <c r="AC24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>100</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>20</v>
+      </c>
+      <c r="O25">
+        <v>20</v>
+      </c>
+      <c r="P25">
+        <v>20</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
+        <v>10</v>
+      </c>
+      <c r="S25">
+        <v>10</v>
+      </c>
+      <c r="T25">
+        <v>20</v>
+      </c>
+      <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>10</v>
+      </c>
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+      <c r="Z25">
+        <v>100</v>
+      </c>
+      <c r="AA25">
+        <v>100</v>
+      </c>
+      <c r="AB25">
+        <v>100</v>
+      </c>
+      <c r="AC25">
+        <v>100</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>100</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>20</v>
+      </c>
+      <c r="O26">
+        <v>20</v>
+      </c>
+      <c r="P26">
+        <v>20</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>20</v>
+      </c>
+      <c r="T26">
+        <v>20</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>10</v>
+      </c>
+      <c r="X26">
+        <v>100</v>
+      </c>
+      <c r="Y26">
+        <v>100</v>
+      </c>
+      <c r="Z26">
+        <v>100</v>
+      </c>
+      <c r="AA26">
+        <v>100</v>
+      </c>
+      <c r="AB26">
+        <v>100</v>
+      </c>
+      <c r="AC26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>100</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>100</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>20</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>10</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>10</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>10</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>10</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>10</v>
+      </c>
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+      <c r="Z27">
+        <v>100</v>
+      </c>
+      <c r="AA27">
+        <v>100</v>
+      </c>
+      <c r="AB27">
+        <v>100</v>
+      </c>
+      <c r="AC27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>100</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+      <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>20</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <v>20</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>20</v>
+      </c>
+      <c r="P28">
+        <v>20</v>
+      </c>
+      <c r="Q28">
+        <v>20</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>20</v>
+      </c>
+      <c r="U28">
+        <v>20</v>
+      </c>
+      <c r="V28">
+        <v>20</v>
+      </c>
+      <c r="W28">
+        <v>10</v>
+      </c>
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>100</v>
+      </c>
+      <c r="Z28">
+        <v>100</v>
+      </c>
+      <c r="AA28">
+        <v>100</v>
+      </c>
+      <c r="AB28">
+        <v>100</v>
+      </c>
+      <c r="AC28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>100</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <v>20</v>
+      </c>
+      <c r="K29">
+        <v>10</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>10</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
+        <v>20</v>
+      </c>
+      <c r="Q29">
+        <v>10</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>10</v>
+      </c>
+      <c r="T29">
+        <v>20</v>
+      </c>
+      <c r="U29">
+        <v>10</v>
+      </c>
+      <c r="V29">
+        <v>20</v>
+      </c>
+      <c r="W29">
+        <v>10</v>
+      </c>
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+      <c r="Z29">
+        <v>100</v>
+      </c>
+      <c r="AA29">
+        <v>100</v>
+      </c>
+      <c r="AB29">
+        <v>100</v>
+      </c>
+      <c r="AC29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>20</v>
+      </c>
+      <c r="K30">
+        <v>20</v>
+      </c>
+      <c r="L30">
+        <v>20</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>20</v>
+      </c>
+      <c r="U30">
+        <v>20</v>
+      </c>
+      <c r="V30">
+        <v>20</v>
+      </c>
+      <c r="W30">
+        <v>10</v>
+      </c>
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+      <c r="Z30">
+        <v>100</v>
+      </c>
+      <c r="AA30">
+        <v>100</v>
+      </c>
+      <c r="AB30">
+        <v>100</v>
+      </c>
+      <c r="AC30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>100</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
+        <v>10</v>
+      </c>
+      <c r="L31">
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>95</v>
+      </c>
+      <c r="N31">
+        <v>95</v>
+      </c>
+      <c r="O31">
+        <v>95</v>
+      </c>
+      <c r="P31">
+        <v>95</v>
+      </c>
+      <c r="Q31">
+        <v>95</v>
+      </c>
+      <c r="R31">
+        <v>10</v>
+      </c>
+      <c r="S31">
+        <v>10</v>
+      </c>
+      <c r="T31">
+        <v>10</v>
+      </c>
+      <c r="U31">
+        <v>10</v>
+      </c>
+      <c r="V31">
+        <v>10</v>
+      </c>
+      <c r="W31">
+        <v>10</v>
+      </c>
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+      <c r="Z31">
+        <v>100</v>
+      </c>
+      <c r="AA31">
+        <v>100</v>
+      </c>
+      <c r="AB31">
+        <v>100</v>
+      </c>
+      <c r="AC31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>100</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>10</v>
+      </c>
+      <c r="M32">
+        <v>99</v>
+      </c>
+      <c r="N32">
+        <v>99</v>
+      </c>
+      <c r="O32">
+        <v>99</v>
+      </c>
+      <c r="P32">
+        <v>99</v>
+      </c>
+      <c r="Q32">
+        <v>99</v>
+      </c>
+      <c r="R32">
+        <v>10</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+      <c r="W32">
+        <v>100</v>
+      </c>
+      <c r="X32">
+        <v>100</v>
+      </c>
+      <c r="Y32">
+        <v>100</v>
+      </c>
+      <c r="Z32">
+        <v>100</v>
+      </c>
+      <c r="AA32">
+        <v>100</v>
+      </c>
+      <c r="AB32">
+        <v>100</v>
+      </c>
+      <c r="AC32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>100</v>
+      </c>
+      <c r="B33">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>10</v>
+      </c>
+      <c r="M33">
+        <v>99</v>
+      </c>
+      <c r="N33">
+        <v>93</v>
+      </c>
+      <c r="O33">
+        <v>99</v>
+      </c>
+      <c r="P33">
+        <v>94</v>
+      </c>
+      <c r="Q33">
+        <v>99</v>
+      </c>
+      <c r="R33">
+        <v>10</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
+        <v>100</v>
+      </c>
+      <c r="X33">
+        <v>100</v>
+      </c>
+      <c r="Y33">
+        <v>100</v>
+      </c>
+      <c r="Z33">
+        <v>100</v>
+      </c>
+      <c r="AA33">
+        <v>100</v>
+      </c>
+      <c r="AB33">
+        <v>100</v>
+      </c>
+      <c r="AC33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>100</v>
+      </c>
+      <c r="B34">
+        <v>100</v>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>100</v>
+      </c>
+      <c r="E34">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <v>99</v>
+      </c>
+      <c r="N34">
+        <v>99</v>
+      </c>
+      <c r="O34">
+        <v>99</v>
+      </c>
+      <c r="P34">
+        <v>99</v>
+      </c>
+      <c r="Q34">
+        <v>99</v>
+      </c>
+      <c r="R34">
+        <v>10</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
+        <v>100</v>
+      </c>
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
+        <v>100</v>
+      </c>
+      <c r="X34">
+        <v>100</v>
+      </c>
+      <c r="Y34">
+        <v>100</v>
+      </c>
+      <c r="Z34">
+        <v>100</v>
+      </c>
+      <c r="AA34">
+        <v>100</v>
+      </c>
+      <c r="AB34">
+        <v>100</v>
+      </c>
+      <c r="AC34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35">
+        <v>100</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>10</v>
+      </c>
+      <c r="M35">
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <v>10</v>
+      </c>
+      <c r="P35">
+        <v>10</v>
+      </c>
+      <c r="Q35">
+        <v>10</v>
+      </c>
+      <c r="R35">
+        <v>10</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+      <c r="Z35">
+        <v>100</v>
+      </c>
+      <c r="AA35">
+        <v>100</v>
+      </c>
+      <c r="AB35">
+        <v>100</v>
+      </c>
+      <c r="AC35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="U39" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9912,7 +16388,7 @@
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO16 K16:P16 Q16:AE34 A17:P23 AE17:AO33 A24:K26 L24:P34 K27:K34 A27:J49 AF34:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
+  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 AF9:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
     <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>

--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oskit-my.sharepoint.com/personal/e1q23083_oit_ac_jp/Documents/ゲーム作るやつ/rtbs_C/Assets/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{0A3DB4F9-3A28-4B76-AC52-CE1DA0ABB6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A088F843-C9EF-4AAF-80BD-740188983E7A}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{0A3DB4F9-3A28-4B76-AC52-CE1DA0ABB6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEDFDF7A-9597-453A-872C-FAE699B65CAA}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
   <sheets>
     <sheet name="stage1" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>W</t>
     <phoneticPr fontId="1"/>
@@ -13218,7 +13218,7 @@
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 AF9:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
+  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO49 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
     <cfRule type="expression" dxfId="12" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
@@ -13246,7 +13246,7 @@
     <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>100</v>
       </c>
@@ -13281,7 +13281,7 @@
         <v>100</v>
       </c>
       <c r="L1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M1">
         <v>10</v>
@@ -13302,19 +13302,19 @@
         <v>10</v>
       </c>
       <c r="S1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="U1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="V1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="W1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="X1">
         <v>100</v>
@@ -13334,8 +13334,26 @@
       <c r="AC1">
         <v>100</v>
       </c>
+      <c r="AD1">
+        <v>100</v>
+      </c>
+      <c r="AE1">
+        <v>100</v>
+      </c>
+      <c r="AF1">
+        <v>100</v>
+      </c>
+      <c r="AG1">
+        <v>100</v>
+      </c>
+      <c r="AH1">
+        <v>100</v>
+      </c>
+      <c r="AI1">
+        <v>100</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>100</v>
       </c>
@@ -13370,1303 +13388,1573 @@
         <v>100</v>
       </c>
       <c r="L2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M2">
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>10</v>
+      </c>
+      <c r="X2">
+        <v>100</v>
+      </c>
+      <c r="Y2">
+        <v>100</v>
+      </c>
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>100</v>
+      </c>
+      <c r="AC2">
+        <v>100</v>
+      </c>
+      <c r="AD2">
+        <v>100</v>
+      </c>
+      <c r="AE2">
+        <v>100</v>
+      </c>
+      <c r="AF2">
+        <v>100</v>
+      </c>
+      <c r="AG2">
+        <v>100</v>
+      </c>
+      <c r="AH2">
+        <v>100</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>100</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>71</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>10</v>
+      </c>
+      <c r="X3">
+        <v>100</v>
+      </c>
+      <c r="Y3">
+        <v>100</v>
+      </c>
+      <c r="Z3">
+        <v>100</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>100</v>
+      </c>
+      <c r="AC3">
+        <v>100</v>
+      </c>
+      <c r="AD3">
+        <v>100</v>
+      </c>
+      <c r="AE3">
+        <v>100</v>
+      </c>
+      <c r="AF3">
+        <v>100</v>
+      </c>
+      <c r="AG3">
+        <v>100</v>
+      </c>
+      <c r="AH3">
+        <v>100</v>
+      </c>
+      <c r="AI3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>10</v>
+      </c>
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <v>100</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AB4">
+        <v>100</v>
+      </c>
+      <c r="AC4">
+        <v>100</v>
+      </c>
+      <c r="AD4">
+        <v>100</v>
+      </c>
+      <c r="AE4">
+        <v>100</v>
+      </c>
+      <c r="AF4">
+        <v>100</v>
+      </c>
+      <c r="AG4">
+        <v>100</v>
+      </c>
+      <c r="AH4">
+        <v>100</v>
+      </c>
+      <c r="AI4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>10</v>
+      </c>
+      <c r="Q5">
+        <v>20</v>
+      </c>
+      <c r="R5">
+        <v>20</v>
+      </c>
+      <c r="S5">
+        <v>20</v>
+      </c>
+      <c r="T5">
+        <v>10</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+      <c r="Z5">
+        <v>100</v>
+      </c>
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AB5">
+        <v>100</v>
+      </c>
+      <c r="AC5">
+        <v>100</v>
+      </c>
+      <c r="AD5">
+        <v>100</v>
+      </c>
+      <c r="AE5">
+        <v>100</v>
+      </c>
+      <c r="AF5">
+        <v>100</v>
+      </c>
+      <c r="AG5">
+        <v>100</v>
+      </c>
+      <c r="AH5">
+        <v>100</v>
+      </c>
+      <c r="AI5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>10</v>
+      </c>
+      <c r="Q6">
+        <v>20</v>
+      </c>
+      <c r="R6">
+        <v>20</v>
+      </c>
+      <c r="S6">
+        <v>20</v>
+      </c>
+      <c r="T6">
+        <v>10</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>10</v>
+      </c>
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>100</v>
+      </c>
+      <c r="Z6">
+        <v>100</v>
+      </c>
+      <c r="AA6">
+        <v>100</v>
+      </c>
+      <c r="AB6">
+        <v>100</v>
+      </c>
+      <c r="AC6">
+        <v>100</v>
+      </c>
+      <c r="AD6">
+        <v>100</v>
+      </c>
+      <c r="AE6">
+        <v>100</v>
+      </c>
+      <c r="AF6">
+        <v>100</v>
+      </c>
+      <c r="AG6">
+        <v>100</v>
+      </c>
+      <c r="AH6">
+        <v>100</v>
+      </c>
+      <c r="AI6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>10</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>10</v>
+      </c>
+      <c r="Q7">
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <v>20</v>
+      </c>
+      <c r="S7">
+        <v>20</v>
+      </c>
+      <c r="T7">
+        <v>10</v>
+      </c>
+      <c r="U7">
+        <v>10</v>
+      </c>
+      <c r="V7">
+        <v>10</v>
+      </c>
+      <c r="W7">
+        <v>10</v>
+      </c>
+      <c r="X7">
+        <v>10</v>
+      </c>
+      <c r="Y7">
+        <v>10</v>
+      </c>
+      <c r="Z7">
+        <v>10</v>
+      </c>
+      <c r="AA7">
+        <v>10</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>10</v>
+      </c>
+      <c r="AE7">
+        <v>10</v>
+      </c>
+      <c r="AF7">
+        <v>100</v>
+      </c>
+      <c r="AG7">
+        <v>100</v>
+      </c>
+      <c r="AH7">
+        <v>100</v>
+      </c>
+      <c r="AI7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>100</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>20</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>20</v>
+      </c>
+      <c r="AC8">
+        <v>20</v>
+      </c>
+      <c r="AD8">
+        <v>20</v>
+      </c>
+      <c r="AE8">
+        <v>10</v>
+      </c>
+      <c r="AF8">
+        <v>100</v>
+      </c>
+      <c r="AG8">
+        <v>100</v>
+      </c>
+      <c r="AH8">
+        <v>100</v>
+      </c>
+      <c r="AI8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <v>20</v>
+      </c>
+      <c r="S9">
+        <v>20</v>
+      </c>
+      <c r="T9">
+        <v>10</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>10</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>10</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>10</v>
+      </c>
+      <c r="AB9">
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>20</v>
+      </c>
+      <c r="AE9">
+        <v>10</v>
+      </c>
+      <c r="AF9">
+        <v>100</v>
+      </c>
+      <c r="AG9">
+        <v>100</v>
+      </c>
+      <c r="AH9">
+        <v>100</v>
+      </c>
+      <c r="AI9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>100</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>20</v>
+      </c>
+      <c r="I10">
+        <v>20</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>20</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10">
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <v>20</v>
+      </c>
+      <c r="S10">
+        <v>20</v>
+      </c>
+      <c r="T10">
+        <v>20</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>20</v>
+      </c>
+      <c r="Z10">
+        <v>20</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <v>20</v>
+      </c>
+      <c r="AD10">
+        <v>20</v>
+      </c>
+      <c r="AE10">
+        <v>10</v>
+      </c>
+      <c r="AF10">
+        <v>100</v>
+      </c>
+      <c r="AG10">
+        <v>100</v>
+      </c>
+      <c r="AH10">
+        <v>100</v>
+      </c>
+      <c r="AI10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>20</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>20</v>
+      </c>
+      <c r="R11">
+        <v>20</v>
+      </c>
+      <c r="S11">
+        <v>20</v>
+      </c>
+      <c r="T11">
+        <v>10</v>
+      </c>
+      <c r="U11">
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <v>10</v>
+      </c>
+      <c r="W11">
+        <v>10</v>
+      </c>
+      <c r="X11">
+        <v>10</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
+        <v>20</v>
+      </c>
+      <c r="AA11">
+        <v>10</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>10</v>
+      </c>
+      <c r="AF11">
+        <v>100</v>
+      </c>
+      <c r="AG11">
+        <v>100</v>
+      </c>
+      <c r="AH11">
+        <v>100</v>
+      </c>
+      <c r="AI11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>80</v>
+      </c>
+      <c r="M12">
+        <v>80</v>
+      </c>
+      <c r="N12">
+        <v>80</v>
+      </c>
+      <c r="O12">
+        <v>80</v>
+      </c>
+      <c r="P12">
+        <v>80</v>
+      </c>
+      <c r="Q12">
+        <v>80</v>
+      </c>
+      <c r="R12">
+        <v>80</v>
+      </c>
+      <c r="S12">
+        <v>80</v>
+      </c>
+      <c r="T12">
+        <v>80</v>
+      </c>
+      <c r="U12">
+        <v>80</v>
+      </c>
+      <c r="V12">
+        <v>80</v>
+      </c>
+      <c r="W12">
+        <v>80</v>
+      </c>
+      <c r="X12">
+        <v>80</v>
+      </c>
+      <c r="Y12">
+        <v>10</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>10</v>
+      </c>
+      <c r="AF12">
+        <v>10</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+      <c r="AH12">
+        <v>10</v>
+      </c>
+      <c r="AI12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
         <v>99</v>
       </c>
-      <c r="N2">
+      <c r="C13">
         <v>99</v>
       </c>
-      <c r="O2">
+      <c r="D13">
         <v>99</v>
       </c>
-      <c r="P2">
+      <c r="E13">
+        <v>95</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>80</v>
+      </c>
+      <c r="M13">
+        <v>80</v>
+      </c>
+      <c r="N13">
+        <v>80</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="P13">
+        <v>80</v>
+      </c>
+      <c r="Q13">
+        <v>80</v>
+      </c>
+      <c r="R13">
+        <v>80</v>
+      </c>
+      <c r="S13">
+        <v>80</v>
+      </c>
+      <c r="T13">
+        <v>80</v>
+      </c>
+      <c r="U13">
+        <v>80</v>
+      </c>
+      <c r="V13">
+        <v>80</v>
+      </c>
+      <c r="W13">
+        <v>80</v>
+      </c>
+      <c r="X13">
+        <v>80</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>20</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>95</v>
+      </c>
+      <c r="AF13">
         <v>99</v>
       </c>
-      <c r="Q2">
+      <c r="AG13">
         <v>99</v>
       </c>
-      <c r="R2">
-        <v>10</v>
-      </c>
-      <c r="S2">
-        <v>100</v>
-      </c>
-      <c r="T2">
-        <v>100</v>
-      </c>
-      <c r="U2">
-        <v>100</v>
-      </c>
-      <c r="V2">
-        <v>100</v>
-      </c>
-      <c r="W2">
-        <v>100</v>
-      </c>
-      <c r="X2">
-        <v>100</v>
-      </c>
-      <c r="Y2">
-        <v>100</v>
-      </c>
-      <c r="Z2">
-        <v>100</v>
-      </c>
-      <c r="AA2">
-        <v>100</v>
-      </c>
-      <c r="AB2">
-        <v>100</v>
-      </c>
-      <c r="AC2">
-        <v>100</v>
+      <c r="AH13">
+        <v>99</v>
+      </c>
+      <c r="AI13">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A3">
-        <v>100</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>100</v>
-      </c>
-      <c r="F3">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>100</v>
-      </c>
-      <c r="I3">
-        <v>100</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
-      </c>
-      <c r="K3">
-        <v>100</v>
-      </c>
-      <c r="L3">
-        <v>10</v>
-      </c>
-      <c r="M3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
         <v>99</v>
       </c>
-      <c r="N3">
+      <c r="C14">
+        <v>93</v>
+      </c>
+      <c r="D14">
+        <v>99</v>
+      </c>
+      <c r="E14">
+        <v>95</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>80</v>
+      </c>
+      <c r="O14">
+        <v>80</v>
+      </c>
+      <c r="P14">
+        <v>80</v>
+      </c>
+      <c r="Q14">
+        <v>80</v>
+      </c>
+      <c r="R14">
+        <v>80</v>
+      </c>
+      <c r="S14">
+        <v>80</v>
+      </c>
+      <c r="T14">
+        <v>80</v>
+      </c>
+      <c r="U14">
+        <v>80</v>
+      </c>
+      <c r="V14">
+        <v>80</v>
+      </c>
+      <c r="W14">
+        <v>80</v>
+      </c>
+      <c r="X14">
+        <v>80</v>
+      </c>
+      <c r="Y14">
+        <v>20</v>
+      </c>
+      <c r="Z14">
+        <v>20</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>20</v>
+      </c>
+      <c r="AC14">
+        <v>20</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>95</v>
+      </c>
+      <c r="AF14">
+        <v>99</v>
+      </c>
+      <c r="AG14">
         <v>91</v>
       </c>
-      <c r="O3">
+      <c r="AH14">
         <v>99</v>
       </c>
-      <c r="P3">
+      <c r="AI14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>10</v>
+      </c>
+      <c r="B15">
+        <v>99</v>
+      </c>
+      <c r="C15">
+        <v>99</v>
+      </c>
+      <c r="D15">
+        <v>99</v>
+      </c>
+      <c r="E15">
+        <v>95</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>20</v>
+      </c>
+      <c r="K15">
+        <v>20</v>
+      </c>
+      <c r="L15">
+        <v>80</v>
+      </c>
+      <c r="M15">
+        <v>80</v>
+      </c>
+      <c r="N15">
+        <v>80</v>
+      </c>
+      <c r="O15">
+        <v>80</v>
+      </c>
+      <c r="P15">
+        <v>80</v>
+      </c>
+      <c r="Q15">
+        <v>80</v>
+      </c>
+      <c r="R15">
+        <v>80</v>
+      </c>
+      <c r="S15">
+        <v>80</v>
+      </c>
+      <c r="T15">
+        <v>80</v>
+      </c>
+      <c r="U15">
+        <v>80</v>
+      </c>
+      <c r="V15">
+        <v>80</v>
+      </c>
+      <c r="W15">
+        <v>80</v>
+      </c>
+      <c r="X15">
+        <v>80</v>
+      </c>
+      <c r="Y15">
+        <v>20</v>
+      </c>
+      <c r="Z15">
+        <v>20</v>
+      </c>
+      <c r="AA15">
+        <v>10</v>
+      </c>
+      <c r="AB15">
+        <v>20</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>95</v>
+      </c>
+      <c r="AF15">
+        <v>99</v>
+      </c>
+      <c r="AG15">
+        <v>99</v>
+      </c>
+      <c r="AH15">
+        <v>99</v>
+      </c>
+      <c r="AI15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>99</v>
+      </c>
+      <c r="C16">
+        <v>94</v>
+      </c>
+      <c r="D16">
+        <v>99</v>
+      </c>
+      <c r="E16">
+        <v>95</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>20</v>
+      </c>
+      <c r="L16">
+        <v>80</v>
+      </c>
+      <c r="M16">
+        <v>80</v>
+      </c>
+      <c r="N16">
+        <v>80</v>
+      </c>
+      <c r="O16">
+        <v>80</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>80</v>
+      </c>
+      <c r="R16">
+        <v>80</v>
+      </c>
+      <c r="S16">
+        <v>80</v>
+      </c>
+      <c r="T16">
+        <v>80</v>
+      </c>
+      <c r="U16">
+        <v>80</v>
+      </c>
+      <c r="V16">
+        <v>80</v>
+      </c>
+      <c r="W16">
+        <v>80</v>
+      </c>
+      <c r="X16">
+        <v>80</v>
+      </c>
+      <c r="Y16">
+        <v>20</v>
+      </c>
+      <c r="Z16">
+        <v>20</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>95</v>
+      </c>
+      <c r="AF16">
+        <v>99</v>
+      </c>
+      <c r="AG16">
         <v>92</v>
       </c>
-      <c r="Q3">
+      <c r="AH16">
         <v>99</v>
       </c>
-      <c r="R3">
-        <v>10</v>
-      </c>
-      <c r="S3">
-        <v>100</v>
-      </c>
-      <c r="T3">
-        <v>100</v>
-      </c>
-      <c r="U3">
-        <v>100</v>
-      </c>
-      <c r="V3">
-        <v>100</v>
-      </c>
-      <c r="W3">
-        <v>100</v>
-      </c>
-      <c r="X3">
-        <v>100</v>
-      </c>
-      <c r="Y3">
-        <v>100</v>
-      </c>
-      <c r="Z3">
-        <v>100</v>
-      </c>
-      <c r="AA3">
-        <v>100</v>
-      </c>
-      <c r="AB3">
-        <v>100</v>
-      </c>
-      <c r="AC3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>100</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4">
-        <v>100</v>
-      </c>
-      <c r="L4">
-        <v>10</v>
-      </c>
-      <c r="M4">
-        <v>99</v>
-      </c>
-      <c r="N4">
-        <v>99</v>
-      </c>
-      <c r="O4">
-        <v>99</v>
-      </c>
-      <c r="P4">
-        <v>99</v>
-      </c>
-      <c r="Q4">
-        <v>99</v>
-      </c>
-      <c r="R4">
-        <v>10</v>
-      </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
-      <c r="U4">
-        <v>100</v>
-      </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-      <c r="W4">
-        <v>100</v>
-      </c>
-      <c r="X4">
-        <v>100</v>
-      </c>
-      <c r="Y4">
-        <v>100</v>
-      </c>
-      <c r="Z4">
-        <v>100</v>
-      </c>
-      <c r="AA4">
-        <v>100</v>
-      </c>
-      <c r="AB4">
-        <v>100</v>
-      </c>
-      <c r="AC4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>100</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>10</v>
-      </c>
-      <c r="M5">
-        <v>95</v>
-      </c>
-      <c r="N5">
-        <v>95</v>
-      </c>
-      <c r="O5">
-        <v>95</v>
-      </c>
-      <c r="P5">
-        <v>95</v>
-      </c>
-      <c r="Q5">
-        <v>95</v>
-      </c>
-      <c r="R5">
-        <v>10</v>
-      </c>
-      <c r="S5">
-        <v>10</v>
-      </c>
-      <c r="T5">
-        <v>10</v>
-      </c>
-      <c r="U5">
-        <v>10</v>
-      </c>
-      <c r="V5">
-        <v>10</v>
-      </c>
-      <c r="W5">
-        <v>10</v>
-      </c>
-      <c r="X5">
-        <v>100</v>
-      </c>
-      <c r="Y5">
-        <v>100</v>
-      </c>
-      <c r="Z5">
-        <v>100</v>
-      </c>
-      <c r="AA5">
-        <v>100</v>
-      </c>
-      <c r="AB5">
-        <v>100</v>
-      </c>
-      <c r="AC5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>100</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>20</v>
-      </c>
-      <c r="S6">
-        <v>20</v>
-      </c>
-      <c r="T6">
-        <v>20</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>10</v>
-      </c>
-      <c r="X6">
-        <v>100</v>
-      </c>
-      <c r="Y6">
-        <v>100</v>
-      </c>
-      <c r="Z6">
-        <v>100</v>
-      </c>
-      <c r="AA6">
-        <v>100</v>
-      </c>
-      <c r="AB6">
-        <v>100</v>
-      </c>
-      <c r="AC6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>100</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>20</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
-      </c>
-      <c r="N7">
-        <v>20</v>
-      </c>
-      <c r="O7">
-        <v>10</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>10</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>10</v>
-      </c>
-      <c r="T7">
-        <v>20</v>
-      </c>
-      <c r="U7">
-        <v>10</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>10</v>
-      </c>
-      <c r="X7">
-        <v>100</v>
-      </c>
-      <c r="Y7">
-        <v>100</v>
-      </c>
-      <c r="Z7">
-        <v>100</v>
-      </c>
-      <c r="AA7">
-        <v>100</v>
-      </c>
-      <c r="AB7">
-        <v>100</v>
-      </c>
-      <c r="AC7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>100</v>
-      </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>100</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>20</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>20</v>
-      </c>
-      <c r="O8">
-        <v>20</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>20</v>
-      </c>
-      <c r="T8">
-        <v>20</v>
-      </c>
-      <c r="U8">
-        <v>20</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>10</v>
-      </c>
-      <c r="X8">
-        <v>100</v>
-      </c>
-      <c r="Y8">
-        <v>100</v>
-      </c>
-      <c r="Z8">
-        <v>100</v>
-      </c>
-      <c r="AA8">
-        <v>100</v>
-      </c>
-      <c r="AB8">
-        <v>100</v>
-      </c>
-      <c r="AC8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>100</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>10</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>10</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>10</v>
-      </c>
-      <c r="T9">
-        <v>20</v>
-      </c>
-      <c r="U9">
-        <v>10</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>10</v>
-      </c>
-      <c r="X9">
-        <v>100</v>
-      </c>
-      <c r="Y9">
-        <v>100</v>
-      </c>
-      <c r="Z9">
-        <v>100</v>
-      </c>
-      <c r="AA9">
-        <v>100</v>
-      </c>
-      <c r="AB9">
-        <v>100</v>
-      </c>
-      <c r="AC9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>100</v>
-      </c>
-      <c r="B10">
-        <v>100</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>20</v>
-      </c>
-      <c r="K10">
-        <v>20</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>20</v>
-      </c>
-      <c r="O10">
-        <v>20</v>
-      </c>
-      <c r="P10">
-        <v>20</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>10</v>
-      </c>
-      <c r="X10">
-        <v>100</v>
-      </c>
-      <c r="Y10">
-        <v>100</v>
-      </c>
-      <c r="Z10">
-        <v>100</v>
-      </c>
-      <c r="AA10">
-        <v>100</v>
-      </c>
-      <c r="AB10">
-        <v>100</v>
-      </c>
-      <c r="AC10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>100</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>10</v>
-      </c>
-      <c r="N11">
-        <v>20</v>
-      </c>
-      <c r="O11">
-        <v>20</v>
-      </c>
-      <c r="P11">
-        <v>20</v>
-      </c>
-      <c r="Q11">
-        <v>10</v>
-      </c>
-      <c r="R11">
-        <v>10</v>
-      </c>
-      <c r="S11">
-        <v>10</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>10</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>10</v>
-      </c>
-      <c r="X11">
-        <v>100</v>
-      </c>
-      <c r="Y11">
-        <v>100</v>
-      </c>
-      <c r="Z11">
-        <v>100</v>
-      </c>
-      <c r="AA11">
-        <v>100</v>
-      </c>
-      <c r="AB11">
-        <v>100</v>
-      </c>
-      <c r="AC11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>100</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>100</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-      <c r="F12">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>80</v>
-      </c>
-      <c r="M12">
-        <v>80</v>
-      </c>
-      <c r="N12">
-        <v>80</v>
-      </c>
-      <c r="O12">
-        <v>80</v>
-      </c>
-      <c r="P12">
-        <v>80</v>
-      </c>
-      <c r="Q12">
-        <v>80</v>
-      </c>
-      <c r="R12">
-        <v>80</v>
-      </c>
-      <c r="S12">
-        <v>10</v>
-      </c>
-      <c r="T12">
-        <v>20</v>
-      </c>
-      <c r="U12">
-        <v>20</v>
-      </c>
-      <c r="V12">
-        <v>20</v>
-      </c>
-      <c r="W12">
-        <v>10</v>
-      </c>
-      <c r="X12">
-        <v>100</v>
-      </c>
-      <c r="Y12">
-        <v>100</v>
-      </c>
-      <c r="Z12">
-        <v>100</v>
-      </c>
-      <c r="AA12">
-        <v>100</v>
-      </c>
-      <c r="AB12">
-        <v>100</v>
-      </c>
-      <c r="AC12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <v>80</v>
-      </c>
-      <c r="M13">
-        <v>80</v>
-      </c>
-      <c r="N13">
-        <v>80</v>
-      </c>
-      <c r="O13">
-        <v>80</v>
-      </c>
-      <c r="P13">
-        <v>80</v>
-      </c>
-      <c r="Q13">
-        <v>80</v>
-      </c>
-      <c r="R13">
-        <v>80</v>
-      </c>
-      <c r="S13">
-        <v>10</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>10</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>10</v>
-      </c>
-      <c r="X13">
-        <v>10</v>
-      </c>
-      <c r="Y13">
-        <v>10</v>
-      </c>
-      <c r="Z13">
-        <v>10</v>
-      </c>
-      <c r="AA13">
-        <v>10</v>
-      </c>
-      <c r="AB13">
-        <v>10</v>
-      </c>
-      <c r="AC13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>10</v>
-      </c>
-      <c r="L14">
-        <v>80</v>
-      </c>
-      <c r="M14">
-        <v>80</v>
-      </c>
-      <c r="N14">
-        <v>80</v>
-      </c>
-      <c r="O14">
-        <v>80</v>
-      </c>
-      <c r="P14">
-        <v>80</v>
-      </c>
-      <c r="Q14">
-        <v>80</v>
-      </c>
-      <c r="R14">
-        <v>80</v>
-      </c>
-      <c r="S14">
-        <v>10</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>10</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>10</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>10</v>
-      </c>
-      <c r="L15">
-        <v>80</v>
-      </c>
-      <c r="M15">
-        <v>80</v>
-      </c>
-      <c r="N15">
-        <v>80</v>
-      </c>
-      <c r="O15">
-        <v>80</v>
-      </c>
-      <c r="P15">
-        <v>80</v>
-      </c>
-      <c r="Q15">
-        <v>80</v>
-      </c>
-      <c r="R15">
-        <v>80</v>
-      </c>
-      <c r="S15">
-        <v>10</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>10</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>10</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16">
-        <v>20</v>
-      </c>
-      <c r="K16">
-        <v>10</v>
-      </c>
-      <c r="L16">
-        <v>80</v>
-      </c>
-      <c r="M16">
-        <v>80</v>
-      </c>
-      <c r="N16">
-        <v>80</v>
-      </c>
-      <c r="O16">
-        <v>80</v>
-      </c>
-      <c r="P16">
-        <v>80</v>
-      </c>
-      <c r="Q16">
-        <v>80</v>
-      </c>
-      <c r="R16">
-        <v>80</v>
-      </c>
-      <c r="S16">
-        <v>10</v>
-      </c>
-      <c r="T16">
-        <v>20</v>
-      </c>
-      <c r="U16">
-        <v>10</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>10</v>
-      </c>
-      <c r="X16">
-        <v>10</v>
-      </c>
-      <c r="Y16">
-        <v>10</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
+      <c r="AI16">
         <v>10</v>
       </c>
     </row>
@@ -14675,34 +14963,34 @@
         <v>10</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>80</v>
@@ -14726,36 +15014,54 @@
         <v>80</v>
       </c>
       <c r="S17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="T17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="U17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="W17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="X17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="Y17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>0</v>
       </c>
       <c r="AC17">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>95</v>
+      </c>
+      <c r="AF17">
+        <v>99</v>
+      </c>
+      <c r="AG17">
+        <v>99</v>
+      </c>
+      <c r="AH17">
+        <v>99</v>
+      </c>
+      <c r="AI17">
         <v>10</v>
       </c>
     </row>
@@ -14764,34 +15070,34 @@
         <v>10</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>80</v>
@@ -14815,152 +15121,188 @@
         <v>80</v>
       </c>
       <c r="S18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="T18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="U18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="W18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="X18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="Y18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AB18">
         <v>0</v>
       </c>
       <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>20</v>
+      </c>
+      <c r="AE18">
+        <v>10</v>
+      </c>
+      <c r="AF18">
+        <v>10</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+      <c r="AH18">
+        <v>10</v>
+      </c>
+      <c r="AI18">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>20</v>
       </c>
       <c r="K19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="R19">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S19">
         <v>20</v>
       </c>
       <c r="T19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC19">
         <v>10</v>
+      </c>
+      <c r="AD19">
+        <v>20</v>
+      </c>
+      <c r="AE19">
+        <v>10</v>
+      </c>
+      <c r="AF19">
+        <v>100</v>
+      </c>
+      <c r="AG19">
+        <v>100</v>
+      </c>
+      <c r="AH19">
+        <v>100</v>
+      </c>
+      <c r="AI19">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -14969,90 +15311,108 @@
         <v>20</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="Q20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20">
         <v>20</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="AD20">
+        <v>20</v>
+      </c>
+      <c r="AE20">
+        <v>10</v>
+      </c>
+      <c r="AF20">
+        <v>100</v>
+      </c>
+      <c r="AG20">
+        <v>100</v>
+      </c>
+      <c r="AH20">
+        <v>100</v>
+      </c>
+      <c r="AI20">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G21">
         <v>10</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -15061,31 +15421,31 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="R21">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>0</v>
@@ -15097,48 +15457,66 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC21">
         <v>10</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>10</v>
+      </c>
+      <c r="AF21">
+        <v>100</v>
+      </c>
+      <c r="AG21">
+        <v>100</v>
+      </c>
+      <c r="AH21">
+        <v>100</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -15147,31 +15525,31 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T22">
         <v>0</v>
@@ -15183,10 +15561,10 @@
         <v>0</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -15201,21 +15579,39 @@
         <v>0</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>10</v>
+      </c>
+      <c r="AF22">
+        <v>100</v>
+      </c>
+      <c r="AG22">
+        <v>100</v>
+      </c>
+      <c r="AH22">
+        <v>100</v>
+      </c>
+      <c r="AI22">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>10</v>
@@ -15227,49 +15623,49 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>10</v>
       </c>
       <c r="L23">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="R23">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -15291,6 +15687,24 @@
       </c>
       <c r="AC23">
         <v>10</v>
+      </c>
+      <c r="AD23">
+        <v>10</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>100</v>
+      </c>
+      <c r="AG23">
+        <v>100</v>
+      </c>
+      <c r="AH23">
+        <v>100</v>
+      </c>
+      <c r="AI23">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.4">
@@ -15313,46 +15727,46 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="R24">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>0</v>
@@ -15379,6 +15793,24 @@
         <v>100</v>
       </c>
       <c r="AC24">
+        <v>100</v>
+      </c>
+      <c r="AD24">
+        <v>100</v>
+      </c>
+      <c r="AE24">
+        <v>100</v>
+      </c>
+      <c r="AF24">
+        <v>100</v>
+      </c>
+      <c r="AG24">
+        <v>100</v>
+      </c>
+      <c r="AH24">
+        <v>100</v>
+      </c>
+      <c r="AI24">
         <v>100</v>
       </c>
     </row>
@@ -15402,49 +15834,49 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>10</v>
       </c>
       <c r="N25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -15470,8 +15902,23 @@
       <c r="AC25">
         <v>100</v>
       </c>
-      <c r="AI25" t="s">
-        <v>0</v>
+      <c r="AD25">
+        <v>100</v>
+      </c>
+      <c r="AE25">
+        <v>100</v>
+      </c>
+      <c r="AF25">
+        <v>100</v>
+      </c>
+      <c r="AG25">
+        <v>100</v>
+      </c>
+      <c r="AH25">
+        <v>100</v>
+      </c>
+      <c r="AI25">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.4">
@@ -15494,34 +15941,34 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -15530,10 +15977,10 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -15560,6 +16007,24 @@
         <v>100</v>
       </c>
       <c r="AC26">
+        <v>100</v>
+      </c>
+      <c r="AD26">
+        <v>100</v>
+      </c>
+      <c r="AE26">
+        <v>100</v>
+      </c>
+      <c r="AF26">
+        <v>100</v>
+      </c>
+      <c r="AG26">
+        <v>100</v>
+      </c>
+      <c r="AH26">
+        <v>100</v>
+      </c>
+      <c r="AI26">
         <v>100</v>
       </c>
     </row>
@@ -15583,22 +16048,22 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -15607,25 +16072,25 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -15649,6 +16114,24 @@
         <v>100</v>
       </c>
       <c r="AC27">
+        <v>100</v>
+      </c>
+      <c r="AD27">
+        <v>100</v>
+      </c>
+      <c r="AE27">
+        <v>100</v>
+      </c>
+      <c r="AF27">
+        <v>100</v>
+      </c>
+      <c r="AG27">
+        <v>100</v>
+      </c>
+      <c r="AH27">
+        <v>100</v>
+      </c>
+      <c r="AI27">
         <v>100</v>
       </c>
     </row>
@@ -15672,37 +16155,37 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -15711,13 +16194,13 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -15738,6 +16221,24 @@
         <v>100</v>
       </c>
       <c r="AC28">
+        <v>100</v>
+      </c>
+      <c r="AD28">
+        <v>100</v>
+      </c>
+      <c r="AE28">
+        <v>100</v>
+      </c>
+      <c r="AF28">
+        <v>100</v>
+      </c>
+      <c r="AG28">
+        <v>100</v>
+      </c>
+      <c r="AH28">
+        <v>100</v>
+      </c>
+      <c r="AI28">
         <v>100</v>
       </c>
     </row>
@@ -15761,52 +16262,52 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>10</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>10</v>
       </c>
       <c r="P29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>10</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>10</v>
       </c>
       <c r="T29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -15829,542 +16330,26 @@
       <c r="AC29">
         <v>100</v>
       </c>
+      <c r="AD29">
+        <v>100</v>
+      </c>
+      <c r="AE29">
+        <v>100</v>
+      </c>
+      <c r="AF29">
+        <v>100</v>
+      </c>
+      <c r="AG29">
+        <v>100</v>
+      </c>
+      <c r="AH29">
+        <v>100</v>
+      </c>
+      <c r="AI29">
+        <v>100</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A30">
-        <v>100</v>
-      </c>
-      <c r="B30">
-        <v>100</v>
-      </c>
-      <c r="C30">
-        <v>100</v>
-      </c>
-      <c r="D30">
-        <v>100</v>
-      </c>
-      <c r="E30">
-        <v>100</v>
-      </c>
-      <c r="F30">
-        <v>100</v>
-      </c>
-      <c r="G30">
-        <v>10</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>20</v>
-      </c>
-      <c r="K30">
-        <v>20</v>
-      </c>
-      <c r="L30">
-        <v>20</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>20</v>
-      </c>
-      <c r="U30">
-        <v>20</v>
-      </c>
-      <c r="V30">
-        <v>20</v>
-      </c>
-      <c r="W30">
-        <v>10</v>
-      </c>
-      <c r="X30">
-        <v>100</v>
-      </c>
-      <c r="Y30">
-        <v>100</v>
-      </c>
-      <c r="Z30">
-        <v>100</v>
-      </c>
-      <c r="AA30">
-        <v>100</v>
-      </c>
-      <c r="AB30">
-        <v>100</v>
-      </c>
-      <c r="AC30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A31">
-        <v>100</v>
-      </c>
-      <c r="B31">
-        <v>100</v>
-      </c>
-      <c r="C31">
-        <v>100</v>
-      </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
-      <c r="E31">
-        <v>100</v>
-      </c>
-      <c r="F31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>10</v>
-      </c>
-      <c r="H31">
-        <v>10</v>
-      </c>
-      <c r="I31">
-        <v>10</v>
-      </c>
-      <c r="J31">
-        <v>10</v>
-      </c>
-      <c r="K31">
-        <v>10</v>
-      </c>
-      <c r="L31">
-        <v>10</v>
-      </c>
-      <c r="M31">
-        <v>95</v>
-      </c>
-      <c r="N31">
-        <v>95</v>
-      </c>
-      <c r="O31">
-        <v>95</v>
-      </c>
-      <c r="P31">
-        <v>95</v>
-      </c>
-      <c r="Q31">
-        <v>95</v>
-      </c>
-      <c r="R31">
-        <v>10</v>
-      </c>
-      <c r="S31">
-        <v>10</v>
-      </c>
-      <c r="T31">
-        <v>10</v>
-      </c>
-      <c r="U31">
-        <v>10</v>
-      </c>
-      <c r="V31">
-        <v>10</v>
-      </c>
-      <c r="W31">
-        <v>10</v>
-      </c>
-      <c r="X31">
-        <v>100</v>
-      </c>
-      <c r="Y31">
-        <v>100</v>
-      </c>
-      <c r="Z31">
-        <v>100</v>
-      </c>
-      <c r="AA31">
-        <v>100</v>
-      </c>
-      <c r="AB31">
-        <v>100</v>
-      </c>
-      <c r="AC31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A32">
-        <v>100</v>
-      </c>
-      <c r="B32">
-        <v>100</v>
-      </c>
-      <c r="C32">
-        <v>100</v>
-      </c>
-      <c r="D32">
-        <v>100</v>
-      </c>
-      <c r="E32">
-        <v>100</v>
-      </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
-      <c r="G32">
-        <v>100</v>
-      </c>
-      <c r="H32">
-        <v>100</v>
-      </c>
-      <c r="I32">
-        <v>100</v>
-      </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
-      <c r="K32">
-        <v>100</v>
-      </c>
-      <c r="L32">
-        <v>10</v>
-      </c>
-      <c r="M32">
-        <v>99</v>
-      </c>
-      <c r="N32">
-        <v>99</v>
-      </c>
-      <c r="O32">
-        <v>99</v>
-      </c>
-      <c r="P32">
-        <v>99</v>
-      </c>
-      <c r="Q32">
-        <v>99</v>
-      </c>
-      <c r="R32">
-        <v>10</v>
-      </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-      <c r="T32">
-        <v>100</v>
-      </c>
-      <c r="U32">
-        <v>100</v>
-      </c>
-      <c r="V32">
-        <v>100</v>
-      </c>
-      <c r="W32">
-        <v>100</v>
-      </c>
-      <c r="X32">
-        <v>100</v>
-      </c>
-      <c r="Y32">
-        <v>100</v>
-      </c>
-      <c r="Z32">
-        <v>100</v>
-      </c>
-      <c r="AA32">
-        <v>100</v>
-      </c>
-      <c r="AB32">
-        <v>100</v>
-      </c>
-      <c r="AC32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A33">
-        <v>100</v>
-      </c>
-      <c r="B33">
-        <v>100</v>
-      </c>
-      <c r="C33">
-        <v>100</v>
-      </c>
-      <c r="D33">
-        <v>100</v>
-      </c>
-      <c r="E33">
-        <v>100</v>
-      </c>
-      <c r="F33">
-        <v>100</v>
-      </c>
-      <c r="G33">
-        <v>100</v>
-      </c>
-      <c r="H33">
-        <v>100</v>
-      </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
-      <c r="K33">
-        <v>100</v>
-      </c>
-      <c r="L33">
-        <v>10</v>
-      </c>
-      <c r="M33">
-        <v>99</v>
-      </c>
-      <c r="N33">
-        <v>93</v>
-      </c>
-      <c r="O33">
-        <v>99</v>
-      </c>
-      <c r="P33">
-        <v>94</v>
-      </c>
-      <c r="Q33">
-        <v>99</v>
-      </c>
-      <c r="R33">
-        <v>10</v>
-      </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>100</v>
-      </c>
-      <c r="U33">
-        <v>100</v>
-      </c>
-      <c r="V33">
-        <v>100</v>
-      </c>
-      <c r="W33">
-        <v>100</v>
-      </c>
-      <c r="X33">
-        <v>100</v>
-      </c>
-      <c r="Y33">
-        <v>100</v>
-      </c>
-      <c r="Z33">
-        <v>100</v>
-      </c>
-      <c r="AA33">
-        <v>100</v>
-      </c>
-      <c r="AB33">
-        <v>100</v>
-      </c>
-      <c r="AC33">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A34">
-        <v>100</v>
-      </c>
-      <c r="B34">
-        <v>100</v>
-      </c>
-      <c r="C34">
-        <v>100</v>
-      </c>
-      <c r="D34">
-        <v>100</v>
-      </c>
-      <c r="E34">
-        <v>100</v>
-      </c>
-      <c r="F34">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>100</v>
-      </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
-      <c r="J34">
-        <v>100</v>
-      </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
-      <c r="L34">
-        <v>10</v>
-      </c>
-      <c r="M34">
-        <v>99</v>
-      </c>
-      <c r="N34">
-        <v>99</v>
-      </c>
-      <c r="O34">
-        <v>99</v>
-      </c>
-      <c r="P34">
-        <v>99</v>
-      </c>
-      <c r="Q34">
-        <v>99</v>
-      </c>
-      <c r="R34">
-        <v>10</v>
-      </c>
-      <c r="S34">
-        <v>100</v>
-      </c>
-      <c r="T34">
-        <v>100</v>
-      </c>
-      <c r="U34">
-        <v>100</v>
-      </c>
-      <c r="V34">
-        <v>100</v>
-      </c>
-      <c r="W34">
-        <v>100</v>
-      </c>
-      <c r="X34">
-        <v>100</v>
-      </c>
-      <c r="Y34">
-        <v>100</v>
-      </c>
-      <c r="Z34">
-        <v>100</v>
-      </c>
-      <c r="AA34">
-        <v>100</v>
-      </c>
-      <c r="AB34">
-        <v>100</v>
-      </c>
-      <c r="AC34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A35">
-        <v>100</v>
-      </c>
-      <c r="B35">
-        <v>100</v>
-      </c>
-      <c r="C35">
-        <v>100</v>
-      </c>
-      <c r="D35">
-        <v>100</v>
-      </c>
-      <c r="E35">
-        <v>100</v>
-      </c>
-      <c r="F35">
-        <v>100</v>
-      </c>
-      <c r="G35">
-        <v>100</v>
-      </c>
-      <c r="H35">
-        <v>100</v>
-      </c>
-      <c r="I35">
-        <v>100</v>
-      </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
-      <c r="K35">
-        <v>100</v>
-      </c>
-      <c r="L35">
-        <v>10</v>
-      </c>
-      <c r="M35">
-        <v>10</v>
-      </c>
-      <c r="N35">
-        <v>10</v>
-      </c>
-      <c r="O35">
-        <v>10</v>
-      </c>
-      <c r="P35">
-        <v>10</v>
-      </c>
-      <c r="Q35">
-        <v>10</v>
-      </c>
-      <c r="R35">
-        <v>10</v>
-      </c>
-      <c r="S35">
-        <v>100</v>
-      </c>
-      <c r="T35">
-        <v>100</v>
-      </c>
-      <c r="U35">
-        <v>100</v>
-      </c>
-      <c r="V35">
-        <v>100</v>
-      </c>
-      <c r="W35">
-        <v>100</v>
-      </c>
-      <c r="X35">
-        <v>100</v>
-      </c>
-      <c r="Y35">
-        <v>100</v>
-      </c>
-      <c r="Z35">
-        <v>100</v>
-      </c>
-      <c r="AA35">
-        <v>100</v>
-      </c>
-      <c r="AB35">
-        <v>100</v>
-      </c>
-      <c r="AC35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="39" spans="21:21" x14ac:dyDescent="0.4">
       <c r="U39" t="s">
         <v>1</v>
       </c>
@@ -16388,7 +16373,7 @@
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 AF9:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
+  <conditionalFormatting sqref="AP1:XFD49 AF9:AO49 K16:P16 Q16:AE34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576 Y1:AO8 A12:A17 E23:AD23 B14:E17 A17:P23 F7:AD7 O2:V6 K1:Q8 R2:X8 L31:W35 N24:W35 M23:W28 L24:P34 A24:K35 C5:K5 C6:L6 J22:AA22 L12:X21 W8:AD11 K9:AE15 AC2:AI29 A1:J16 F9:F19 G8:AD8 Z14:Z16 J14:K16">
     <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>

--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oskit-my.sharepoint.com/personal/e1q23083_oit_ac_jp/Documents/ゲーム作るやつ/rtbs_C/Assets/Resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hotat\OneDrive\デスクトップ\GCP\DecoBom\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{0A3DB4F9-3A28-4B76-AC52-CE1DA0ABB6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEDFDF7A-9597-453A-872C-FAE699B65CAA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFC911-854C-499D-8482-EB835791895F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
   <sheets>
     <sheet name="stage1" sheetId="3" r:id="rId1"/>
@@ -100,7 +100,42 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -139,28 +174,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -675,15 +689,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B4B7A3-2A67-49C0-8CF3-3D0110D1C797}">
   <dimension ref="A1:U49"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>100</v>
       </c>
@@ -748,7 +762,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>100</v>
       </c>
@@ -813,7 +827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>100</v>
       </c>
@@ -878,7 +892,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>100</v>
       </c>
@@ -943,7 +957,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1008,7 +1022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>10</v>
       </c>
@@ -1073,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>10</v>
       </c>
@@ -1138,7 +1152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>10</v>
       </c>
@@ -1203,7 +1217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>10</v>
       </c>
@@ -1268,7 +1282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>10</v>
       </c>
@@ -1333,7 +1347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1398,7 +1412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1463,7 +1477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1528,7 +1542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1593,7 +1607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>10</v>
       </c>
@@ -1658,7 +1672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>10</v>
       </c>
@@ -1723,7 +1737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>10</v>
       </c>
@@ -1788,7 +1802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>10</v>
       </c>
@@ -1853,7 +1867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>10</v>
       </c>
@@ -1918,7 +1932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>10</v>
       </c>
@@ -1983,7 +1997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>10</v>
       </c>
@@ -2048,7 +2062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -2113,7 +2127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2178,7 +2192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>10</v>
       </c>
@@ -2243,7 +2257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>10</v>
       </c>
@@ -2308,7 +2322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>10</v>
       </c>
@@ -2373,7 +2387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2438,7 +2452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2503,7 +2517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>10</v>
       </c>
@@ -2568,7 +2582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>10</v>
       </c>
@@ -2633,7 +2647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>10</v>
       </c>
@@ -2698,7 +2712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>10</v>
       </c>
@@ -2763,7 +2777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>10</v>
       </c>
@@ -2828,7 +2842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>10</v>
       </c>
@@ -2893,7 +2907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>10</v>
       </c>
@@ -2958,7 +2972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>10</v>
       </c>
@@ -3023,7 +3037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>10</v>
       </c>
@@ -3088,7 +3102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>10</v>
       </c>
@@ -3153,7 +3167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>10</v>
       </c>
@@ -3218,7 +3232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>10</v>
       </c>
@@ -3283,7 +3297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>10</v>
       </c>
@@ -3348,7 +3362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>10</v>
       </c>
@@ -3413,7 +3427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>10</v>
       </c>
@@ -3478,7 +3492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>10</v>
       </c>
@@ -3543,7 +3557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>10</v>
       </c>
@@ -3608,7 +3622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>100</v>
       </c>
@@ -3673,7 +3687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>100</v>
       </c>
@@ -3738,7 +3752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>100</v>
       </c>
@@ -3803,7 +3817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>100</v>
       </c>
@@ -3871,27 +3885,27 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:G8 O1:U8 V1:XFD49 H2:N8 A9:U49 A50:XFD1048576">
-    <cfRule type="expression" dxfId="33" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="4" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="5" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="6" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="7" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="2" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3902,14 +3916,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA832E2E-F317-49D4-B89F-5814654F6E87}">
   <dimension ref="A1:AO49"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>100</v>
       </c>
@@ -4034,7 +4048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>100</v>
       </c>
@@ -4159,7 +4173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>100</v>
       </c>
@@ -4284,7 +4298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>100</v>
       </c>
@@ -4409,7 +4423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>100</v>
       </c>
@@ -4534,7 +4548,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>100</v>
       </c>
@@ -4659,7 +4673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>100</v>
       </c>
@@ -4784,7 +4798,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>100</v>
       </c>
@@ -4909,7 +4923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>100</v>
       </c>
@@ -5034,7 +5048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>100</v>
       </c>
@@ -5159,7 +5173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>100</v>
       </c>
@@ -5284,7 +5298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>100</v>
       </c>
@@ -5409,7 +5423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>100</v>
       </c>
@@ -5534,7 +5548,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>100</v>
       </c>
@@ -5659,7 +5673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>100</v>
       </c>
@@ -5784,7 +5798,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>100</v>
       </c>
@@ -5909,7 +5923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>10</v>
       </c>
@@ -6034,7 +6048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>10</v>
       </c>
@@ -6159,7 +6173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>10</v>
       </c>
@@ -6284,7 +6298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>10</v>
       </c>
@@ -6409,7 +6423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>10</v>
       </c>
@@ -6534,7 +6548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -6659,7 +6673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -6784,7 +6798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>10</v>
       </c>
@@ -6909,7 +6923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>10</v>
       </c>
@@ -7034,7 +7048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>10</v>
       </c>
@@ -7159,7 +7173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -7284,7 +7298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -7409,7 +7423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>10</v>
       </c>
@@ -7534,7 +7548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>10</v>
       </c>
@@ -7659,7 +7673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>10</v>
       </c>
@@ -7784,7 +7798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>10</v>
       </c>
@@ -7909,7 +7923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>10</v>
       </c>
@@ -8034,7 +8048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>100</v>
       </c>
@@ -8159,7 +8173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>100</v>
       </c>
@@ -8284,7 +8298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>100</v>
       </c>
@@ -8409,7 +8423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>100</v>
       </c>
@@ -8534,7 +8548,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>100</v>
       </c>
@@ -8659,7 +8673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>100</v>
       </c>
@@ -8784,7 +8798,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>100</v>
       </c>
@@ -8909,7 +8923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>100</v>
       </c>
@@ -9034,7 +9048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>100</v>
       </c>
@@ -9159,7 +9173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>100</v>
       </c>
@@ -9284,7 +9298,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>100</v>
       </c>
@@ -9409,7 +9423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>100</v>
       </c>
@@ -9534,7 +9548,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>100</v>
       </c>
@@ -9659,7 +9673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>100</v>
       </c>
@@ -9784,7 +9798,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>100</v>
       </c>
@@ -9909,7 +9923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>100</v>
       </c>
@@ -10037,33 +10051,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="27" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="26" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO16 K16:P16 Q16:AE34 A17:P23 AE17:AO33 A24:K26 L24:P34 K27:K34 A27:J49 AF34:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="21" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10074,14 +10088,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B5306A-7794-4650-A46E-0976E8D9B4A4}">
   <dimension ref="A1:AI35"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>100</v>
       </c>
@@ -10170,7 +10184,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>100</v>
       </c>
@@ -10259,7 +10273,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>100</v>
       </c>
@@ -10348,7 +10362,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>100</v>
       </c>
@@ -10437,7 +10451,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>100</v>
       </c>
@@ -10526,7 +10540,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>100</v>
       </c>
@@ -10615,7 +10629,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>100</v>
       </c>
@@ -10704,7 +10718,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>100</v>
       </c>
@@ -10793,7 +10807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>100</v>
       </c>
@@ -10882,7 +10896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>100</v>
       </c>
@@ -10971,7 +10985,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>100</v>
       </c>
@@ -11060,7 +11074,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>100</v>
       </c>
@@ -11149,7 +11163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>10</v>
       </c>
@@ -11238,7 +11252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>10</v>
       </c>
@@ -11327,7 +11341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>10</v>
       </c>
@@ -11416,7 +11430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>10</v>
       </c>
@@ -11505,7 +11519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>10</v>
       </c>
@@ -11594,7 +11608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>10</v>
       </c>
@@ -11683,7 +11697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>10</v>
       </c>
@@ -11772,7 +11786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>10</v>
       </c>
@@ -11861,7 +11875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>10</v>
       </c>
@@ -11950,7 +11964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -12039,7 +12053,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -12128,7 +12142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>100</v>
       </c>
@@ -12217,7 +12231,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>100</v>
       </c>
@@ -12309,7 +12323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>100</v>
       </c>
@@ -12398,7 +12412,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>100</v>
       </c>
@@ -12487,7 +12501,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>100</v>
       </c>
@@ -12576,7 +12590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>100</v>
       </c>
@@ -12665,7 +12679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>100</v>
       </c>
@@ -12754,7 +12768,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>100</v>
       </c>
@@ -12843,7 +12857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>100</v>
       </c>
@@ -12932,7 +12946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>100</v>
       </c>
@@ -13021,7 +13035,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>100</v>
       </c>
@@ -13110,7 +13124,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>100</v>
       </c>
@@ -13202,33 +13216,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO49 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="12" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13238,15 +13252,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A64FA3-C0B1-40B6-B9C2-665C3D824C39}">
-  <dimension ref="A1:AI39"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AQ39"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="17" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="25" max="41" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="17" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="39" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="4.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>100</v>
       </c>
@@ -13284,76 +13302,100 @@
         <v>100</v>
       </c>
       <c r="M1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="P1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="Q1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="S1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="U1">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="V1">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="W1">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="X1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Z1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AA1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AB1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AC1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AD1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AE1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH1">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AI1">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="AJ1">
+        <v>101</v>
+      </c>
+      <c r="AK1">
+        <v>101</v>
+      </c>
+      <c r="AL1">
+        <v>101</v>
+      </c>
+      <c r="AM1">
+        <v>101</v>
+      </c>
+      <c r="AN1">
+        <v>101</v>
+      </c>
+      <c r="AO1">
+        <v>101</v>
+      </c>
+      <c r="AP1">
+        <v>101</v>
+      </c>
+      <c r="AQ1">
+        <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>100</v>
       </c>
@@ -13391,76 +13433,100 @@
         <v>100</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W2">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="X2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Z2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AB2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AD2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AE2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AH2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="AJ2">
+        <v>101</v>
+      </c>
+      <c r="AK2">
+        <v>101</v>
+      </c>
+      <c r="AL2">
+        <v>101</v>
+      </c>
+      <c r="AM2">
+        <v>101</v>
+      </c>
+      <c r="AN2">
+        <v>101</v>
+      </c>
+      <c r="AO2">
+        <v>101</v>
+      </c>
+      <c r="AP2">
+        <v>101</v>
+      </c>
+      <c r="AQ2">
+        <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>100</v>
       </c>
@@ -13498,2858 +13564,4554 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R3">
+        <v>100</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+      <c r="T3">
+        <v>100</v>
+      </c>
+      <c r="U3">
+        <v>102</v>
+      </c>
+      <c r="V3">
+        <v>102</v>
+      </c>
+      <c r="W3">
+        <v>102</v>
+      </c>
+      <c r="X3">
+        <v>101</v>
+      </c>
+      <c r="Y3">
+        <v>101</v>
+      </c>
+      <c r="Z3">
+        <v>101</v>
+      </c>
+      <c r="AA3">
+        <v>101</v>
+      </c>
+      <c r="AB3">
+        <v>101</v>
+      </c>
+      <c r="AC3">
+        <v>101</v>
+      </c>
+      <c r="AD3">
+        <v>101</v>
+      </c>
+      <c r="AE3">
+        <v>101</v>
+      </c>
+      <c r="AF3">
+        <v>101</v>
+      </c>
+      <c r="AG3">
+        <v>101</v>
+      </c>
+      <c r="AH3">
+        <v>101</v>
+      </c>
+      <c r="AI3">
+        <v>101</v>
+      </c>
+      <c r="AJ3">
+        <v>101</v>
+      </c>
+      <c r="AK3">
+        <v>101</v>
+      </c>
+      <c r="AL3">
+        <v>101</v>
+      </c>
+      <c r="AM3">
+        <v>101</v>
+      </c>
+      <c r="AN3">
+        <v>101</v>
+      </c>
+      <c r="AO3">
+        <v>101</v>
+      </c>
+      <c r="AP3">
+        <v>101</v>
+      </c>
+      <c r="AQ3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>100</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>102</v>
+      </c>
+      <c r="V4">
+        <v>102</v>
+      </c>
+      <c r="W4">
+        <v>102</v>
+      </c>
+      <c r="X4">
+        <v>101</v>
+      </c>
+      <c r="Y4">
+        <v>101</v>
+      </c>
+      <c r="Z4">
+        <v>101</v>
+      </c>
+      <c r="AA4">
+        <v>101</v>
+      </c>
+      <c r="AB4">
+        <v>101</v>
+      </c>
+      <c r="AC4">
+        <v>101</v>
+      </c>
+      <c r="AD4">
+        <v>101</v>
+      </c>
+      <c r="AE4">
+        <v>101</v>
+      </c>
+      <c r="AF4">
+        <v>101</v>
+      </c>
+      <c r="AG4">
+        <v>101</v>
+      </c>
+      <c r="AH4">
+        <v>101</v>
+      </c>
+      <c r="AI4">
+        <v>101</v>
+      </c>
+      <c r="AJ4">
+        <v>101</v>
+      </c>
+      <c r="AK4">
+        <v>101</v>
+      </c>
+      <c r="AL4">
+        <v>101</v>
+      </c>
+      <c r="AM4">
+        <v>101</v>
+      </c>
+      <c r="AN4">
+        <v>101</v>
+      </c>
+      <c r="AO4">
+        <v>101</v>
+      </c>
+      <c r="AP4">
+        <v>101</v>
+      </c>
+      <c r="AQ4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <v>10</v>
+      </c>
+      <c r="T5">
+        <v>10</v>
+      </c>
+      <c r="U5">
+        <v>10</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>10</v>
+      </c>
+      <c r="Y5">
+        <v>10</v>
+      </c>
+      <c r="Z5">
+        <v>10</v>
+      </c>
+      <c r="AA5">
+        <v>10</v>
+      </c>
+      <c r="AB5">
+        <v>101</v>
+      </c>
+      <c r="AC5">
+        <v>101</v>
+      </c>
+      <c r="AD5">
+        <v>101</v>
+      </c>
+      <c r="AE5">
+        <v>101</v>
+      </c>
+      <c r="AF5">
+        <v>101</v>
+      </c>
+      <c r="AG5">
+        <v>101</v>
+      </c>
+      <c r="AH5">
+        <v>101</v>
+      </c>
+      <c r="AI5">
+        <v>101</v>
+      </c>
+      <c r="AJ5">
+        <v>101</v>
+      </c>
+      <c r="AK5">
+        <v>101</v>
+      </c>
+      <c r="AL5">
+        <v>101</v>
+      </c>
+      <c r="AM5">
+        <v>101</v>
+      </c>
+      <c r="AN5">
+        <v>101</v>
+      </c>
+      <c r="AO5">
+        <v>101</v>
+      </c>
+      <c r="AP5">
+        <v>101</v>
+      </c>
+      <c r="AQ5">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>10</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>10</v>
+      </c>
+      <c r="AB6">
+        <v>101</v>
+      </c>
+      <c r="AC6">
+        <v>101</v>
+      </c>
+      <c r="AD6">
+        <v>101</v>
+      </c>
+      <c r="AE6">
+        <v>101</v>
+      </c>
+      <c r="AF6">
+        <v>101</v>
+      </c>
+      <c r="AG6">
+        <v>101</v>
+      </c>
+      <c r="AH6">
+        <v>101</v>
+      </c>
+      <c r="AI6">
+        <v>101</v>
+      </c>
+      <c r="AJ6">
+        <v>101</v>
+      </c>
+      <c r="AK6">
+        <v>101</v>
+      </c>
+      <c r="AL6">
+        <v>101</v>
+      </c>
+      <c r="AM6">
+        <v>101</v>
+      </c>
+      <c r="AN6">
+        <v>101</v>
+      </c>
+      <c r="AO6">
+        <v>101</v>
+      </c>
+      <c r="AP6">
+        <v>101</v>
+      </c>
+      <c r="AQ6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
         <v>71</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>10</v>
-      </c>
-      <c r="X3">
-        <v>100</v>
-      </c>
-      <c r="Y3">
-        <v>100</v>
-      </c>
-      <c r="Z3">
-        <v>100</v>
-      </c>
-      <c r="AA3">
-        <v>100</v>
-      </c>
-      <c r="AB3">
-        <v>100</v>
-      </c>
-      <c r="AC3">
-        <v>100</v>
-      </c>
-      <c r="AD3">
-        <v>100</v>
-      </c>
-      <c r="AE3">
-        <v>100</v>
-      </c>
-      <c r="AF3">
-        <v>100</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>100</v>
-      </c>
-      <c r="AI3">
-        <v>100</v>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>10</v>
+      </c>
+      <c r="AB7">
+        <v>101</v>
+      </c>
+      <c r="AC7">
+        <v>101</v>
+      </c>
+      <c r="AD7">
+        <v>101</v>
+      </c>
+      <c r="AE7">
+        <v>101</v>
+      </c>
+      <c r="AF7">
+        <v>101</v>
+      </c>
+      <c r="AG7">
+        <v>101</v>
+      </c>
+      <c r="AH7">
+        <v>101</v>
+      </c>
+      <c r="AI7">
+        <v>101</v>
+      </c>
+      <c r="AJ7">
+        <v>101</v>
+      </c>
+      <c r="AK7">
+        <v>101</v>
+      </c>
+      <c r="AL7">
+        <v>101</v>
+      </c>
+      <c r="AM7">
+        <v>101</v>
+      </c>
+      <c r="AN7">
+        <v>101</v>
+      </c>
+      <c r="AO7">
+        <v>101</v>
+      </c>
+      <c r="AP7">
+        <v>101</v>
+      </c>
+      <c r="AQ7">
+        <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A4">
-        <v>100</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4">
-        <v>100</v>
-      </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>10</v>
-      </c>
-      <c r="X4">
-        <v>100</v>
-      </c>
-      <c r="Y4">
-        <v>100</v>
-      </c>
-      <c r="Z4">
-        <v>100</v>
-      </c>
-      <c r="AA4">
-        <v>100</v>
-      </c>
-      <c r="AB4">
-        <v>100</v>
-      </c>
-      <c r="AC4">
-        <v>100</v>
-      </c>
-      <c r="AD4">
-        <v>100</v>
-      </c>
-      <c r="AE4">
-        <v>100</v>
-      </c>
-      <c r="AF4">
-        <v>100</v>
-      </c>
-      <c r="AG4">
-        <v>100</v>
-      </c>
-      <c r="AH4">
-        <v>100</v>
-      </c>
-      <c r="AI4">
-        <v>100</v>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>100</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>10</v>
+      </c>
+      <c r="AB8">
+        <v>101</v>
+      </c>
+      <c r="AC8">
+        <v>101</v>
+      </c>
+      <c r="AD8">
+        <v>101</v>
+      </c>
+      <c r="AE8">
+        <v>101</v>
+      </c>
+      <c r="AF8">
+        <v>101</v>
+      </c>
+      <c r="AG8">
+        <v>101</v>
+      </c>
+      <c r="AH8">
+        <v>101</v>
+      </c>
+      <c r="AI8">
+        <v>101</v>
+      </c>
+      <c r="AJ8">
+        <v>101</v>
+      </c>
+      <c r="AK8">
+        <v>101</v>
+      </c>
+      <c r="AL8">
+        <v>101</v>
+      </c>
+      <c r="AM8">
+        <v>101</v>
+      </c>
+      <c r="AN8">
+        <v>101</v>
+      </c>
+      <c r="AO8">
+        <v>101</v>
+      </c>
+      <c r="AP8">
+        <v>101</v>
+      </c>
+      <c r="AQ8">
+        <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>100</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>10</v>
-      </c>
-      <c r="Q5">
-        <v>20</v>
-      </c>
-      <c r="R5">
-        <v>20</v>
-      </c>
-      <c r="S5">
-        <v>20</v>
-      </c>
-      <c r="T5">
-        <v>10</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>10</v>
-      </c>
-      <c r="X5">
-        <v>100</v>
-      </c>
-      <c r="Y5">
-        <v>100</v>
-      </c>
-      <c r="Z5">
-        <v>100</v>
-      </c>
-      <c r="AA5">
-        <v>100</v>
-      </c>
-      <c r="AB5">
-        <v>100</v>
-      </c>
-      <c r="AC5">
-        <v>100</v>
-      </c>
-      <c r="AD5">
-        <v>100</v>
-      </c>
-      <c r="AE5">
-        <v>100</v>
-      </c>
-      <c r="AF5">
-        <v>100</v>
-      </c>
-      <c r="AG5">
-        <v>100</v>
-      </c>
-      <c r="AH5">
-        <v>100</v>
-      </c>
-      <c r="AI5">
-        <v>100</v>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>10</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>10</v>
+      </c>
+      <c r="U9">
+        <v>20</v>
+      </c>
+      <c r="V9">
+        <v>20</v>
+      </c>
+      <c r="W9">
+        <v>20</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>10</v>
+      </c>
+      <c r="AB9">
+        <v>101</v>
+      </c>
+      <c r="AC9">
+        <v>101</v>
+      </c>
+      <c r="AD9">
+        <v>101</v>
+      </c>
+      <c r="AE9">
+        <v>101</v>
+      </c>
+      <c r="AF9">
+        <v>101</v>
+      </c>
+      <c r="AG9">
+        <v>101</v>
+      </c>
+      <c r="AH9">
+        <v>101</v>
+      </c>
+      <c r="AI9">
+        <v>101</v>
+      </c>
+      <c r="AJ9">
+        <v>101</v>
+      </c>
+      <c r="AK9">
+        <v>101</v>
+      </c>
+      <c r="AL9">
+        <v>101</v>
+      </c>
+      <c r="AM9">
+        <v>101</v>
+      </c>
+      <c r="AN9">
+        <v>101</v>
+      </c>
+      <c r="AO9">
+        <v>101</v>
+      </c>
+      <c r="AP9">
+        <v>101</v>
+      </c>
+      <c r="AQ9">
+        <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>100</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-      <c r="K6">
-        <v>100</v>
-      </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>10</v>
-      </c>
-      <c r="Q6">
-        <v>20</v>
-      </c>
-      <c r="R6">
-        <v>20</v>
-      </c>
-      <c r="S6">
-        <v>20</v>
-      </c>
-      <c r="T6">
-        <v>10</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>10</v>
-      </c>
-      <c r="X6">
-        <v>100</v>
-      </c>
-      <c r="Y6">
-        <v>100</v>
-      </c>
-      <c r="Z6">
-        <v>100</v>
-      </c>
-      <c r="AA6">
-        <v>100</v>
-      </c>
-      <c r="AB6">
-        <v>100</v>
-      </c>
-      <c r="AC6">
-        <v>100</v>
-      </c>
-      <c r="AD6">
-        <v>100</v>
-      </c>
-      <c r="AE6">
-        <v>100</v>
-      </c>
-      <c r="AF6">
-        <v>100</v>
-      </c>
-      <c r="AG6">
-        <v>100</v>
-      </c>
-      <c r="AH6">
-        <v>100</v>
-      </c>
-      <c r="AI6">
-        <v>100</v>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>100</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>10</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>10</v>
+      </c>
+      <c r="U10">
+        <v>20</v>
+      </c>
+      <c r="V10">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>20</v>
+      </c>
+      <c r="X10">
+        <v>10</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>10</v>
+      </c>
+      <c r="AB10">
+        <v>101</v>
+      </c>
+      <c r="AC10">
+        <v>101</v>
+      </c>
+      <c r="AD10">
+        <v>101</v>
+      </c>
+      <c r="AE10">
+        <v>101</v>
+      </c>
+      <c r="AF10">
+        <v>101</v>
+      </c>
+      <c r="AG10">
+        <v>101</v>
+      </c>
+      <c r="AH10">
+        <v>101</v>
+      </c>
+      <c r="AI10">
+        <v>101</v>
+      </c>
+      <c r="AJ10">
+        <v>101</v>
+      </c>
+      <c r="AK10">
+        <v>101</v>
+      </c>
+      <c r="AL10">
+        <v>101</v>
+      </c>
+      <c r="AM10">
+        <v>101</v>
+      </c>
+      <c r="AN10">
+        <v>101</v>
+      </c>
+      <c r="AO10">
+        <v>101</v>
+      </c>
+      <c r="AP10">
+        <v>101</v>
+      </c>
+      <c r="AQ10">
+        <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>100</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>10</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>10</v>
-      </c>
-      <c r="N7">
-        <v>10</v>
-      </c>
-      <c r="O7">
-        <v>10</v>
-      </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>20</v>
-      </c>
-      <c r="R7">
-        <v>20</v>
-      </c>
-      <c r="S7">
-        <v>20</v>
-      </c>
-      <c r="T7">
-        <v>10</v>
-      </c>
-      <c r="U7">
-        <v>10</v>
-      </c>
-      <c r="V7">
-        <v>10</v>
-      </c>
-      <c r="W7">
-        <v>10</v>
-      </c>
-      <c r="X7">
-        <v>10</v>
-      </c>
-      <c r="Y7">
-        <v>10</v>
-      </c>
-      <c r="Z7">
-        <v>10</v>
-      </c>
-      <c r="AA7">
-        <v>10</v>
-      </c>
-      <c r="AB7">
-        <v>10</v>
-      </c>
-      <c r="AC7">
-        <v>10</v>
-      </c>
-      <c r="AD7">
-        <v>10</v>
-      </c>
-      <c r="AE7">
-        <v>10</v>
-      </c>
-      <c r="AF7">
-        <v>100</v>
-      </c>
-      <c r="AG7">
-        <v>100</v>
-      </c>
-      <c r="AH7">
-        <v>100</v>
-      </c>
-      <c r="AI7">
-        <v>100</v>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
+        <v>10</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <v>10</v>
+      </c>
+      <c r="U11">
+        <v>20</v>
+      </c>
+      <c r="V11">
+        <v>20</v>
+      </c>
+      <c r="W11">
+        <v>20</v>
+      </c>
+      <c r="X11">
+        <v>10</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
+        <v>10</v>
+      </c>
+      <c r="AA11">
+        <v>10</v>
+      </c>
+      <c r="AB11">
+        <v>10</v>
+      </c>
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11">
+        <v>10</v>
+      </c>
+      <c r="AE11">
+        <v>10</v>
+      </c>
+      <c r="AF11">
+        <v>10</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+      <c r="AH11">
+        <v>10</v>
+      </c>
+      <c r="AI11">
+        <v>10</v>
+      </c>
+      <c r="AJ11">
+        <v>101</v>
+      </c>
+      <c r="AK11">
+        <v>101</v>
+      </c>
+      <c r="AL11">
+        <v>101</v>
+      </c>
+      <c r="AM11">
+        <v>101</v>
+      </c>
+      <c r="AN11">
+        <v>101</v>
+      </c>
+      <c r="AO11">
+        <v>101</v>
+      </c>
+      <c r="AP11">
+        <v>101</v>
+      </c>
+      <c r="AQ11">
+        <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A8">
-        <v>100</v>
-      </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>100</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>20</v>
-      </c>
-      <c r="AC8">
-        <v>20</v>
-      </c>
-      <c r="AD8">
-        <v>20</v>
-      </c>
-      <c r="AE8">
-        <v>10</v>
-      </c>
-      <c r="AF8">
-        <v>100</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>100</v>
-      </c>
-      <c r="AI8">
-        <v>100</v>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>20</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>20</v>
+      </c>
+      <c r="AG12">
+        <v>20</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>10</v>
+      </c>
+      <c r="AJ12">
+        <v>101</v>
+      </c>
+      <c r="AK12">
+        <v>101</v>
+      </c>
+      <c r="AL12">
+        <v>101</v>
+      </c>
+      <c r="AM12">
+        <v>101</v>
+      </c>
+      <c r="AN12">
+        <v>101</v>
+      </c>
+      <c r="AO12">
+        <v>101</v>
+      </c>
+      <c r="AP12">
+        <v>101</v>
+      </c>
+      <c r="AQ12">
+        <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A9">
-        <v>100</v>
-      </c>
-      <c r="B9">
-        <v>100</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9">
-        <v>20</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>10</v>
-      </c>
-      <c r="L9">
-        <v>20</v>
-      </c>
-      <c r="M9">
-        <v>10</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>10</v>
-      </c>
-      <c r="P9">
-        <v>10</v>
-      </c>
-      <c r="Q9">
-        <v>20</v>
-      </c>
-      <c r="R9">
-        <v>20</v>
-      </c>
-      <c r="S9">
-        <v>20</v>
-      </c>
-      <c r="T9">
-        <v>10</v>
-      </c>
-      <c r="U9">
-        <v>10</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>10</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>10</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>10</v>
-      </c>
-      <c r="AB9">
-        <v>20</v>
-      </c>
-      <c r="AC9">
-        <v>10</v>
-      </c>
-      <c r="AD9">
-        <v>20</v>
-      </c>
-      <c r="AE9">
-        <v>10</v>
-      </c>
-      <c r="AF9">
-        <v>100</v>
-      </c>
-      <c r="AG9">
-        <v>100</v>
-      </c>
-      <c r="AH9">
-        <v>100</v>
-      </c>
-      <c r="AI9">
-        <v>100</v>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>100</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>20</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <v>10</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <v>20</v>
+      </c>
+      <c r="V13">
+        <v>20</v>
+      </c>
+      <c r="W13">
+        <v>20</v>
+      </c>
+      <c r="X13">
+        <v>10</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>10</v>
+      </c>
+      <c r="AF13">
+        <v>20</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+      <c r="AH13">
+        <v>20</v>
+      </c>
+      <c r="AI13">
+        <v>10</v>
+      </c>
+      <c r="AJ13">
+        <v>101</v>
+      </c>
+      <c r="AK13">
+        <v>101</v>
+      </c>
+      <c r="AL13">
+        <v>101</v>
+      </c>
+      <c r="AM13">
+        <v>101</v>
+      </c>
+      <c r="AN13">
+        <v>101</v>
+      </c>
+      <c r="AO13">
+        <v>101</v>
+      </c>
+      <c r="AP13">
+        <v>101</v>
+      </c>
+      <c r="AQ13">
+        <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A10">
-        <v>100</v>
-      </c>
-      <c r="B10">
-        <v>100</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>20</v>
-      </c>
-      <c r="G10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="I10">
-        <v>20</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>20</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>20</v>
-      </c>
-      <c r="Q10">
-        <v>20</v>
-      </c>
-      <c r="R10">
-        <v>20</v>
-      </c>
-      <c r="S10">
-        <v>20</v>
-      </c>
-      <c r="T10">
-        <v>20</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>20</v>
-      </c>
-      <c r="Z10">
-        <v>20</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>20</v>
-      </c>
-      <c r="AC10">
-        <v>20</v>
-      </c>
-      <c r="AD10">
-        <v>20</v>
-      </c>
-      <c r="AE10">
-        <v>10</v>
-      </c>
-      <c r="AF10">
-        <v>100</v>
-      </c>
-      <c r="AG10">
-        <v>100</v>
-      </c>
-      <c r="AH10">
-        <v>100</v>
-      </c>
-      <c r="AI10">
-        <v>100</v>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>20</v>
+      </c>
+      <c r="M14">
+        <v>20</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>20</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>20</v>
+      </c>
+      <c r="U14">
+        <v>20</v>
+      </c>
+      <c r="V14">
+        <v>20</v>
+      </c>
+      <c r="W14">
+        <v>20</v>
+      </c>
+      <c r="X14">
+        <v>20</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>20</v>
+      </c>
+      <c r="AD14">
+        <v>20</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>20</v>
+      </c>
+      <c r="AG14">
+        <v>20</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>10</v>
+      </c>
+      <c r="AJ14">
+        <v>101</v>
+      </c>
+      <c r="AK14">
+        <v>101</v>
+      </c>
+      <c r="AL14">
+        <v>101</v>
+      </c>
+      <c r="AM14">
+        <v>101</v>
+      </c>
+      <c r="AN14">
+        <v>101</v>
+      </c>
+      <c r="AO14">
+        <v>101</v>
+      </c>
+      <c r="AP14">
+        <v>101</v>
+      </c>
+      <c r="AQ14">
+        <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A11">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>100</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>10</v>
-      </c>
-      <c r="N11">
-        <v>10</v>
-      </c>
-      <c r="O11">
-        <v>10</v>
-      </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-      <c r="Q11">
-        <v>20</v>
-      </c>
-      <c r="R11">
-        <v>20</v>
-      </c>
-      <c r="S11">
-        <v>20</v>
-      </c>
-      <c r="T11">
-        <v>10</v>
-      </c>
-      <c r="U11">
-        <v>10</v>
-      </c>
-      <c r="V11">
-        <v>10</v>
-      </c>
-      <c r="W11">
-        <v>10</v>
-      </c>
-      <c r="X11">
-        <v>10</v>
-      </c>
-      <c r="Y11">
-        <v>10</v>
-      </c>
-      <c r="Z11">
-        <v>20</v>
-      </c>
-      <c r="AA11">
-        <v>10</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>10</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>10</v>
-      </c>
-      <c r="AF11">
-        <v>100</v>
-      </c>
-      <c r="AG11">
-        <v>100</v>
-      </c>
-      <c r="AH11">
-        <v>100</v>
-      </c>
-      <c r="AI11">
-        <v>100</v>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>100</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>20</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>10</v>
+      </c>
+      <c r="R15">
+        <v>10</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+      <c r="T15">
+        <v>10</v>
+      </c>
+      <c r="U15">
+        <v>20</v>
+      </c>
+      <c r="V15">
+        <v>20</v>
+      </c>
+      <c r="W15">
+        <v>20</v>
+      </c>
+      <c r="X15">
+        <v>10</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>10</v>
+      </c>
+      <c r="AA15">
+        <v>10</v>
+      </c>
+      <c r="AB15">
+        <v>10</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>20</v>
+      </c>
+      <c r="AE15">
+        <v>10</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>10</v>
+      </c>
+      <c r="AJ15">
+        <v>101</v>
+      </c>
+      <c r="AK15">
+        <v>101</v>
+      </c>
+      <c r="AL15">
+        <v>101</v>
+      </c>
+      <c r="AM15">
+        <v>101</v>
+      </c>
+      <c r="AN15">
+        <v>101</v>
+      </c>
+      <c r="AO15">
+        <v>101</v>
+      </c>
+      <c r="AP15">
+        <v>101</v>
+      </c>
+      <c r="AQ15">
+        <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>20</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>10</v>
-      </c>
-      <c r="L12">
-        <v>80</v>
-      </c>
-      <c r="M12">
-        <v>80</v>
-      </c>
-      <c r="N12">
-        <v>80</v>
-      </c>
-      <c r="O12">
-        <v>80</v>
-      </c>
-      <c r="P12">
-        <v>80</v>
-      </c>
-      <c r="Q12">
-        <v>80</v>
-      </c>
-      <c r="R12">
-        <v>80</v>
-      </c>
-      <c r="S12">
-        <v>80</v>
-      </c>
-      <c r="T12">
-        <v>80</v>
-      </c>
-      <c r="U12">
-        <v>80</v>
-      </c>
-      <c r="V12">
-        <v>80</v>
-      </c>
-      <c r="W12">
-        <v>80</v>
-      </c>
-      <c r="X12">
-        <v>80</v>
-      </c>
-      <c r="Y12">
-        <v>10</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>10</v>
-      </c>
-      <c r="AF12">
-        <v>10</v>
-      </c>
-      <c r="AG12">
-        <v>10</v>
-      </c>
-      <c r="AH12">
-        <v>10</v>
-      </c>
-      <c r="AI12">
-        <v>10</v>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>100</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>80</v>
+      </c>
+      <c r="R16">
+        <v>80</v>
+      </c>
+      <c r="S16">
+        <v>80</v>
+      </c>
+      <c r="T16">
+        <v>80</v>
+      </c>
+      <c r="U16">
+        <v>80</v>
+      </c>
+      <c r="V16">
+        <v>80</v>
+      </c>
+      <c r="W16">
+        <v>80</v>
+      </c>
+      <c r="X16">
+        <v>80</v>
+      </c>
+      <c r="Y16">
+        <v>80</v>
+      </c>
+      <c r="Z16">
+        <v>80</v>
+      </c>
+      <c r="AA16">
+        <v>80</v>
+      </c>
+      <c r="AB16">
+        <v>80</v>
+      </c>
+      <c r="AC16">
+        <v>10</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>10</v>
+      </c>
+      <c r="AJ16">
+        <v>10</v>
+      </c>
+      <c r="AK16">
+        <v>10</v>
+      </c>
+      <c r="AL16">
+        <v>10</v>
+      </c>
+      <c r="AM16">
+        <v>10</v>
+      </c>
+      <c r="AN16">
+        <v>101</v>
+      </c>
+      <c r="AO16">
+        <v>101</v>
+      </c>
+      <c r="AP16">
+        <v>101</v>
+      </c>
+      <c r="AQ16">
+        <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>100</v>
+      </c>
+      <c r="B17">
+        <v>100</v>
+      </c>
+      <c r="C17">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
         <v>99</v>
       </c>
-      <c r="C13">
+      <c r="G17">
         <v>99</v>
       </c>
-      <c r="D13">
+      <c r="H17">
         <v>99</v>
       </c>
-      <c r="E13">
+      <c r="I17">
         <v>95</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <v>80</v>
-      </c>
-      <c r="M13">
-        <v>80</v>
-      </c>
-      <c r="N13">
-        <v>80</v>
-      </c>
-      <c r="O13">
-        <v>80</v>
-      </c>
-      <c r="P13">
-        <v>80</v>
-      </c>
-      <c r="Q13">
-        <v>80</v>
-      </c>
-      <c r="R13">
-        <v>80</v>
-      </c>
-      <c r="S13">
-        <v>80</v>
-      </c>
-      <c r="T13">
-        <v>80</v>
-      </c>
-      <c r="U13">
-        <v>80</v>
-      </c>
-      <c r="V13">
-        <v>80</v>
-      </c>
-      <c r="W13">
-        <v>80</v>
-      </c>
-      <c r="X13">
-        <v>80</v>
-      </c>
-      <c r="Y13">
-        <v>10</v>
-      </c>
-      <c r="Z13">
-        <v>10</v>
-      </c>
-      <c r="AA13">
-        <v>10</v>
-      </c>
-      <c r="AB13">
-        <v>20</v>
-      </c>
-      <c r="AC13">
-        <v>10</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>10</v>
+      </c>
+      <c r="P17">
+        <v>80</v>
+      </c>
+      <c r="Q17">
+        <v>80</v>
+      </c>
+      <c r="R17">
+        <v>80</v>
+      </c>
+      <c r="S17">
+        <v>80</v>
+      </c>
+      <c r="T17">
+        <v>80</v>
+      </c>
+      <c r="U17">
+        <v>80</v>
+      </c>
+      <c r="V17">
+        <v>80</v>
+      </c>
+      <c r="W17">
+        <v>80</v>
+      </c>
+      <c r="X17">
+        <v>80</v>
+      </c>
+      <c r="Y17">
+        <v>80</v>
+      </c>
+      <c r="Z17">
+        <v>80</v>
+      </c>
+      <c r="AA17">
+        <v>80</v>
+      </c>
+      <c r="AB17">
+        <v>80</v>
+      </c>
+      <c r="AC17">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>10</v>
+      </c>
+      <c r="AE17">
+        <v>10</v>
+      </c>
+      <c r="AF17">
+        <v>20</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
         <v>95</v>
       </c>
-      <c r="AF13">
+      <c r="AJ17">
         <v>99</v>
       </c>
-      <c r="AG13">
+      <c r="AK17">
         <v>99</v>
       </c>
-      <c r="AH13">
+      <c r="AL17">
         <v>99</v>
       </c>
-      <c r="AI13">
-        <v>10</v>
+      <c r="AM17">
+        <v>10</v>
+      </c>
+      <c r="AN17">
+        <v>101</v>
+      </c>
+      <c r="AO17">
+        <v>101</v>
+      </c>
+      <c r="AP17">
+        <v>101</v>
+      </c>
+      <c r="AQ17">
+        <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>100</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
         <v>99</v>
       </c>
-      <c r="C14">
+      <c r="G18">
         <v>93</v>
       </c>
-      <c r="D14">
+      <c r="H18">
         <v>99</v>
       </c>
-      <c r="E14">
+      <c r="I18">
         <v>95</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>20</v>
-      </c>
-      <c r="K14">
-        <v>20</v>
-      </c>
-      <c r="L14">
-        <v>80</v>
-      </c>
-      <c r="M14">
-        <v>80</v>
-      </c>
-      <c r="N14">
-        <v>80</v>
-      </c>
-      <c r="O14">
-        <v>80</v>
-      </c>
-      <c r="P14">
-        <v>80</v>
-      </c>
-      <c r="Q14">
-        <v>80</v>
-      </c>
-      <c r="R14">
-        <v>80</v>
-      </c>
-      <c r="S14">
-        <v>80</v>
-      </c>
-      <c r="T14">
-        <v>80</v>
-      </c>
-      <c r="U14">
-        <v>80</v>
-      </c>
-      <c r="V14">
-        <v>80</v>
-      </c>
-      <c r="W14">
-        <v>80</v>
-      </c>
-      <c r="X14">
-        <v>80</v>
-      </c>
-      <c r="Y14">
-        <v>20</v>
-      </c>
-      <c r="Z14">
-        <v>20</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>20</v>
-      </c>
-      <c r="AC14">
-        <v>20</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>20</v>
+      </c>
+      <c r="O18">
+        <v>20</v>
+      </c>
+      <c r="P18">
+        <v>80</v>
+      </c>
+      <c r="Q18">
+        <v>80</v>
+      </c>
+      <c r="R18">
+        <v>80</v>
+      </c>
+      <c r="S18">
+        <v>80</v>
+      </c>
+      <c r="T18">
+        <v>80</v>
+      </c>
+      <c r="U18">
+        <v>80</v>
+      </c>
+      <c r="V18">
+        <v>80</v>
+      </c>
+      <c r="W18">
+        <v>80</v>
+      </c>
+      <c r="X18">
+        <v>80</v>
+      </c>
+      <c r="Y18">
+        <v>80</v>
+      </c>
+      <c r="Z18">
+        <v>80</v>
+      </c>
+      <c r="AA18">
+        <v>80</v>
+      </c>
+      <c r="AB18">
+        <v>80</v>
+      </c>
+      <c r="AC18">
+        <v>20</v>
+      </c>
+      <c r="AD18">
+        <v>20</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>20</v>
+      </c>
+      <c r="AG18">
+        <v>20</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
         <v>95</v>
       </c>
-      <c r="AF14">
+      <c r="AJ18">
         <v>99</v>
       </c>
-      <c r="AG14">
+      <c r="AK18">
         <v>91</v>
       </c>
-      <c r="AH14">
+      <c r="AL18">
         <v>99</v>
       </c>
-      <c r="AI14">
-        <v>10</v>
+      <c r="AM18">
+        <v>10</v>
+      </c>
+      <c r="AN18">
+        <v>101</v>
+      </c>
+      <c r="AO18">
+        <v>101</v>
+      </c>
+      <c r="AP18">
+        <v>101</v>
+      </c>
+      <c r="AQ18">
+        <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>10</v>
-      </c>
-      <c r="B15">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>100</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
         <v>99</v>
       </c>
-      <c r="C15">
+      <c r="G19">
         <v>99</v>
       </c>
-      <c r="D15">
+      <c r="H19">
         <v>99</v>
       </c>
-      <c r="E15">
+      <c r="I19">
         <v>95</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>10</v>
-      </c>
-      <c r="H15">
-        <v>20</v>
-      </c>
-      <c r="I15">
-        <v>10</v>
-      </c>
-      <c r="J15">
-        <v>20</v>
-      </c>
-      <c r="K15">
-        <v>20</v>
-      </c>
-      <c r="L15">
-        <v>80</v>
-      </c>
-      <c r="M15">
-        <v>80</v>
-      </c>
-      <c r="N15">
-        <v>80</v>
-      </c>
-      <c r="O15">
-        <v>80</v>
-      </c>
-      <c r="P15">
-        <v>80</v>
-      </c>
-      <c r="Q15">
-        <v>80</v>
-      </c>
-      <c r="R15">
-        <v>80</v>
-      </c>
-      <c r="S15">
-        <v>80</v>
-      </c>
-      <c r="T15">
-        <v>80</v>
-      </c>
-      <c r="U15">
-        <v>80</v>
-      </c>
-      <c r="V15">
-        <v>80</v>
-      </c>
-      <c r="W15">
-        <v>80</v>
-      </c>
-      <c r="X15">
-        <v>80</v>
-      </c>
-      <c r="Y15">
-        <v>20</v>
-      </c>
-      <c r="Z15">
-        <v>20</v>
-      </c>
-      <c r="AA15">
-        <v>10</v>
-      </c>
-      <c r="AB15">
-        <v>20</v>
-      </c>
-      <c r="AC15">
-        <v>10</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>20</v>
+      </c>
+      <c r="M19">
+        <v>10</v>
+      </c>
+      <c r="N19">
+        <v>20</v>
+      </c>
+      <c r="O19">
+        <v>20</v>
+      </c>
+      <c r="P19">
+        <v>80</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
+      </c>
+      <c r="R19">
+        <v>80</v>
+      </c>
+      <c r="S19">
+        <v>80</v>
+      </c>
+      <c r="T19">
+        <v>80</v>
+      </c>
+      <c r="U19">
+        <v>80</v>
+      </c>
+      <c r="V19">
+        <v>80</v>
+      </c>
+      <c r="W19">
+        <v>80</v>
+      </c>
+      <c r="X19">
+        <v>80</v>
+      </c>
+      <c r="Y19">
+        <v>80</v>
+      </c>
+      <c r="Z19">
+        <v>80</v>
+      </c>
+      <c r="AA19">
+        <v>80</v>
+      </c>
+      <c r="AB19">
+        <v>80</v>
+      </c>
+      <c r="AC19">
+        <v>20</v>
+      </c>
+      <c r="AD19">
+        <v>20</v>
+      </c>
+      <c r="AE19">
+        <v>10</v>
+      </c>
+      <c r="AF19">
+        <v>20</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
         <v>95</v>
       </c>
-      <c r="AF15">
+      <c r="AJ19">
         <v>99</v>
       </c>
-      <c r="AG15">
+      <c r="AK19">
         <v>99</v>
       </c>
-      <c r="AH15">
+      <c r="AL19">
         <v>99</v>
       </c>
-      <c r="AI15">
-        <v>10</v>
+      <c r="AM19">
+        <v>10</v>
+      </c>
+      <c r="AN19">
+        <v>101</v>
+      </c>
+      <c r="AO19">
+        <v>101</v>
+      </c>
+      <c r="AP19">
+        <v>101</v>
+      </c>
+      <c r="AQ19">
+        <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>100</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
         <v>99</v>
       </c>
-      <c r="C16">
+      <c r="G20">
         <v>94</v>
       </c>
-      <c r="D16">
+      <c r="H20">
         <v>99</v>
       </c>
-      <c r="E16">
+      <c r="I20">
         <v>95</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>20</v>
-      </c>
-      <c r="H16">
-        <v>20</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>20</v>
-      </c>
-      <c r="K16">
-        <v>20</v>
-      </c>
-      <c r="L16">
-        <v>80</v>
-      </c>
-      <c r="M16">
-        <v>80</v>
-      </c>
-      <c r="N16">
-        <v>80</v>
-      </c>
-      <c r="O16">
-        <v>80</v>
-      </c>
-      <c r="P16">
-        <v>80</v>
-      </c>
-      <c r="Q16">
-        <v>80</v>
-      </c>
-      <c r="R16">
-        <v>80</v>
-      </c>
-      <c r="S16">
-        <v>80</v>
-      </c>
-      <c r="T16">
-        <v>80</v>
-      </c>
-      <c r="U16">
-        <v>80</v>
-      </c>
-      <c r="V16">
-        <v>80</v>
-      </c>
-      <c r="W16">
-        <v>80</v>
-      </c>
-      <c r="X16">
-        <v>80</v>
-      </c>
-      <c r="Y16">
-        <v>20</v>
-      </c>
-      <c r="Z16">
-        <v>20</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>20</v>
+      </c>
+      <c r="L20">
+        <v>20</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>20</v>
+      </c>
+      <c r="O20">
+        <v>20</v>
+      </c>
+      <c r="P20">
+        <v>80</v>
+      </c>
+      <c r="Q20">
+        <v>80</v>
+      </c>
+      <c r="R20">
+        <v>80</v>
+      </c>
+      <c r="S20">
+        <v>80</v>
+      </c>
+      <c r="T20">
+        <v>80</v>
+      </c>
+      <c r="U20">
+        <v>80</v>
+      </c>
+      <c r="V20">
+        <v>80</v>
+      </c>
+      <c r="W20">
+        <v>80</v>
+      </c>
+      <c r="X20">
+        <v>80</v>
+      </c>
+      <c r="Y20">
+        <v>80</v>
+      </c>
+      <c r="Z20">
+        <v>80</v>
+      </c>
+      <c r="AA20">
+        <v>80</v>
+      </c>
+      <c r="AB20">
+        <v>80</v>
+      </c>
+      <c r="AC20">
+        <v>20</v>
+      </c>
+      <c r="AD20">
+        <v>20</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
         <v>95</v>
       </c>
-      <c r="AF16">
+      <c r="AJ20">
         <v>99</v>
       </c>
-      <c r="AG16">
+      <c r="AK20">
         <v>92</v>
       </c>
-      <c r="AH16">
+      <c r="AL20">
         <v>99</v>
       </c>
-      <c r="AI16">
-        <v>10</v>
+      <c r="AM20">
+        <v>10</v>
+      </c>
+      <c r="AN20">
+        <v>101</v>
+      </c>
+      <c r="AO20">
+        <v>101</v>
+      </c>
+      <c r="AP20">
+        <v>101</v>
+      </c>
+      <c r="AQ20">
+        <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>100</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>100</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
         <v>99</v>
       </c>
-      <c r="C17">
+      <c r="G21">
         <v>99</v>
       </c>
-      <c r="D17">
+      <c r="H21">
         <v>99</v>
       </c>
-      <c r="E17">
+      <c r="I21">
         <v>95</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>10</v>
-      </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
-      <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>10</v>
-      </c>
-      <c r="L17">
-        <v>80</v>
-      </c>
-      <c r="M17">
-        <v>80</v>
-      </c>
-      <c r="N17">
-        <v>80</v>
-      </c>
-      <c r="O17">
-        <v>80</v>
-      </c>
-      <c r="P17">
-        <v>80</v>
-      </c>
-      <c r="Q17">
-        <v>80</v>
-      </c>
-      <c r="R17">
-        <v>80</v>
-      </c>
-      <c r="S17">
-        <v>80</v>
-      </c>
-      <c r="T17">
-        <v>80</v>
-      </c>
-      <c r="U17">
-        <v>80</v>
-      </c>
-      <c r="V17">
-        <v>80</v>
-      </c>
-      <c r="W17">
-        <v>80</v>
-      </c>
-      <c r="X17">
-        <v>80</v>
-      </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>10</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>10</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>20</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>10</v>
+      </c>
+      <c r="P21">
+        <v>80</v>
+      </c>
+      <c r="Q21">
+        <v>80</v>
+      </c>
+      <c r="R21">
+        <v>80</v>
+      </c>
+      <c r="S21">
+        <v>80</v>
+      </c>
+      <c r="T21">
+        <v>80</v>
+      </c>
+      <c r="U21">
+        <v>80</v>
+      </c>
+      <c r="V21">
+        <v>80</v>
+      </c>
+      <c r="W21">
+        <v>80</v>
+      </c>
+      <c r="X21">
+        <v>80</v>
+      </c>
+      <c r="Y21">
+        <v>80</v>
+      </c>
+      <c r="Z21">
+        <v>80</v>
+      </c>
+      <c r="AA21">
+        <v>80</v>
+      </c>
+      <c r="AB21">
+        <v>80</v>
+      </c>
+      <c r="AC21">
+        <v>10</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>10</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
         <v>95</v>
       </c>
-      <c r="AF17">
+      <c r="AJ21">
         <v>99</v>
       </c>
-      <c r="AG17">
+      <c r="AK21">
         <v>99</v>
       </c>
-      <c r="AH17">
+      <c r="AL21">
         <v>99</v>
       </c>
-      <c r="AI17">
-        <v>10</v>
+      <c r="AM21">
+        <v>10</v>
+      </c>
+      <c r="AN21">
+        <v>101</v>
+      </c>
+      <c r="AO21">
+        <v>101</v>
+      </c>
+      <c r="AP21">
+        <v>101</v>
+      </c>
+      <c r="AQ21">
+        <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A18">
-        <v>10</v>
-      </c>
-      <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>10</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>10</v>
-      </c>
-      <c r="L18">
-        <v>80</v>
-      </c>
-      <c r="M18">
-        <v>80</v>
-      </c>
-      <c r="N18">
-        <v>80</v>
-      </c>
-      <c r="O18">
-        <v>80</v>
-      </c>
-      <c r="P18">
-        <v>80</v>
-      </c>
-      <c r="Q18">
-        <v>80</v>
-      </c>
-      <c r="R18">
-        <v>80</v>
-      </c>
-      <c r="S18">
-        <v>80</v>
-      </c>
-      <c r="T18">
-        <v>80</v>
-      </c>
-      <c r="U18">
-        <v>80</v>
-      </c>
-      <c r="V18">
-        <v>80</v>
-      </c>
-      <c r="W18">
-        <v>80</v>
-      </c>
-      <c r="X18">
-        <v>80</v>
-      </c>
-      <c r="Y18">
-        <v>10</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>20</v>
-      </c>
-      <c r="AE18">
-        <v>10</v>
-      </c>
-      <c r="AF18">
-        <v>10</v>
-      </c>
-      <c r="AG18">
-        <v>10</v>
-      </c>
-      <c r="AH18">
-        <v>10</v>
-      </c>
-      <c r="AI18">
-        <v>10</v>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>100</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
+        <v>100</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>10</v>
+      </c>
+      <c r="P22">
+        <v>80</v>
+      </c>
+      <c r="Q22">
+        <v>80</v>
+      </c>
+      <c r="R22">
+        <v>80</v>
+      </c>
+      <c r="S22">
+        <v>80</v>
+      </c>
+      <c r="T22">
+        <v>80</v>
+      </c>
+      <c r="U22">
+        <v>80</v>
+      </c>
+      <c r="V22">
+        <v>80</v>
+      </c>
+      <c r="W22">
+        <v>80</v>
+      </c>
+      <c r="X22">
+        <v>80</v>
+      </c>
+      <c r="Y22">
+        <v>80</v>
+      </c>
+      <c r="Z22">
+        <v>80</v>
+      </c>
+      <c r="AA22">
+        <v>80</v>
+      </c>
+      <c r="AB22">
+        <v>80</v>
+      </c>
+      <c r="AC22">
+        <v>10</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>20</v>
+      </c>
+      <c r="AI22">
+        <v>10</v>
+      </c>
+      <c r="AJ22">
+        <v>10</v>
+      </c>
+      <c r="AK22">
+        <v>10</v>
+      </c>
+      <c r="AL22">
+        <v>10</v>
+      </c>
+      <c r="AM22">
+        <v>10</v>
+      </c>
+      <c r="AN22">
+        <v>101</v>
+      </c>
+      <c r="AO22">
+        <v>101</v>
+      </c>
+      <c r="AP22">
+        <v>101</v>
+      </c>
+      <c r="AQ22">
+        <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>100</v>
-      </c>
-      <c r="B19">
-        <v>100</v>
-      </c>
-      <c r="C19">
-        <v>100</v>
-      </c>
-      <c r="D19">
-        <v>100</v>
-      </c>
-      <c r="E19">
-        <v>10</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>10</v>
-      </c>
-      <c r="J19">
-        <v>20</v>
-      </c>
-      <c r="K19">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <v>10</v>
-      </c>
-      <c r="M19">
-        <v>10</v>
-      </c>
-      <c r="N19">
-        <v>10</v>
-      </c>
-      <c r="O19">
-        <v>10</v>
-      </c>
-      <c r="P19">
-        <v>10</v>
-      </c>
-      <c r="Q19">
-        <v>20</v>
-      </c>
-      <c r="R19">
-        <v>20</v>
-      </c>
-      <c r="S19">
-        <v>20</v>
-      </c>
-      <c r="T19">
-        <v>10</v>
-      </c>
-      <c r="U19">
-        <v>10</v>
-      </c>
-      <c r="V19">
-        <v>10</v>
-      </c>
-      <c r="W19">
-        <v>10</v>
-      </c>
-      <c r="X19">
-        <v>10</v>
-      </c>
-      <c r="Y19">
-        <v>10</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>10</v>
-      </c>
-      <c r="AB19">
-        <v>20</v>
-      </c>
-      <c r="AC19">
-        <v>10</v>
-      </c>
-      <c r="AD19">
-        <v>20</v>
-      </c>
-      <c r="AE19">
-        <v>10</v>
-      </c>
-      <c r="AF19">
-        <v>100</v>
-      </c>
-      <c r="AG19">
-        <v>100</v>
-      </c>
-      <c r="AH19">
-        <v>100</v>
-      </c>
-      <c r="AI19">
-        <v>100</v>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>100</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>20</v>
+      </c>
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23">
+        <v>10</v>
+      </c>
+      <c r="Q23">
+        <v>10</v>
+      </c>
+      <c r="R23">
+        <v>10</v>
+      </c>
+      <c r="S23">
+        <v>10</v>
+      </c>
+      <c r="T23">
+        <v>10</v>
+      </c>
+      <c r="U23">
+        <v>20</v>
+      </c>
+      <c r="V23">
+        <v>20</v>
+      </c>
+      <c r="W23">
+        <v>20</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
+        <v>10</v>
+      </c>
+      <c r="Z23">
+        <v>10</v>
+      </c>
+      <c r="AA23">
+        <v>10</v>
+      </c>
+      <c r="AB23">
+        <v>10</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>20</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+      <c r="AH23">
+        <v>20</v>
+      </c>
+      <c r="AI23">
+        <v>10</v>
+      </c>
+      <c r="AJ23">
+        <v>101</v>
+      </c>
+      <c r="AK23">
+        <v>101</v>
+      </c>
+      <c r="AL23">
+        <v>101</v>
+      </c>
+      <c r="AM23">
+        <v>101</v>
+      </c>
+      <c r="AN23">
+        <v>101</v>
+      </c>
+      <c r="AO23">
+        <v>101</v>
+      </c>
+      <c r="AP23">
+        <v>101</v>
+      </c>
+      <c r="AQ23">
+        <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>100</v>
-      </c>
-      <c r="B20">
-        <v>100</v>
-      </c>
-      <c r="C20">
-        <v>100</v>
-      </c>
-      <c r="D20">
-        <v>100</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>20</v>
-      </c>
-      <c r="G20">
-        <v>20</v>
-      </c>
-      <c r="H20">
-        <v>20</v>
-      </c>
-      <c r="I20">
-        <v>10</v>
-      </c>
-      <c r="J20">
-        <v>20</v>
-      </c>
-      <c r="K20">
-        <v>20</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>20</v>
-      </c>
-      <c r="Q20">
-        <v>20</v>
-      </c>
-      <c r="R20">
-        <v>20</v>
-      </c>
-      <c r="S20">
-        <v>20</v>
-      </c>
-      <c r="T20">
-        <v>20</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>20</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>20</v>
-      </c>
-      <c r="AB20">
-        <v>20</v>
-      </c>
-      <c r="AC20">
-        <v>20</v>
-      </c>
-      <c r="AD20">
-        <v>20</v>
-      </c>
-      <c r="AE20">
-        <v>10</v>
-      </c>
-      <c r="AF20">
-        <v>100</v>
-      </c>
-      <c r="AG20">
-        <v>100</v>
-      </c>
-      <c r="AH20">
-        <v>100</v>
-      </c>
-      <c r="AI20">
-        <v>100</v>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>100</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <v>20</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+      <c r="N24">
+        <v>20</v>
+      </c>
+      <c r="O24">
+        <v>20</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>20</v>
+      </c>
+      <c r="U24">
+        <v>20</v>
+      </c>
+      <c r="V24">
+        <v>20</v>
+      </c>
+      <c r="W24">
+        <v>20</v>
+      </c>
+      <c r="X24">
+        <v>20</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>20</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>20</v>
+      </c>
+      <c r="AF24">
+        <v>20</v>
+      </c>
+      <c r="AG24">
+        <v>20</v>
+      </c>
+      <c r="AH24">
+        <v>20</v>
+      </c>
+      <c r="AI24">
+        <v>10</v>
+      </c>
+      <c r="AJ24">
+        <v>101</v>
+      </c>
+      <c r="AK24">
+        <v>101</v>
+      </c>
+      <c r="AL24">
+        <v>101</v>
+      </c>
+      <c r="AM24">
+        <v>101</v>
+      </c>
+      <c r="AN24">
+        <v>101</v>
+      </c>
+      <c r="AO24">
+        <v>101</v>
+      </c>
+      <c r="AP24">
+        <v>101</v>
+      </c>
+      <c r="AQ24">
+        <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A21">
-        <v>100</v>
-      </c>
-      <c r="B21">
-        <v>100</v>
-      </c>
-      <c r="C21">
-        <v>100</v>
-      </c>
-      <c r="D21">
-        <v>100</v>
-      </c>
-      <c r="E21">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>20</v>
-      </c>
-      <c r="G21">
-        <v>10</v>
-      </c>
-      <c r="H21">
-        <v>20</v>
-      </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>10</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>10</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>10</v>
-      </c>
-      <c r="Q21">
-        <v>20</v>
-      </c>
-      <c r="R21">
-        <v>20</v>
-      </c>
-      <c r="S21">
-        <v>20</v>
-      </c>
-      <c r="T21">
-        <v>10</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>10</v>
-      </c>
-      <c r="X21">
-        <v>20</v>
-      </c>
-      <c r="Y21">
-        <v>10</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>10</v>
-      </c>
-      <c r="AB21">
-        <v>20</v>
-      </c>
-      <c r="AC21">
-        <v>10</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>10</v>
-      </c>
-      <c r="AF21">
-        <v>100</v>
-      </c>
-      <c r="AG21">
-        <v>100</v>
-      </c>
-      <c r="AH21">
-        <v>100</v>
-      </c>
-      <c r="AI21">
-        <v>100</v>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>100</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>20</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25">
+        <v>20</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>10</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>10</v>
+      </c>
+      <c r="U25">
+        <v>20</v>
+      </c>
+      <c r="V25">
+        <v>20</v>
+      </c>
+      <c r="W25">
+        <v>20</v>
+      </c>
+      <c r="X25">
+        <v>10</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>10</v>
+      </c>
+      <c r="AB25">
+        <v>20</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>10</v>
+      </c>
+      <c r="AF25">
+        <v>20</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>10</v>
+      </c>
+      <c r="AJ25">
+        <v>101</v>
+      </c>
+      <c r="AK25">
+        <v>101</v>
+      </c>
+      <c r="AL25">
+        <v>101</v>
+      </c>
+      <c r="AM25">
+        <v>101</v>
+      </c>
+      <c r="AN25">
+        <v>101</v>
+      </c>
+      <c r="AO25">
+        <v>101</v>
+      </c>
+      <c r="AP25">
+        <v>101</v>
+      </c>
+      <c r="AQ25">
+        <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A22">
-        <v>100</v>
-      </c>
-      <c r="B22">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>100</v>
-      </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
-      <c r="E22">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>20</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
-      </c>
-      <c r="H22">
-        <v>20</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>20</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>10</v>
-      </c>
-      <c r="AF22">
-        <v>100</v>
-      </c>
-      <c r="AG22">
-        <v>100</v>
-      </c>
-      <c r="AH22">
-        <v>100</v>
-      </c>
-      <c r="AI22">
-        <v>100</v>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>100</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <v>20</v>
+      </c>
+      <c r="L26">
+        <v>20</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>20</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>10</v>
+      </c>
+      <c r="AJ26">
+        <v>101</v>
+      </c>
+      <c r="AK26">
+        <v>101</v>
+      </c>
+      <c r="AL26">
+        <v>101</v>
+      </c>
+      <c r="AM26">
+        <v>101</v>
+      </c>
+      <c r="AN26">
+        <v>101</v>
+      </c>
+      <c r="AO26">
+        <v>101</v>
+      </c>
+      <c r="AP26">
+        <v>101</v>
+      </c>
+      <c r="AQ26">
+        <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A23">
-        <v>100</v>
-      </c>
-      <c r="B23">
-        <v>100</v>
-      </c>
-      <c r="C23">
-        <v>100</v>
-      </c>
-      <c r="D23">
-        <v>100</v>
-      </c>
-      <c r="E23">
-        <v>10</v>
-      </c>
-      <c r="F23">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>10</v>
-      </c>
-      <c r="H23">
-        <v>10</v>
-      </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>10</v>
-      </c>
-      <c r="K23">
-        <v>10</v>
-      </c>
-      <c r="L23">
-        <v>10</v>
-      </c>
-      <c r="M23">
-        <v>10</v>
-      </c>
-      <c r="N23">
-        <v>10</v>
-      </c>
-      <c r="O23">
-        <v>10</v>
-      </c>
-      <c r="P23">
-        <v>10</v>
-      </c>
-      <c r="Q23">
-        <v>20</v>
-      </c>
-      <c r="R23">
-        <v>20</v>
-      </c>
-      <c r="S23">
-        <v>20</v>
-      </c>
-      <c r="T23">
-        <v>10</v>
-      </c>
-      <c r="U23">
-        <v>10</v>
-      </c>
-      <c r="V23">
-        <v>10</v>
-      </c>
-      <c r="W23">
-        <v>10</v>
-      </c>
-      <c r="X23">
-        <v>10</v>
-      </c>
-      <c r="Y23">
-        <v>10</v>
-      </c>
-      <c r="Z23">
-        <v>10</v>
-      </c>
-      <c r="AA23">
-        <v>10</v>
-      </c>
-      <c r="AB23">
-        <v>10</v>
-      </c>
-      <c r="AC23">
-        <v>10</v>
-      </c>
-      <c r="AD23">
-        <v>10</v>
-      </c>
-      <c r="AE23">
-        <v>10</v>
-      </c>
-      <c r="AF23">
-        <v>100</v>
-      </c>
-      <c r="AG23">
-        <v>100</v>
-      </c>
-      <c r="AH23">
-        <v>100</v>
-      </c>
-      <c r="AI23">
-        <v>100</v>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>100</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>100</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>10</v>
+      </c>
+      <c r="N27">
+        <v>10</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
+        <v>10</v>
+      </c>
+      <c r="Q27">
+        <v>10</v>
+      </c>
+      <c r="R27">
+        <v>10</v>
+      </c>
+      <c r="S27">
+        <v>10</v>
+      </c>
+      <c r="T27">
+        <v>10</v>
+      </c>
+      <c r="U27">
+        <v>20</v>
+      </c>
+      <c r="V27">
+        <v>20</v>
+      </c>
+      <c r="W27">
+        <v>20</v>
+      </c>
+      <c r="X27">
+        <v>10</v>
+      </c>
+      <c r="Y27">
+        <v>10</v>
+      </c>
+      <c r="Z27">
+        <v>10</v>
+      </c>
+      <c r="AA27">
+        <v>10</v>
+      </c>
+      <c r="AB27">
+        <v>10</v>
+      </c>
+      <c r="AC27">
+        <v>10</v>
+      </c>
+      <c r="AD27">
+        <v>10</v>
+      </c>
+      <c r="AE27">
+        <v>10</v>
+      </c>
+      <c r="AF27">
+        <v>10</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+      <c r="AH27">
+        <v>10</v>
+      </c>
+      <c r="AI27">
+        <v>10</v>
+      </c>
+      <c r="AJ27">
+        <v>101</v>
+      </c>
+      <c r="AK27">
+        <v>101</v>
+      </c>
+      <c r="AL27">
+        <v>101</v>
+      </c>
+      <c r="AM27">
+        <v>101</v>
+      </c>
+      <c r="AN27">
+        <v>101</v>
+      </c>
+      <c r="AO27">
+        <v>101</v>
+      </c>
+      <c r="AP27">
+        <v>101</v>
+      </c>
+      <c r="AQ27">
+        <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A24">
-        <v>100</v>
-      </c>
-      <c r="B24">
-        <v>100</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-      <c r="D24">
-        <v>100</v>
-      </c>
-      <c r="E24">
-        <v>100</v>
-      </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
-      <c r="G24">
-        <v>100</v>
-      </c>
-      <c r="H24">
-        <v>100</v>
-      </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
-        <v>10</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>10</v>
-      </c>
-      <c r="Q24">
-        <v>20</v>
-      </c>
-      <c r="R24">
-        <v>20</v>
-      </c>
-      <c r="S24">
-        <v>20</v>
-      </c>
-      <c r="T24">
-        <v>10</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>10</v>
-      </c>
-      <c r="X24">
-        <v>100</v>
-      </c>
-      <c r="Y24">
-        <v>100</v>
-      </c>
-      <c r="Z24">
-        <v>100</v>
-      </c>
-      <c r="AA24">
-        <v>100</v>
-      </c>
-      <c r="AB24">
-        <v>100</v>
-      </c>
-      <c r="AC24">
-        <v>100</v>
-      </c>
-      <c r="AD24">
-        <v>100</v>
-      </c>
-      <c r="AE24">
-        <v>100</v>
-      </c>
-      <c r="AF24">
-        <v>100</v>
-      </c>
-      <c r="AG24">
-        <v>100</v>
-      </c>
-      <c r="AH24">
-        <v>100</v>
-      </c>
-      <c r="AI24">
-        <v>100</v>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>100</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
+        <v>100</v>
+      </c>
+      <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>10</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>10</v>
+      </c>
+      <c r="U28">
+        <v>20</v>
+      </c>
+      <c r="V28">
+        <v>20</v>
+      </c>
+      <c r="W28">
+        <v>20</v>
+      </c>
+      <c r="X28">
+        <v>10</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>10</v>
+      </c>
+      <c r="AB28">
+        <v>101</v>
+      </c>
+      <c r="AC28">
+        <v>101</v>
+      </c>
+      <c r="AD28">
+        <v>101</v>
+      </c>
+      <c r="AE28">
+        <v>101</v>
+      </c>
+      <c r="AF28">
+        <v>101</v>
+      </c>
+      <c r="AG28">
+        <v>101</v>
+      </c>
+      <c r="AH28">
+        <v>101</v>
+      </c>
+      <c r="AI28">
+        <v>101</v>
+      </c>
+      <c r="AJ28">
+        <v>101</v>
+      </c>
+      <c r="AK28">
+        <v>101</v>
+      </c>
+      <c r="AL28">
+        <v>101</v>
+      </c>
+      <c r="AM28">
+        <v>101</v>
+      </c>
+      <c r="AN28">
+        <v>101</v>
+      </c>
+      <c r="AO28">
+        <v>101</v>
+      </c>
+      <c r="AP28">
+        <v>101</v>
+      </c>
+      <c r="AQ28">
+        <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A25">
-        <v>100</v>
-      </c>
-      <c r="B25">
-        <v>100</v>
-      </c>
-      <c r="C25">
-        <v>100</v>
-      </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
-      <c r="E25">
-        <v>100</v>
-      </c>
-      <c r="F25">
-        <v>100</v>
-      </c>
-      <c r="G25">
-        <v>100</v>
-      </c>
-      <c r="H25">
-        <v>100</v>
-      </c>
-      <c r="I25">
-        <v>100</v>
-      </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
-        <v>10</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>10</v>
-      </c>
-      <c r="Q25">
-        <v>20</v>
-      </c>
-      <c r="R25">
-        <v>20</v>
-      </c>
-      <c r="S25">
-        <v>20</v>
-      </c>
-      <c r="T25">
-        <v>10</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>10</v>
-      </c>
-      <c r="X25">
-        <v>100</v>
-      </c>
-      <c r="Y25">
-        <v>100</v>
-      </c>
-      <c r="Z25">
-        <v>100</v>
-      </c>
-      <c r="AA25">
-        <v>100</v>
-      </c>
-      <c r="AB25">
-        <v>100</v>
-      </c>
-      <c r="AC25">
-        <v>100</v>
-      </c>
-      <c r="AD25">
-        <v>100</v>
-      </c>
-      <c r="AE25">
-        <v>100</v>
-      </c>
-      <c r="AF25">
-        <v>100</v>
-      </c>
-      <c r="AG25">
-        <v>100</v>
-      </c>
-      <c r="AH25">
-        <v>100</v>
-      </c>
-      <c r="AI25">
-        <v>100</v>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>100</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
+      <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
+        <v>100</v>
+      </c>
+      <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="P29">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>10</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>10</v>
+      </c>
+      <c r="U29">
+        <v>20</v>
+      </c>
+      <c r="V29">
+        <v>20</v>
+      </c>
+      <c r="W29">
+        <v>20</v>
+      </c>
+      <c r="X29">
+        <v>10</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>10</v>
+      </c>
+      <c r="AB29">
+        <v>101</v>
+      </c>
+      <c r="AC29">
+        <v>101</v>
+      </c>
+      <c r="AD29">
+        <v>101</v>
+      </c>
+      <c r="AE29">
+        <v>101</v>
+      </c>
+      <c r="AF29">
+        <v>101</v>
+      </c>
+      <c r="AG29">
+        <v>101</v>
+      </c>
+      <c r="AH29">
+        <v>101</v>
+      </c>
+      <c r="AI29">
+        <v>101</v>
+      </c>
+      <c r="AJ29">
+        <v>101</v>
+      </c>
+      <c r="AK29">
+        <v>101</v>
+      </c>
+      <c r="AL29">
+        <v>101</v>
+      </c>
+      <c r="AM29">
+        <v>101</v>
+      </c>
+      <c r="AN29">
+        <v>101</v>
+      </c>
+      <c r="AO29">
+        <v>101</v>
+      </c>
+      <c r="AP29">
+        <v>101</v>
+      </c>
+      <c r="AQ29">
+        <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A26">
-        <v>100</v>
-      </c>
-      <c r="B26">
-        <v>100</v>
-      </c>
-      <c r="C26">
-        <v>100</v>
-      </c>
-      <c r="D26">
-        <v>100</v>
-      </c>
-      <c r="E26">
-        <v>100</v>
-      </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
-      <c r="H26">
-        <v>100</v>
-      </c>
-      <c r="I26">
-        <v>100</v>
-      </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
-        <v>10</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>10</v>
-      </c>
-      <c r="X26">
-        <v>100</v>
-      </c>
-      <c r="Y26">
-        <v>100</v>
-      </c>
-      <c r="Z26">
-        <v>100</v>
-      </c>
-      <c r="AA26">
-        <v>100</v>
-      </c>
-      <c r="AB26">
-        <v>100</v>
-      </c>
-      <c r="AC26">
-        <v>100</v>
-      </c>
-      <c r="AD26">
-        <v>100</v>
-      </c>
-      <c r="AE26">
-        <v>100</v>
-      </c>
-      <c r="AF26">
-        <v>100</v>
-      </c>
-      <c r="AG26">
-        <v>100</v>
-      </c>
-      <c r="AH26">
-        <v>100</v>
-      </c>
-      <c r="AI26">
-        <v>100</v>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>100</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30">
+        <v>100</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>100</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30">
+        <v>100</v>
+      </c>
+      <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>10</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>10</v>
+      </c>
+      <c r="AB30">
+        <v>101</v>
+      </c>
+      <c r="AC30">
+        <v>101</v>
+      </c>
+      <c r="AD30">
+        <v>101</v>
+      </c>
+      <c r="AE30">
+        <v>101</v>
+      </c>
+      <c r="AF30">
+        <v>101</v>
+      </c>
+      <c r="AG30">
+        <v>101</v>
+      </c>
+      <c r="AH30">
+        <v>101</v>
+      </c>
+      <c r="AI30">
+        <v>101</v>
+      </c>
+      <c r="AJ30">
+        <v>101</v>
+      </c>
+      <c r="AK30">
+        <v>101</v>
+      </c>
+      <c r="AL30">
+        <v>101</v>
+      </c>
+      <c r="AM30">
+        <v>101</v>
+      </c>
+      <c r="AN30">
+        <v>101</v>
+      </c>
+      <c r="AO30">
+        <v>101</v>
+      </c>
+      <c r="AP30">
+        <v>101</v>
+      </c>
+      <c r="AQ30">
+        <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A27">
-        <v>100</v>
-      </c>
-      <c r="B27">
-        <v>100</v>
-      </c>
-      <c r="C27">
-        <v>100</v>
-      </c>
-      <c r="D27">
-        <v>100</v>
-      </c>
-      <c r="E27">
-        <v>100</v>
-      </c>
-      <c r="F27">
-        <v>100</v>
-      </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
-      <c r="H27">
-        <v>100</v>
-      </c>
-      <c r="I27">
-        <v>100</v>
-      </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
-      <c r="M27">
-        <v>10</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>100</v>
+      </c>
+      <c r="B31">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>10</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
         <v>72</v>
       </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>10</v>
-      </c>
-      <c r="X27">
-        <v>100</v>
-      </c>
-      <c r="Y27">
-        <v>100</v>
-      </c>
-      <c r="Z27">
-        <v>100</v>
-      </c>
-      <c r="AA27">
-        <v>100</v>
-      </c>
-      <c r="AB27">
-        <v>100</v>
-      </c>
-      <c r="AC27">
-        <v>100</v>
-      </c>
-      <c r="AD27">
-        <v>100</v>
-      </c>
-      <c r="AE27">
-        <v>100</v>
-      </c>
-      <c r="AF27">
-        <v>100</v>
-      </c>
-      <c r="AG27">
-        <v>100</v>
-      </c>
-      <c r="AH27">
-        <v>100</v>
-      </c>
-      <c r="AI27">
-        <v>100</v>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>10</v>
+      </c>
+      <c r="AB31">
+        <v>101</v>
+      </c>
+      <c r="AC31">
+        <v>101</v>
+      </c>
+      <c r="AD31">
+        <v>101</v>
+      </c>
+      <c r="AE31">
+        <v>101</v>
+      </c>
+      <c r="AF31">
+        <v>101</v>
+      </c>
+      <c r="AG31">
+        <v>101</v>
+      </c>
+      <c r="AH31">
+        <v>101</v>
+      </c>
+      <c r="AI31">
+        <v>101</v>
+      </c>
+      <c r="AJ31">
+        <v>101</v>
+      </c>
+      <c r="AK31">
+        <v>101</v>
+      </c>
+      <c r="AL31">
+        <v>101</v>
+      </c>
+      <c r="AM31">
+        <v>101</v>
+      </c>
+      <c r="AN31">
+        <v>101</v>
+      </c>
+      <c r="AO31">
+        <v>101</v>
+      </c>
+      <c r="AP31">
+        <v>101</v>
+      </c>
+      <c r="AQ31">
+        <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>100</v>
-      </c>
-      <c r="B28">
-        <v>100</v>
-      </c>
-      <c r="C28">
-        <v>100</v>
-      </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
-      <c r="E28">
-        <v>100</v>
-      </c>
-      <c r="F28">
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <v>100</v>
-      </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
-      <c r="I28">
-        <v>100</v>
-      </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>10</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>10</v>
-      </c>
-      <c r="X28">
-        <v>100</v>
-      </c>
-      <c r="Y28">
-        <v>100</v>
-      </c>
-      <c r="Z28">
-        <v>100</v>
-      </c>
-      <c r="AA28">
-        <v>100</v>
-      </c>
-      <c r="AB28">
-        <v>100</v>
-      </c>
-      <c r="AC28">
-        <v>100</v>
-      </c>
-      <c r="AD28">
-        <v>100</v>
-      </c>
-      <c r="AE28">
-        <v>100</v>
-      </c>
-      <c r="AF28">
-        <v>100</v>
-      </c>
-      <c r="AG28">
-        <v>100</v>
-      </c>
-      <c r="AH28">
-        <v>100</v>
-      </c>
-      <c r="AI28">
-        <v>100</v>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>100</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
+        <v>100</v>
+      </c>
+      <c r="P32">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>10</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>10</v>
+      </c>
+      <c r="AB32">
+        <v>101</v>
+      </c>
+      <c r="AC32">
+        <v>101</v>
+      </c>
+      <c r="AD32">
+        <v>101</v>
+      </c>
+      <c r="AE32">
+        <v>101</v>
+      </c>
+      <c r="AF32">
+        <v>101</v>
+      </c>
+      <c r="AG32">
+        <v>101</v>
+      </c>
+      <c r="AH32">
+        <v>101</v>
+      </c>
+      <c r="AI32">
+        <v>101</v>
+      </c>
+      <c r="AJ32">
+        <v>101</v>
+      </c>
+      <c r="AK32">
+        <v>101</v>
+      </c>
+      <c r="AL32">
+        <v>101</v>
+      </c>
+      <c r="AM32">
+        <v>101</v>
+      </c>
+      <c r="AN32">
+        <v>101</v>
+      </c>
+      <c r="AO32">
+        <v>101</v>
+      </c>
+      <c r="AP32">
+        <v>101</v>
+      </c>
+      <c r="AQ32">
+        <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>100</v>
-      </c>
-      <c r="B29">
-        <v>100</v>
-      </c>
-      <c r="C29">
-        <v>100</v>
-      </c>
-      <c r="D29">
-        <v>100</v>
-      </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
-      </c>
-      <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29">
-        <v>100</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
-      <c r="M29">
-        <v>10</v>
-      </c>
-      <c r="N29">
-        <v>10</v>
-      </c>
-      <c r="O29">
-        <v>10</v>
-      </c>
-      <c r="P29">
-        <v>10</v>
-      </c>
-      <c r="Q29">
-        <v>10</v>
-      </c>
-      <c r="R29">
-        <v>10</v>
-      </c>
-      <c r="S29">
-        <v>10</v>
-      </c>
-      <c r="T29">
-        <v>10</v>
-      </c>
-      <c r="U29">
-        <v>10</v>
-      </c>
-      <c r="V29">
-        <v>10</v>
-      </c>
-      <c r="W29">
-        <v>10</v>
-      </c>
-      <c r="X29">
-        <v>100</v>
-      </c>
-      <c r="Y29">
-        <v>100</v>
-      </c>
-      <c r="Z29">
-        <v>100</v>
-      </c>
-      <c r="AA29">
-        <v>100</v>
-      </c>
-      <c r="AB29">
-        <v>100</v>
-      </c>
-      <c r="AC29">
-        <v>100</v>
-      </c>
-      <c r="AD29">
-        <v>100</v>
-      </c>
-      <c r="AE29">
-        <v>100</v>
-      </c>
-      <c r="AF29">
-        <v>100</v>
-      </c>
-      <c r="AG29">
-        <v>100</v>
-      </c>
-      <c r="AH29">
-        <v>100</v>
-      </c>
-      <c r="AI29">
-        <v>100</v>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>100</v>
+      </c>
+      <c r="B33">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
+        <v>100</v>
+      </c>
+      <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>10</v>
+      </c>
+      <c r="R33">
+        <v>10</v>
+      </c>
+      <c r="S33">
+        <v>10</v>
+      </c>
+      <c r="T33">
+        <v>10</v>
+      </c>
+      <c r="U33">
+        <v>10</v>
+      </c>
+      <c r="V33">
+        <v>10</v>
+      </c>
+      <c r="W33">
+        <v>10</v>
+      </c>
+      <c r="X33">
+        <v>10</v>
+      </c>
+      <c r="Y33">
+        <v>10</v>
+      </c>
+      <c r="Z33">
+        <v>10</v>
+      </c>
+      <c r="AA33">
+        <v>10</v>
+      </c>
+      <c r="AB33">
+        <v>101</v>
+      </c>
+      <c r="AC33">
+        <v>101</v>
+      </c>
+      <c r="AD33">
+        <v>101</v>
+      </c>
+      <c r="AE33">
+        <v>101</v>
+      </c>
+      <c r="AF33">
+        <v>101</v>
+      </c>
+      <c r="AG33">
+        <v>101</v>
+      </c>
+      <c r="AH33">
+        <v>101</v>
+      </c>
+      <c r="AI33">
+        <v>101</v>
+      </c>
+      <c r="AJ33">
+        <v>101</v>
+      </c>
+      <c r="AK33">
+        <v>101</v>
+      </c>
+      <c r="AL33">
+        <v>101</v>
+      </c>
+      <c r="AM33">
+        <v>101</v>
+      </c>
+      <c r="AN33">
+        <v>101</v>
+      </c>
+      <c r="AO33">
+        <v>101</v>
+      </c>
+      <c r="AP33">
+        <v>101</v>
+      </c>
+      <c r="AQ33">
+        <v>101</v>
       </c>
     </row>
-    <row r="39" spans="21:21" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>100</v>
+      </c>
+      <c r="B34">
+        <v>100</v>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>100</v>
+      </c>
+      <c r="E34">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34">
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>100</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>100</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="P34">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
+        <v>102</v>
+      </c>
+      <c r="V34">
+        <v>102</v>
+      </c>
+      <c r="W34">
+        <v>102</v>
+      </c>
+      <c r="X34">
+        <v>101</v>
+      </c>
+      <c r="Y34">
+        <v>101</v>
+      </c>
+      <c r="Z34">
+        <v>101</v>
+      </c>
+      <c r="AA34">
+        <v>101</v>
+      </c>
+      <c r="AB34">
+        <v>101</v>
+      </c>
+      <c r="AC34">
+        <v>101</v>
+      </c>
+      <c r="AD34">
+        <v>101</v>
+      </c>
+      <c r="AE34">
+        <v>101</v>
+      </c>
+      <c r="AF34">
+        <v>101</v>
+      </c>
+      <c r="AG34">
+        <v>101</v>
+      </c>
+      <c r="AH34">
+        <v>101</v>
+      </c>
+      <c r="AI34">
+        <v>101</v>
+      </c>
+      <c r="AJ34">
+        <v>101</v>
+      </c>
+      <c r="AK34">
+        <v>101</v>
+      </c>
+      <c r="AL34">
+        <v>101</v>
+      </c>
+      <c r="AM34">
+        <v>101</v>
+      </c>
+      <c r="AN34">
+        <v>101</v>
+      </c>
+      <c r="AO34">
+        <v>101</v>
+      </c>
+      <c r="AP34">
+        <v>101</v>
+      </c>
+      <c r="AQ34">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35">
+        <v>100</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>100</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>100</v>
+      </c>
+      <c r="M35">
+        <v>100</v>
+      </c>
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
+        <v>100</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
+        <v>100</v>
+      </c>
+      <c r="U35">
+        <v>102</v>
+      </c>
+      <c r="V35">
+        <v>102</v>
+      </c>
+      <c r="W35">
+        <v>102</v>
+      </c>
+      <c r="X35">
+        <v>101</v>
+      </c>
+      <c r="Y35">
+        <v>101</v>
+      </c>
+      <c r="Z35">
+        <v>101</v>
+      </c>
+      <c r="AA35">
+        <v>101</v>
+      </c>
+      <c r="AB35">
+        <v>101</v>
+      </c>
+      <c r="AC35">
+        <v>101</v>
+      </c>
+      <c r="AD35">
+        <v>101</v>
+      </c>
+      <c r="AE35">
+        <v>101</v>
+      </c>
+      <c r="AF35">
+        <v>101</v>
+      </c>
+      <c r="AG35">
+        <v>101</v>
+      </c>
+      <c r="AH35">
+        <v>101</v>
+      </c>
+      <c r="AI35">
+        <v>101</v>
+      </c>
+      <c r="AJ35">
+        <v>101</v>
+      </c>
+      <c r="AK35">
+        <v>101</v>
+      </c>
+      <c r="AL35">
+        <v>101</v>
+      </c>
+      <c r="AM35">
+        <v>101</v>
+      </c>
+      <c r="AN35">
+        <v>101</v>
+      </c>
+      <c r="AO35">
+        <v>101</v>
+      </c>
+      <c r="AP35">
+        <v>101</v>
+      </c>
+      <c r="AQ35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>100</v>
+      </c>
+      <c r="B36">
+        <v>100</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36">
+        <v>100</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
+        <v>100</v>
+      </c>
+      <c r="N36">
+        <v>100</v>
+      </c>
+      <c r="O36">
+        <v>100</v>
+      </c>
+      <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
+        <v>100</v>
+      </c>
+      <c r="U36">
+        <v>102</v>
+      </c>
+      <c r="V36">
+        <v>102</v>
+      </c>
+      <c r="W36">
+        <v>102</v>
+      </c>
+      <c r="X36">
+        <v>101</v>
+      </c>
+      <c r="Y36">
+        <v>101</v>
+      </c>
+      <c r="Z36">
+        <v>101</v>
+      </c>
+      <c r="AA36">
+        <v>101</v>
+      </c>
+      <c r="AB36">
+        <v>101</v>
+      </c>
+      <c r="AC36">
+        <v>101</v>
+      </c>
+      <c r="AD36">
+        <v>101</v>
+      </c>
+      <c r="AE36">
+        <v>101</v>
+      </c>
+      <c r="AF36">
+        <v>101</v>
+      </c>
+      <c r="AG36">
+        <v>101</v>
+      </c>
+      <c r="AH36">
+        <v>101</v>
+      </c>
+      <c r="AI36">
+        <v>101</v>
+      </c>
+      <c r="AJ36">
+        <v>101</v>
+      </c>
+      <c r="AK36">
+        <v>101</v>
+      </c>
+      <c r="AL36">
+        <v>101</v>
+      </c>
+      <c r="AM36">
+        <v>101</v>
+      </c>
+      <c r="AN36">
+        <v>101</v>
+      </c>
+      <c r="AO36">
+        <v>101</v>
+      </c>
+      <c r="AP36">
+        <v>101</v>
+      </c>
+      <c r="AQ36">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>100</v>
+      </c>
+      <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>100</v>
+      </c>
+      <c r="D37">
+        <v>100</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>100</v>
+      </c>
+      <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+      <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>100</v>
+      </c>
+      <c r="M37">
+        <v>100</v>
+      </c>
+      <c r="N37">
+        <v>100</v>
+      </c>
+      <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>102</v>
+      </c>
+      <c r="V37">
+        <v>102</v>
+      </c>
+      <c r="W37">
+        <v>102</v>
+      </c>
+      <c r="X37">
+        <v>101</v>
+      </c>
+      <c r="Y37">
+        <v>101</v>
+      </c>
+      <c r="Z37">
+        <v>101</v>
+      </c>
+      <c r="AA37">
+        <v>101</v>
+      </c>
+      <c r="AB37">
+        <v>101</v>
+      </c>
+      <c r="AC37">
+        <v>101</v>
+      </c>
+      <c r="AD37">
+        <v>101</v>
+      </c>
+      <c r="AE37">
+        <v>101</v>
+      </c>
+      <c r="AF37">
+        <v>101</v>
+      </c>
+      <c r="AG37">
+        <v>101</v>
+      </c>
+      <c r="AH37">
+        <v>101</v>
+      </c>
+      <c r="AI37">
+        <v>101</v>
+      </c>
+      <c r="AJ37">
+        <v>101</v>
+      </c>
+      <c r="AK37">
+        <v>101</v>
+      </c>
+      <c r="AL37">
+        <v>101</v>
+      </c>
+      <c r="AM37">
+        <v>101</v>
+      </c>
+      <c r="AN37">
+        <v>101</v>
+      </c>
+      <c r="AO37">
+        <v>101</v>
+      </c>
+      <c r="AP37">
+        <v>101</v>
+      </c>
+      <c r="AQ37">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:43" x14ac:dyDescent="0.45">
       <c r="U39" t="s">
         <v>1</v>
       </c>
@@ -16357,34 +18119,42 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
+      <formula>A1=102</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>A1=101</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1:T4 E1:P5 AP1:XFD49 Q5:U5 O6:AA10 AC6:AM10 E6:N20 AG6:AM27 G9:O9 G10:P10 J11:AH11 O11:AM12 K12:AH12 AA12:AH15 O13:AI19 J13:J23 E16:E21 P16:AB25 N18:O20 AD18:AD20 F18:I21 O20:T20 U20:AI27 E21:T27 N26:AE26 I27:AH27 Q27:AA32 P28:T34 R28:AA35 AC33:AM37 P34:AA35 Q34:T37 O35:AA37 K38:AE45 AF38:AO49 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576 A38:J49 E28:P37 A1:D37 AN1:AQ37">
+    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
+      <formula>A1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="10" stopIfTrue="1">
+      <formula>A1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="11" stopIfTrue="1">
+      <formula>A1=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1:T4 X1:AA4 E1:P5 AB1:AM10 Q5:AA5 E6:AA10 E11:AM37 A38:XFD1048576 A1:D37 AN1:XFD37">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>A1=100</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AP1:XFD49 AF9:AO49 K16:P16 Q16:AE34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576 Y1:AO8 A12:A17 E23:AD23 B14:E17 A17:P23 F7:AD7 O2:V6 K1:Q8 R2:X8 L31:W35 N24:W35 M23:W28 L24:P34 A24:K35 C5:K5 C6:L6 J22:AA22 L12:X21 W8:AD11 K9:AE15 AC2:AI29 A1:J16 F9:F19 G8:AD8 Z14:Z16 J14:K16">
-    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
-      <formula>A1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
-      <formula>A1=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
-      <formula>A1=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9" stopIfTrue="1">
-      <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hotat\OneDrive\デスクトップ\GCP\DecoBom\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFC911-854C-499D-8482-EB835791895F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7B0D32-C4E0-437F-84F7-026C9EC9F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
@@ -100,7 +100,63 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="145">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -167,6 +223,650 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
@@ -175,6 +875,69 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3885,27 +4648,27 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:G8 O1:U8 V1:XFD49 H2:N8 A9:U49 A50:XFD1048576">
-    <cfRule type="expression" dxfId="35" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="4" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="143" priority="5" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="6" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="141" priority="7" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="31" priority="1">
+    <cfRule type="expression" dxfId="140" priority="1">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="139" priority="2" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="138" priority="3" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10051,33 +10814,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="137" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="136" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="3">
+    <cfRule type="expression" dxfId="135" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="134" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO16 K16:P16 Q16:AE34 A17:P23 AE17:AO33 A24:K26 L24:P34 K27:K34 A27:J49 AF34:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="23" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="132" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="131" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="130" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="129" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13216,33 +13979,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="128" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="127" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="126" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="125" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="124" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO49 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="14" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="123" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="122" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="121" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="120" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13252,7 +14015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9A64FA3-C0B1-40B6-B9C2-665C3D824C39}">
-  <dimension ref="A1:AQ39"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="4" width="4.8984375" bestFit="1" customWidth="1"/>
@@ -13261,51 +14024,51 @@
     <col min="25" max="39" width="5.8984375" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="4.8984375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="5.8984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="42" max="51" width="4.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O1">
         <v>100</v>
@@ -13314,16 +14077,16 @@
         <v>100</v>
       </c>
       <c r="Q1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U1">
         <v>102</v>
@@ -13335,16 +14098,16 @@
         <v>102</v>
       </c>
       <c r="X1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB1">
         <v>101</v>
@@ -13371,10 +14134,10 @@
         <v>101</v>
       </c>
       <c r="AJ1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL1">
         <v>101</v>
@@ -13394,49 +14157,73 @@
       <c r="AQ1">
         <v>101</v>
       </c>
+      <c r="AR1">
+        <v>101</v>
+      </c>
+      <c r="AS1">
+        <v>101</v>
+      </c>
+      <c r="AT1">
+        <v>101</v>
+      </c>
+      <c r="AU1">
+        <v>101</v>
+      </c>
+      <c r="AV1">
+        <v>101</v>
+      </c>
+      <c r="AW1">
+        <v>101</v>
+      </c>
+      <c r="AX1">
+        <v>101</v>
+      </c>
+      <c r="AY1">
+        <v>101</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O2">
         <v>100</v>
@@ -13445,16 +14232,16 @@
         <v>100</v>
       </c>
       <c r="Q2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U2">
         <v>102</v>
@@ -13466,16 +14253,16 @@
         <v>102</v>
       </c>
       <c r="X2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>101</v>
@@ -13502,10 +14289,10 @@
         <v>101</v>
       </c>
       <c r="AJ2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL2">
         <v>101</v>
@@ -13525,49 +14312,73 @@
       <c r="AQ2">
         <v>101</v>
       </c>
+      <c r="AR2">
+        <v>101</v>
+      </c>
+      <c r="AS2">
+        <v>101</v>
+      </c>
+      <c r="AT2">
+        <v>101</v>
+      </c>
+      <c r="AU2">
+        <v>101</v>
+      </c>
+      <c r="AV2">
+        <v>101</v>
+      </c>
+      <c r="AW2">
+        <v>101</v>
+      </c>
+      <c r="AX2">
+        <v>101</v>
+      </c>
+      <c r="AY2">
+        <v>101</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O3">
         <v>100</v>
@@ -13576,16 +14387,16 @@
         <v>100</v>
       </c>
       <c r="Q3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U3">
         <v>102</v>
@@ -13597,16 +14408,16 @@
         <v>102</v>
       </c>
       <c r="X3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB3">
         <v>101</v>
@@ -13633,10 +14444,10 @@
         <v>101</v>
       </c>
       <c r="AJ3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL3">
         <v>101</v>
@@ -13656,49 +14467,73 @@
       <c r="AQ3">
         <v>101</v>
       </c>
+      <c r="AR3">
+        <v>101</v>
+      </c>
+      <c r="AS3">
+        <v>101</v>
+      </c>
+      <c r="AT3">
+        <v>101</v>
+      </c>
+      <c r="AU3">
+        <v>101</v>
+      </c>
+      <c r="AV3">
+        <v>101</v>
+      </c>
+      <c r="AW3">
+        <v>101</v>
+      </c>
+      <c r="AX3">
+        <v>101</v>
+      </c>
+      <c r="AY3">
+        <v>101</v>
+      </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -13707,16 +14542,16 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U4">
         <v>102</v>
@@ -13728,16 +14563,16 @@
         <v>102</v>
       </c>
       <c r="X4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB4">
         <v>101</v>
@@ -13764,10 +14599,10 @@
         <v>101</v>
       </c>
       <c r="AJ4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL4">
         <v>101</v>
@@ -13787,8 +14622,32 @@
       <c r="AQ4">
         <v>101</v>
       </c>
+      <c r="AR4">
+        <v>101</v>
+      </c>
+      <c r="AS4">
+        <v>101</v>
+      </c>
+      <c r="AT4">
+        <v>101</v>
+      </c>
+      <c r="AU4">
+        <v>101</v>
+      </c>
+      <c r="AV4">
+        <v>101</v>
+      </c>
+      <c r="AW4">
+        <v>101</v>
+      </c>
+      <c r="AX4">
+        <v>101</v>
+      </c>
+      <c r="AY4">
+        <v>101</v>
+      </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>100</v>
       </c>
@@ -13838,16 +14697,16 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -13871,16 +14730,16 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF5">
         <v>101</v>
@@ -13895,31 +14754,55 @@
         <v>101</v>
       </c>
       <c r="AJ5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AM5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP5">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AQ5">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="AR5">
+        <v>100</v>
+      </c>
+      <c r="AS5">
+        <v>100</v>
+      </c>
+      <c r="AT5">
+        <v>100</v>
+      </c>
+      <c r="AU5">
+        <v>100</v>
+      </c>
+      <c r="AV5">
+        <v>100</v>
+      </c>
+      <c r="AW5">
+        <v>100</v>
+      </c>
+      <c r="AX5">
+        <v>100</v>
+      </c>
+      <c r="AY5">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>100</v>
       </c>
@@ -13969,19 +14852,19 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -13999,19 +14882,19 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>101</v>
@@ -14026,72 +14909,96 @@
         <v>101</v>
       </c>
       <c r="AJ6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AM6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP6">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AQ6">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="AR6">
+        <v>100</v>
+      </c>
+      <c r="AS6">
+        <v>100</v>
+      </c>
+      <c r="AT6">
+        <v>100</v>
+      </c>
+      <c r="AU6">
+        <v>100</v>
+      </c>
+      <c r="AV6">
+        <v>100</v>
+      </c>
+      <c r="AW6">
+        <v>100</v>
+      </c>
+      <c r="AX6">
+        <v>100</v>
+      </c>
+      <c r="AY6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -14100,49 +15007,49 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
         <v>71</v>
       </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
       <c r="AA7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>101</v>
@@ -14157,10 +15064,10 @@
         <v>101</v>
       </c>
       <c r="AJ7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL7">
         <v>101</v>
@@ -14180,49 +15087,73 @@
       <c r="AQ7">
         <v>101</v>
       </c>
+      <c r="AR7">
+        <v>101</v>
+      </c>
+      <c r="AS7">
+        <v>101</v>
+      </c>
+      <c r="AT7">
+        <v>101</v>
+      </c>
+      <c r="AU7">
+        <v>101</v>
+      </c>
+      <c r="AV7">
+        <v>101</v>
+      </c>
+      <c r="AW7">
+        <v>101</v>
+      </c>
+      <c r="AX7">
+        <v>101</v>
+      </c>
+      <c r="AY7">
+        <v>101</v>
+      </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -14231,19 +15162,19 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -14261,19 +15192,19 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>101</v>
@@ -14288,10 +15219,10 @@
         <v>101</v>
       </c>
       <c r="AJ8">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK8">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL8">
         <v>101</v>
@@ -14311,49 +15242,73 @@
       <c r="AQ8">
         <v>101</v>
       </c>
+      <c r="AR8">
+        <v>101</v>
+      </c>
+      <c r="AS8">
+        <v>101</v>
+      </c>
+      <c r="AT8">
+        <v>101</v>
+      </c>
+      <c r="AU8">
+        <v>101</v>
+      </c>
+      <c r="AV8">
+        <v>101</v>
+      </c>
+      <c r="AW8">
+        <v>101</v>
+      </c>
+      <c r="AX8">
+        <v>101</v>
+      </c>
+      <c r="AY8">
+        <v>101</v>
+      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -14362,49 +15317,49 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB9">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF9">
         <v>101</v>
@@ -14419,10 +15374,10 @@
         <v>101</v>
       </c>
       <c r="AJ9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL9">
         <v>101</v>
@@ -14442,49 +15397,73 @@
       <c r="AQ9">
         <v>101</v>
       </c>
+      <c r="AR9">
+        <v>101</v>
+      </c>
+      <c r="AS9">
+        <v>101</v>
+      </c>
+      <c r="AT9">
+        <v>101</v>
+      </c>
+      <c r="AU9">
+        <v>101</v>
+      </c>
+      <c r="AV9">
+        <v>101</v>
+      </c>
+      <c r="AW9">
+        <v>101</v>
+      </c>
+      <c r="AX9">
+        <v>101</v>
+      </c>
+      <c r="AY9">
+        <v>101</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -14493,49 +15472,49 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB10">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF10">
         <v>101</v>
@@ -14550,10 +15529,10 @@
         <v>101</v>
       </c>
       <c r="AJ10">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK10">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL10">
         <v>101</v>
@@ -14573,43 +15552,67 @@
       <c r="AQ10">
         <v>101</v>
       </c>
+      <c r="AR10">
+        <v>101</v>
+      </c>
+      <c r="AS10">
+        <v>101</v>
+      </c>
+      <c r="AT10">
+        <v>101</v>
+      </c>
+      <c r="AU10">
+        <v>101</v>
+      </c>
+      <c r="AV10">
+        <v>101</v>
+      </c>
+      <c r="AW10">
+        <v>101</v>
+      </c>
+      <c r="AX10">
+        <v>101</v>
+      </c>
+      <c r="AY10">
+        <v>101</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L11">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -14636,25 +15639,25 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB11">
         <v>10</v>
@@ -14681,16 +15684,16 @@
         <v>10</v>
       </c>
       <c r="AJ11">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AK11">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL11">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AM11">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN11">
         <v>101</v>
@@ -14704,46 +15707,70 @@
       <c r="AQ11">
         <v>101</v>
       </c>
+      <c r="AR11">
+        <v>101</v>
+      </c>
+      <c r="AS11">
+        <v>101</v>
+      </c>
+      <c r="AT11">
+        <v>101</v>
+      </c>
+      <c r="AU11">
+        <v>101</v>
+      </c>
+      <c r="AV11">
+        <v>101</v>
+      </c>
+      <c r="AW11">
+        <v>101</v>
+      </c>
+      <c r="AX11">
+        <v>101</v>
+      </c>
+      <c r="AY11">
+        <v>101</v>
+      </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -14752,7 +15779,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -14764,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U12">
         <v>0</v>
@@ -14800,28 +15827,28 @@
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK12">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AL12">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AM12">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN12">
         <v>101</v>
@@ -14835,43 +15862,67 @@
       <c r="AQ12">
         <v>101</v>
       </c>
+      <c r="AR12">
+        <v>101</v>
+      </c>
+      <c r="AS12">
+        <v>101</v>
+      </c>
+      <c r="AT12">
+        <v>101</v>
+      </c>
+      <c r="AU12">
+        <v>101</v>
+      </c>
+      <c r="AV12">
+        <v>101</v>
+      </c>
+      <c r="AW12">
+        <v>101</v>
+      </c>
+      <c r="AX12">
+        <v>101</v>
+      </c>
+      <c r="AY12">
+        <v>101</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L13">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -14895,31 +15946,31 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>10</v>
@@ -14931,28 +15982,28 @@
         <v>10</v>
       </c>
       <c r="AF13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG13">
         <v>10</v>
       </c>
       <c r="AH13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI13">
         <v>10</v>
       </c>
       <c r="AJ13">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK13">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL13">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AM13">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN13">
         <v>101</v>
@@ -14966,58 +16017,82 @@
       <c r="AQ13">
         <v>101</v>
       </c>
+      <c r="AR13">
+        <v>101</v>
+      </c>
+      <c r="AS13">
+        <v>101</v>
+      </c>
+      <c r="AT13">
+        <v>101</v>
+      </c>
+      <c r="AU13">
+        <v>101</v>
+      </c>
+      <c r="AV13">
+        <v>101</v>
+      </c>
+      <c r="AW13">
+        <v>101</v>
+      </c>
+      <c r="AX13">
+        <v>101</v>
+      </c>
+      <c r="AY13">
+        <v>101</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J14">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K14">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="L14">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P14">
         <v>20</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -15029,40 +16104,40 @@
         <v>20</v>
       </c>
       <c r="U14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X14">
         <v>20</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG14">
         <v>20</v>
@@ -15071,19 +16146,19 @@
         <v>20</v>
       </c>
       <c r="AI14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK14">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AL14">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AM14">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN14">
         <v>101</v>
@@ -15097,61 +16172,85 @@
       <c r="AQ14">
         <v>101</v>
       </c>
+      <c r="AR14">
+        <v>101</v>
+      </c>
+      <c r="AS14">
+        <v>101</v>
+      </c>
+      <c r="AT14">
+        <v>101</v>
+      </c>
+      <c r="AU14">
+        <v>101</v>
+      </c>
+      <c r="AV14">
+        <v>101</v>
+      </c>
+      <c r="AW14">
+        <v>101</v>
+      </c>
+      <c r="AX14">
+        <v>101</v>
+      </c>
+      <c r="AY14">
+        <v>101</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J15">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M15">
         <v>10</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O15">
         <v>10</v>
       </c>
       <c r="P15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q15">
         <v>10</v>
       </c>
       <c r="R15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -15160,25 +16259,25 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -15187,34 +16286,34 @@
         <v>10</v>
       </c>
       <c r="AD15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AE15">
         <v>10</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI15">
         <v>10</v>
       </c>
       <c r="AJ15">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL15">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN15">
         <v>101</v>
@@ -15228,64 +16327,88 @@
       <c r="AQ15">
         <v>101</v>
       </c>
+      <c r="AR15">
+        <v>101</v>
+      </c>
+      <c r="AS15">
+        <v>101</v>
+      </c>
+      <c r="AT15">
+        <v>101</v>
+      </c>
+      <c r="AU15">
+        <v>101</v>
+      </c>
+      <c r="AV15">
+        <v>101</v>
+      </c>
+      <c r="AW15">
+        <v>101</v>
+      </c>
+      <c r="AX15">
+        <v>101</v>
+      </c>
+      <c r="AY15">
+        <v>101</v>
+      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="H16">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>80</v>
@@ -15315,91 +16438,115 @@
         <v>80</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AI16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM16">
         <v>10</v>
       </c>
       <c r="AN16">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AO16">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AP16">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
+        <v>10</v>
+      </c>
+      <c r="AR16">
+        <v>101</v>
+      </c>
+      <c r="AS16">
+        <v>101</v>
+      </c>
+      <c r="AT16">
+        <v>101</v>
+      </c>
+      <c r="AU16">
+        <v>101</v>
+      </c>
+      <c r="AV16">
+        <v>101</v>
+      </c>
+      <c r="AW16">
+        <v>101</v>
+      </c>
+      <c r="AX16">
+        <v>101</v>
+      </c>
+      <c r="AY16">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F17">
+        <v>102</v>
+      </c>
+      <c r="G17">
+        <v>102</v>
+      </c>
+      <c r="H17">
+        <v>102</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
         <v>99</v>
       </c>
-      <c r="G17">
+      <c r="K17">
         <v>99</v>
       </c>
-      <c r="H17">
+      <c r="L17">
         <v>99</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>95</v>
       </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>10</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>10</v>
-      </c>
       <c r="N17">
         <v>0</v>
       </c>
@@ -15407,16 +16554,16 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>80</v>
@@ -15446,108 +16593,132 @@
         <v>80</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AF17">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AG17">
         <v>10</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI17">
+        <v>10</v>
+      </c>
+      <c r="AJ17">
+        <v>20</v>
+      </c>
+      <c r="AK17">
+        <v>10</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
         <v>95</v>
       </c>
-      <c r="AJ17">
+      <c r="AN17">
         <v>99</v>
       </c>
-      <c r="AK17">
+      <c r="AO17">
         <v>99</v>
       </c>
-      <c r="AL17">
+      <c r="AP17">
         <v>99</v>
       </c>
-      <c r="AM17">
-        <v>10</v>
-      </c>
-      <c r="AN17">
-        <v>101</v>
-      </c>
-      <c r="AO17">
-        <v>101</v>
-      </c>
-      <c r="AP17">
-        <v>101</v>
-      </c>
       <c r="AQ17">
+        <v>10</v>
+      </c>
+      <c r="AR17">
+        <v>101</v>
+      </c>
+      <c r="AS17">
+        <v>101</v>
+      </c>
+      <c r="AT17">
+        <v>101</v>
+      </c>
+      <c r="AU17">
+        <v>101</v>
+      </c>
+      <c r="AV17">
+        <v>101</v>
+      </c>
+      <c r="AW17">
+        <v>101</v>
+      </c>
+      <c r="AX17">
+        <v>101</v>
+      </c>
+      <c r="AY17">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F18">
+        <v>102</v>
+      </c>
+      <c r="G18">
+        <v>102</v>
+      </c>
+      <c r="H18">
+        <v>102</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
         <v>99</v>
       </c>
-      <c r="G18">
+      <c r="K18">
         <v>93</v>
       </c>
-      <c r="H18">
+      <c r="L18">
         <v>99</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>95</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
       <c r="N18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S18">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="T18">
         <v>80</v>
@@ -15577,108 +16748,132 @@
         <v>80</v>
       </c>
       <c r="AC18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AD18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF18">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AG18">
         <v>20</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>20</v>
+      </c>
+      <c r="AK18">
+        <v>20</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
         <v>95</v>
       </c>
-      <c r="AJ18">
+      <c r="AN18">
         <v>99</v>
       </c>
-      <c r="AK18">
+      <c r="AO18">
         <v>91</v>
       </c>
-      <c r="AL18">
+      <c r="AP18">
         <v>99</v>
       </c>
-      <c r="AM18">
-        <v>10</v>
-      </c>
-      <c r="AN18">
-        <v>101</v>
-      </c>
-      <c r="AO18">
-        <v>101</v>
-      </c>
-      <c r="AP18">
-        <v>101</v>
-      </c>
       <c r="AQ18">
+        <v>10</v>
+      </c>
+      <c r="AR18">
+        <v>101</v>
+      </c>
+      <c r="AS18">
+        <v>101</v>
+      </c>
+      <c r="AT18">
+        <v>101</v>
+      </c>
+      <c r="AU18">
+        <v>101</v>
+      </c>
+      <c r="AV18">
+        <v>101</v>
+      </c>
+      <c r="AW18">
+        <v>101</v>
+      </c>
+      <c r="AX18">
+        <v>101</v>
+      </c>
+      <c r="AY18">
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F19">
+        <v>102</v>
+      </c>
+      <c r="G19">
+        <v>102</v>
+      </c>
+      <c r="H19">
+        <v>102</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
         <v>99</v>
       </c>
-      <c r="G19">
+      <c r="K19">
         <v>99</v>
       </c>
-      <c r="H19">
+      <c r="L19">
         <v>99</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>95</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>10</v>
-      </c>
-      <c r="L19">
-        <v>20</v>
-      </c>
-      <c r="M19">
-        <v>10</v>
-      </c>
       <c r="N19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="Q19">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S19">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="T19">
         <v>80</v>
@@ -15708,108 +16903,132 @@
         <v>80</v>
       </c>
       <c r="AC19">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AD19">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AF19">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AG19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI19">
+        <v>10</v>
+      </c>
+      <c r="AJ19">
+        <v>20</v>
+      </c>
+      <c r="AK19">
+        <v>10</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
         <v>95</v>
       </c>
-      <c r="AJ19">
+      <c r="AN19">
         <v>99</v>
       </c>
-      <c r="AK19">
+      <c r="AO19">
         <v>99</v>
       </c>
-      <c r="AL19">
+      <c r="AP19">
         <v>99</v>
       </c>
-      <c r="AM19">
-        <v>10</v>
-      </c>
-      <c r="AN19">
-        <v>101</v>
-      </c>
-      <c r="AO19">
-        <v>101</v>
-      </c>
-      <c r="AP19">
-        <v>101</v>
-      </c>
       <c r="AQ19">
+        <v>10</v>
+      </c>
+      <c r="AR19">
+        <v>101</v>
+      </c>
+      <c r="AS19">
+        <v>101</v>
+      </c>
+      <c r="AT19">
+        <v>101</v>
+      </c>
+      <c r="AU19">
+        <v>101</v>
+      </c>
+      <c r="AV19">
+        <v>101</v>
+      </c>
+      <c r="AW19">
+        <v>101</v>
+      </c>
+      <c r="AX19">
+        <v>101</v>
+      </c>
+      <c r="AY19">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F20">
+        <v>102</v>
+      </c>
+      <c r="G20">
+        <v>102</v>
+      </c>
+      <c r="H20">
+        <v>102</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
         <v>99</v>
       </c>
-      <c r="G20">
+      <c r="K20">
         <v>94</v>
       </c>
-      <c r="H20">
+      <c r="L20">
         <v>99</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>95</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>20</v>
-      </c>
-      <c r="L20">
-        <v>20</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
       <c r="N20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>20</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="Q20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="T20">
         <v>80</v>
@@ -15839,91 +17058,115 @@
         <v>80</v>
       </c>
       <c r="AC20">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AD20">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
         <v>95</v>
       </c>
-      <c r="AJ20">
+      <c r="AN20">
         <v>99</v>
       </c>
-      <c r="AK20">
+      <c r="AO20">
         <v>92</v>
       </c>
-      <c r="AL20">
+      <c r="AP20">
         <v>99</v>
       </c>
-      <c r="AM20">
-        <v>10</v>
-      </c>
-      <c r="AN20">
-        <v>101</v>
-      </c>
-      <c r="AO20">
-        <v>101</v>
-      </c>
-      <c r="AP20">
-        <v>101</v>
-      </c>
       <c r="AQ20">
+        <v>10</v>
+      </c>
+      <c r="AR20">
+        <v>101</v>
+      </c>
+      <c r="AS20">
+        <v>101</v>
+      </c>
+      <c r="AT20">
+        <v>101</v>
+      </c>
+      <c r="AU20">
+        <v>101</v>
+      </c>
+      <c r="AV20">
+        <v>101</v>
+      </c>
+      <c r="AW20">
+        <v>101</v>
+      </c>
+      <c r="AX20">
+        <v>101</v>
+      </c>
+      <c r="AY20">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F21">
+        <v>102</v>
+      </c>
+      <c r="G21">
+        <v>102</v>
+      </c>
+      <c r="H21">
+        <v>102</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
         <v>99</v>
       </c>
-      <c r="G21">
+      <c r="K21">
         <v>99</v>
       </c>
-      <c r="H21">
+      <c r="L21">
         <v>99</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>95</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>10</v>
-      </c>
-      <c r="L21">
-        <v>20</v>
-      </c>
-      <c r="M21">
-        <v>10</v>
-      </c>
       <c r="N21">
         <v>0</v>
       </c>
@@ -15931,16 +17174,16 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="Q21">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>80</v>
@@ -15970,16 +17213,16 @@
         <v>80</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -15988,90 +17231,114 @@
         <v>0</v>
       </c>
       <c r="AI21">
+        <v>10</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>10</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
         <v>95</v>
       </c>
-      <c r="AJ21">
+      <c r="AN21">
         <v>99</v>
       </c>
-      <c r="AK21">
+      <c r="AO21">
         <v>99</v>
       </c>
-      <c r="AL21">
+      <c r="AP21">
         <v>99</v>
       </c>
-      <c r="AM21">
-        <v>10</v>
-      </c>
-      <c r="AN21">
-        <v>101</v>
-      </c>
-      <c r="AO21">
-        <v>101</v>
-      </c>
-      <c r="AP21">
-        <v>101</v>
-      </c>
       <c r="AQ21">
+        <v>10</v>
+      </c>
+      <c r="AR21">
+        <v>101</v>
+      </c>
+      <c r="AS21">
+        <v>101</v>
+      </c>
+      <c r="AT21">
+        <v>101</v>
+      </c>
+      <c r="AU21">
+        <v>101</v>
+      </c>
+      <c r="AV21">
+        <v>101</v>
+      </c>
+      <c r="AW21">
+        <v>101</v>
+      </c>
+      <c r="AX21">
+        <v>101</v>
+      </c>
+      <c r="AY21">
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="I22">
         <v>10</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>80</v>
@@ -16101,105 +17368,129 @@
         <v>80</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AM22">
         <v>10</v>
       </c>
       <c r="AN22">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AO22">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AP22">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
+        <v>10</v>
+      </c>
+      <c r="AR22">
+        <v>101</v>
+      </c>
+      <c r="AS22">
+        <v>101</v>
+      </c>
+      <c r="AT22">
+        <v>101</v>
+      </c>
+      <c r="AU22">
+        <v>101</v>
+      </c>
+      <c r="AV22">
+        <v>101</v>
+      </c>
+      <c r="AW22">
+        <v>101</v>
+      </c>
+      <c r="AX22">
+        <v>101</v>
+      </c>
+      <c r="AY22">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M23">
         <v>10</v>
       </c>
       <c r="N23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>10</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>10</v>
       </c>
       <c r="R23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -16208,25 +17499,25 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -16235,34 +17526,34 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AG23">
         <v>10</v>
       </c>
       <c r="AH23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI23">
         <v>10</v>
       </c>
       <c r="AJ23">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK23">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL23">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AM23">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN23">
         <v>101</v>
@@ -16276,43 +17567,67 @@
       <c r="AQ23">
         <v>101</v>
       </c>
+      <c r="AR23">
+        <v>101</v>
+      </c>
+      <c r="AS23">
+        <v>101</v>
+      </c>
+      <c r="AT23">
+        <v>101</v>
+      </c>
+      <c r="AU23">
+        <v>101</v>
+      </c>
+      <c r="AV23">
+        <v>101</v>
+      </c>
+      <c r="AW23">
+        <v>101</v>
+      </c>
+      <c r="AX23">
+        <v>101</v>
+      </c>
+      <c r="AY23">
+        <v>101</v>
+      </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K24">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="L24">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -16324,40 +17639,40 @@
         <v>20</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X24">
         <v>20</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB24">
         <v>20</v>
@@ -16369,31 +17684,31 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF24">
         <v>20</v>
       </c>
       <c r="AG24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ24">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK24">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AL24">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AM24">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN24">
         <v>101</v>
@@ -16407,55 +17722,79 @@
       <c r="AQ24">
         <v>101</v>
       </c>
+      <c r="AR24">
+        <v>101</v>
+      </c>
+      <c r="AS24">
+        <v>101</v>
+      </c>
+      <c r="AT24">
+        <v>101</v>
+      </c>
+      <c r="AU24">
+        <v>101</v>
+      </c>
+      <c r="AV24">
+        <v>101</v>
+      </c>
+      <c r="AW24">
+        <v>101</v>
+      </c>
+      <c r="AX24">
+        <v>101</v>
+      </c>
+      <c r="AY24">
+        <v>101</v>
+      </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J25">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L25">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M25">
         <v>10</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O25">
         <v>10</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -16464,37 +17803,37 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -16515,16 +17854,16 @@
         <v>10</v>
       </c>
       <c r="AJ25">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="AK25">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL25">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN25">
         <v>101</v>
@@ -16538,55 +17877,79 @@
       <c r="AQ25">
         <v>101</v>
       </c>
+      <c r="AR25">
+        <v>101</v>
+      </c>
+      <c r="AS25">
+        <v>101</v>
+      </c>
+      <c r="AT25">
+        <v>101</v>
+      </c>
+      <c r="AU25">
+        <v>101</v>
+      </c>
+      <c r="AV25">
+        <v>101</v>
+      </c>
+      <c r="AW25">
+        <v>101</v>
+      </c>
+      <c r="AX25">
+        <v>101</v>
+      </c>
+      <c r="AY25">
+        <v>101</v>
+      </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J26">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="K26">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="L26">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -16622,7 +17985,7 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -16634,7 +17997,7 @@
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG26">
         <v>0</v>
@@ -16643,19 +18006,19 @@
         <v>0</v>
       </c>
       <c r="AI26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN26">
         <v>101</v>
@@ -16669,43 +18032,67 @@
       <c r="AQ26">
         <v>101</v>
       </c>
+      <c r="AR26">
+        <v>101</v>
+      </c>
+      <c r="AS26">
+        <v>101</v>
+      </c>
+      <c r="AT26">
+        <v>101</v>
+      </c>
+      <c r="AU26">
+        <v>101</v>
+      </c>
+      <c r="AV26">
+        <v>101</v>
+      </c>
+      <c r="AW26">
+        <v>101</v>
+      </c>
+      <c r="AX26">
+        <v>101</v>
+      </c>
+      <c r="AY26">
+        <v>101</v>
+      </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="J27">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -16732,25 +18119,25 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -16777,16 +18164,16 @@
         <v>10</v>
       </c>
       <c r="AJ27">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AK27">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AL27">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AM27">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AN27">
         <v>101</v>
@@ -16800,49 +18187,73 @@
       <c r="AQ27">
         <v>101</v>
       </c>
+      <c r="AR27">
+        <v>101</v>
+      </c>
+      <c r="AS27">
+        <v>101</v>
+      </c>
+      <c r="AT27">
+        <v>101</v>
+      </c>
+      <c r="AU27">
+        <v>101</v>
+      </c>
+      <c r="AV27">
+        <v>101</v>
+      </c>
+      <c r="AW27">
+        <v>101</v>
+      </c>
+      <c r="AX27">
+        <v>101</v>
+      </c>
+      <c r="AY27">
+        <v>101</v>
+      </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -16851,49 +18262,49 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB28">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF28">
         <v>101</v>
@@ -16908,10 +18319,10 @@
         <v>101</v>
       </c>
       <c r="AJ28">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK28">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL28">
         <v>101</v>
@@ -16931,49 +18342,73 @@
       <c r="AQ28">
         <v>101</v>
       </c>
+      <c r="AR28">
+        <v>101</v>
+      </c>
+      <c r="AS28">
+        <v>101</v>
+      </c>
+      <c r="AT28">
+        <v>101</v>
+      </c>
+      <c r="AU28">
+        <v>101</v>
+      </c>
+      <c r="AV28">
+        <v>101</v>
+      </c>
+      <c r="AW28">
+        <v>101</v>
+      </c>
+      <c r="AX28">
+        <v>101</v>
+      </c>
+      <c r="AY28">
+        <v>101</v>
+      </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -16982,49 +18417,49 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB29">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF29">
         <v>101</v>
@@ -17039,10 +18474,10 @@
         <v>101</v>
       </c>
       <c r="AJ29">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK29">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL29">
         <v>101</v>
@@ -17062,49 +18497,73 @@
       <c r="AQ29">
         <v>101</v>
       </c>
+      <c r="AR29">
+        <v>101</v>
+      </c>
+      <c r="AS29">
+        <v>101</v>
+      </c>
+      <c r="AT29">
+        <v>101</v>
+      </c>
+      <c r="AU29">
+        <v>101</v>
+      </c>
+      <c r="AV29">
+        <v>101</v>
+      </c>
+      <c r="AW29">
+        <v>101</v>
+      </c>
+      <c r="AX29">
+        <v>101</v>
+      </c>
+      <c r="AY29">
+        <v>101</v>
+      </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -17113,19 +18572,19 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -17143,19 +18602,19 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF30">
         <v>101</v>
@@ -17170,10 +18629,10 @@
         <v>101</v>
       </c>
       <c r="AJ30">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK30">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL30">
         <v>101</v>
@@ -17193,49 +18652,73 @@
       <c r="AQ30">
         <v>101</v>
       </c>
+      <c r="AR30">
+        <v>101</v>
+      </c>
+      <c r="AS30">
+        <v>101</v>
+      </c>
+      <c r="AT30">
+        <v>101</v>
+      </c>
+      <c r="AU30">
+        <v>101</v>
+      </c>
+      <c r="AV30">
+        <v>101</v>
+      </c>
+      <c r="AW30">
+        <v>101</v>
+      </c>
+      <c r="AX30">
+        <v>101</v>
+      </c>
+      <c r="AY30">
+        <v>101</v>
+      </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -17244,49 +18727,49 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
         <v>72</v>
       </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
       <c r="AA31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF31">
         <v>101</v>
@@ -17301,10 +18784,10 @@
         <v>101</v>
       </c>
       <c r="AJ31">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK31">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL31">
         <v>101</v>
@@ -17324,8 +18807,32 @@
       <c r="AQ31">
         <v>101</v>
       </c>
+      <c r="AR31">
+        <v>101</v>
+      </c>
+      <c r="AS31">
+        <v>101</v>
+      </c>
+      <c r="AT31">
+        <v>101</v>
+      </c>
+      <c r="AU31">
+        <v>101</v>
+      </c>
+      <c r="AV31">
+        <v>101</v>
+      </c>
+      <c r="AW31">
+        <v>101</v>
+      </c>
+      <c r="AX31">
+        <v>101</v>
+      </c>
+      <c r="AY31">
+        <v>101</v>
+      </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>100</v>
       </c>
@@ -17375,19 +18882,19 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -17405,19 +18912,19 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF32">
         <v>101</v>
@@ -17432,31 +18939,55 @@
         <v>101</v>
       </c>
       <c r="AJ32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AM32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP32">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AQ32">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="AR32">
+        <v>100</v>
+      </c>
+      <c r="AS32">
+        <v>100</v>
+      </c>
+      <c r="AT32">
+        <v>100</v>
+      </c>
+      <c r="AU32">
+        <v>100</v>
+      </c>
+      <c r="AV32">
+        <v>100</v>
+      </c>
+      <c r="AW32">
+        <v>100</v>
+      </c>
+      <c r="AX32">
+        <v>100</v>
+      </c>
+      <c r="AY32">
+        <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>100</v>
       </c>
@@ -17506,16 +19037,16 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="R33">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="S33">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -17539,16 +19070,16 @@
         <v>10</v>
       </c>
       <c r="AB33">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AE33">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="AF33">
         <v>101</v>
@@ -17563,72 +19094,96 @@
         <v>101</v>
       </c>
       <c r="AJ33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AM33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AN33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AO33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AP33">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AQ33">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="AR33">
+        <v>100</v>
+      </c>
+      <c r="AS33">
+        <v>100</v>
+      </c>
+      <c r="AT33">
+        <v>100</v>
+      </c>
+      <c r="AU33">
+        <v>100</v>
+      </c>
+      <c r="AV33">
+        <v>100</v>
+      </c>
+      <c r="AW33">
+        <v>100</v>
+      </c>
+      <c r="AX33">
+        <v>100</v>
+      </c>
+      <c r="AY33">
+        <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -17637,37 +19192,37 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U34">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V34">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="W34">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB34">
         <v>101</v>
@@ -17694,10 +19249,10 @@
         <v>101</v>
       </c>
       <c r="AJ34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK34">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL34">
         <v>101</v>
@@ -17717,49 +19272,73 @@
       <c r="AQ34">
         <v>101</v>
       </c>
+      <c r="AR34">
+        <v>101</v>
+      </c>
+      <c r="AS34">
+        <v>101</v>
+      </c>
+      <c r="AT34">
+        <v>101</v>
+      </c>
+      <c r="AU34">
+        <v>101</v>
+      </c>
+      <c r="AV34">
+        <v>101</v>
+      </c>
+      <c r="AW34">
+        <v>101</v>
+      </c>
+      <c r="AX34">
+        <v>101</v>
+      </c>
+      <c r="AY34">
+        <v>101</v>
+      </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -17768,37 +19347,37 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U35">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V35">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="W35">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB35">
         <v>101</v>
@@ -17825,10 +19404,10 @@
         <v>101</v>
       </c>
       <c r="AJ35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK35">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL35">
         <v>101</v>
@@ -17848,49 +19427,73 @@
       <c r="AQ35">
         <v>101</v>
       </c>
+      <c r="AR35">
+        <v>101</v>
+      </c>
+      <c r="AS35">
+        <v>101</v>
+      </c>
+      <c r="AT35">
+        <v>101</v>
+      </c>
+      <c r="AU35">
+        <v>101</v>
+      </c>
+      <c r="AV35">
+        <v>101</v>
+      </c>
+      <c r="AW35">
+        <v>101</v>
+      </c>
+      <c r="AX35">
+        <v>101</v>
+      </c>
+      <c r="AY35">
+        <v>101</v>
+      </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -17899,37 +19502,37 @@
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T36">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U36">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V36">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="W36">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB36">
         <v>101</v>
@@ -17956,10 +19559,10 @@
         <v>101</v>
       </c>
       <c r="AJ36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK36">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL36">
         <v>101</v>
@@ -17979,49 +19582,73 @@
       <c r="AQ36">
         <v>101</v>
       </c>
+      <c r="AR36">
+        <v>101</v>
+      </c>
+      <c r="AS36">
+        <v>101</v>
+      </c>
+      <c r="AT36">
+        <v>101</v>
+      </c>
+      <c r="AU36">
+        <v>101</v>
+      </c>
+      <c r="AV36">
+        <v>101</v>
+      </c>
+      <c r="AW36">
+        <v>101</v>
+      </c>
+      <c r="AX36">
+        <v>101</v>
+      </c>
+      <c r="AY36">
+        <v>101</v>
+      </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O37">
         <v>100</v>
@@ -18030,37 +19657,37 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U37">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V37">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="W37">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Z37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AA37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AB37">
         <v>101</v>
@@ -18087,10 +19714,10 @@
         <v>101</v>
       </c>
       <c r="AJ37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK37">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AL37">
         <v>101</v>
@@ -18110,51 +19737,420 @@
       <c r="AQ37">
         <v>101</v>
       </c>
+      <c r="AR37">
+        <v>101</v>
+      </c>
+      <c r="AS37">
+        <v>101</v>
+      </c>
+      <c r="AT37">
+        <v>101</v>
+      </c>
+      <c r="AU37">
+        <v>101</v>
+      </c>
+      <c r="AV37">
+        <v>101</v>
+      </c>
+      <c r="AW37">
+        <v>101</v>
+      </c>
+      <c r="AX37">
+        <v>101</v>
+      </c>
+      <c r="AY37">
+        <v>101</v>
+      </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.45">
       <c r="U39" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:X4 I1:T5 A1:H37 U5:Y5 S6:AE10 AG6:AQ10 I6:R20 AK6:AQ27 N11:AL11 S11:AQ12 A11:L15 O12:AL12 AE12:AL15 S13:AM19 N13:N23 I16:I21 T16:AF25 R18:S20 AH18:AH20 J18:M21 S20:X20 Y20:AM27 I21:X27 A23:L28 R26:AI26 M27:AL27 U27:AE32 T28:X34 V28:AE35 AG33:AQ37 T34:AE35 U34:X37 S35:AE37 K38:AE45 A38:J49 AF38:XFD1048576 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AL6:AY6 AR1:XFD37 AK33:AY33 A28:T37 A5:T10">
+    <cfRule type="expression" dxfId="119" priority="120" stopIfTrue="1">
+      <formula>A1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="119" stopIfTrue="1">
+      <formula>A1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="118" stopIfTrue="1">
+      <formula>A1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="117" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:X4 I1:T5 O1:P10 AF1:AQ10 A1:H37 AR1:XFD37 U5:AE5 I6:AE10 A11:L15 I11:AQ37 A23:L28 A38:XFD1048576 AB1:AE4 AL5:AY6 AK32:AY33 A28:T37 A5:T10">
+    <cfRule type="expression" dxfId="115" priority="113">
+      <formula>A1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="114" priority="112">
+      <formula>A1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="116" stopIfTrue="1">
+      <formula>A1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="115" stopIfTrue="1">
+      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="114">
+      <formula>A1=80</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="110" priority="111">
+      <formula>A1=101</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="110">
       <formula>A1=102</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>A1=101</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:P10">
+    <cfRule type="expression" dxfId="108" priority="60" stopIfTrue="1">
+      <formula>O1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="64" stopIfTrue="1">
+      <formula>O1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="65" stopIfTrue="1">
+      <formula>O1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="53">
+      <formula>O1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="104" priority="54">
+      <formula>O1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="55">
+      <formula>O1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="56" stopIfTrue="1">
+      <formula>AND(O1&gt;=90, O1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="57" stopIfTrue="1">
+      <formula>O1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="58" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="59" stopIfTrue="1">
+      <formula>O1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="61" stopIfTrue="1">
+      <formula>O1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="62" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="63" stopIfTrue="1">
+      <formula>O1=11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:T4 E1:P5 AP1:XFD49 Q5:U5 O6:AA10 AC6:AM10 E6:N20 AG6:AM27 G9:O9 G10:P10 J11:AH11 O11:AM12 K12:AH12 AA12:AH15 O13:AI19 J13:J23 E16:E21 P16:AB25 N18:O20 AD18:AD20 F18:I21 O20:T20 U20:AI27 E21:T27 N26:AE26 I27:AH27 Q27:AA32 P28:T34 R28:AA35 AC33:AM37 P34:AA35 Q34:T37 O35:AA37 K38:AE45 AF38:AO49 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576 A38:J49 E28:P37 A1:D37 AN1:AQ37">
-    <cfRule type="expression" dxfId="8" priority="8" stopIfTrue="1">
-      <formula>A1=20</formula>
+  <conditionalFormatting sqref="O28:P37">
+    <cfRule type="expression" dxfId="95" priority="41">
+      <formula>O28=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
-      <formula>A1=11</formula>
+    <cfRule type="expression" dxfId="94" priority="42">
+      <formula>O28=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="10" stopIfTrue="1">
-      <formula>A1=10</formula>
+    <cfRule type="expression" dxfId="93" priority="43" stopIfTrue="1">
+      <formula>AND(O28&gt;=90, O28&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="11" stopIfTrue="1">
-      <formula>A1=0</formula>
+    <cfRule type="expression" dxfId="92" priority="44" stopIfTrue="1">
+      <formula>O28=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="45" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="46" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="47" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="48" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="49" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="51" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="52" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="50" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="40">
+      <formula>O28=72</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:T4 X1:AA4 E1:P5 AB1:AM10 Q5:AA5 E6:AA10 E11:AM37 A38:XFD1048576 A1:D37 AN1:XFD37">
-    <cfRule type="expression" dxfId="4" priority="3">
-      <formula>A1=72</formula>
+  <conditionalFormatting sqref="Y1:AA4">
+    <cfRule type="expression" dxfId="82" priority="109" stopIfTrue="1">
+      <formula>Y1=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>A1=71</formula>
+    <cfRule type="expression" dxfId="81" priority="108" stopIfTrue="1">
+      <formula>Y1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
-      <formula>A1=80</formula>
+    <cfRule type="expression" dxfId="80" priority="107" stopIfTrue="1">
+      <formula>Y1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
-      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    <cfRule type="expression" dxfId="79" priority="106" stopIfTrue="1">
+      <formula>Y1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>A1=100</formula>
+    <cfRule type="expression" dxfId="78" priority="105" stopIfTrue="1">
+      <formula>Y1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="103">
+      <formula>Y1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="102">
+      <formula>Y1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="101">
+      <formula>Y1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="104" stopIfTrue="1">
+      <formula>AND(Y1&gt;=90, Y1&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y34:AA37">
+    <cfRule type="expression" dxfId="73" priority="95" stopIfTrue="1">
+      <formula>AND(Y34&gt;=90, Y34&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="96" stopIfTrue="1">
+      <formula>Y34=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="97" stopIfTrue="1">
+      <formula>Y34=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="98" stopIfTrue="1">
+      <formula>Y34=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="100" stopIfTrue="1">
+      <formula>Y34=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="94">
+      <formula>Y34=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="99" stopIfTrue="1">
+      <formula>Y34=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="92">
+      <formula>Y34=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="93">
+      <formula>Y34=71</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ1:AK10 AL5:AY6">
+    <cfRule type="expression" dxfId="64" priority="66">
+      <formula>AJ1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="67">
+      <formula>AJ1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="68">
+      <formula>AJ1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="69" stopIfTrue="1">
+      <formula>AND(AJ1&gt;=90, AJ1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="74" stopIfTrue="1">
+      <formula>AJ1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="78" stopIfTrue="1">
+      <formula>AJ1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="77" stopIfTrue="1">
+      <formula>AJ1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="76" stopIfTrue="1">
+      <formula>AJ1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="75" stopIfTrue="1">
+      <formula>AJ1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="73" stopIfTrue="1">
+      <formula>AJ1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="72" stopIfTrue="1">
+      <formula>AJ1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="71" stopIfTrue="1">
+      <formula>AJ1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="70" stopIfTrue="1">
+      <formula>AJ1=100</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ28:AL31 AJ32:AK37">
+    <cfRule type="expression" dxfId="51" priority="84" stopIfTrue="1">
+      <formula>AJ28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="83" stopIfTrue="1">
+      <formula>AJ28=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="81">
+      <formula>AJ28=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="79">
+      <formula>AJ28=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="91" stopIfTrue="1">
+      <formula>AJ28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="90" stopIfTrue="1">
+      <formula>AJ28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="89" stopIfTrue="1">
+      <formula>AJ28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="82" stopIfTrue="1">
+      <formula>AND(AJ28&gt;=90, AJ28&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="88" stopIfTrue="1">
+      <formula>AJ28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="87" stopIfTrue="1">
+      <formula>AJ28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="86" stopIfTrue="1">
+      <formula>AJ28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="85" stopIfTrue="1">
+      <formula>AJ28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="80">
+      <formula>AJ28=71</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK32:AY33">
+    <cfRule type="expression" dxfId="38" priority="27">
+      <formula>AK32=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="28">
+      <formula>AK32=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="29">
+      <formula>AK32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="30" stopIfTrue="1">
+      <formula>AND(AK32&gt;=90, AK32&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="31" stopIfTrue="1">
+      <formula>AK32=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="32" stopIfTrue="1">
+      <formula>AK32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="33" stopIfTrue="1">
+      <formula>AK32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="34" stopIfTrue="1">
+      <formula>AK32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
+      <formula>AK32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="36" stopIfTrue="1">
+      <formula>AK32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="37" stopIfTrue="1">
+      <formula>AK32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="38" stopIfTrue="1">
+      <formula>AK32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="39" stopIfTrue="1">
+      <formula>AK32=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:N33">
+    <cfRule type="expression" dxfId="25" priority="14">
+      <formula>A32=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="15">
+      <formula>A32=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="16">
+      <formula>A32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="17" stopIfTrue="1">
+      <formula>AND(A32&gt;=90, A32&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="18" stopIfTrue="1">
+      <formula>A32=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="19" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="20" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="22" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="23" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:N6">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>A5=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="2">
+      <formula>A5=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="3">
+      <formula>A5=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
+      <formula>AND(A5&gt;=90, A5&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="5" stopIfTrue="1">
+      <formula>A5=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+      <formula>A5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
+      <formula>A5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="10" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="11" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="12" stopIfTrue="1">
+      <formula>A5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="13" stopIfTrue="1">
+      <formula>A5=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hotat\OneDrive\デスクトップ\GCP\DecoBom\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7B0D32-C4E0-437F-84F7-026C9EC9F1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09A226D-4D8B-42D0-8EE7-3AD8C0D08F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
   <sheets>
     <sheet name="stage1" sheetId="3" r:id="rId1"/>
     <sheet name="stage2" sheetId="1" r:id="rId2"/>
     <sheet name="stage3" sheetId="4" r:id="rId3"/>
     <sheet name="stage4" sheetId="5" r:id="rId4"/>
+    <sheet name="stage5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -100,7 +101,28 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="276">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -111,6 +133,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -118,6 +154,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -125,6 +168,69 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -132,6 +238,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -139,6 +266,41 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -146,6 +308,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -167,6 +350,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -174,6 +378,41 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -181,6 +420,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -195,6 +455,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -223,6 +490,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -237,6 +525,41 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -258,6 +581,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -265,6 +644,104 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -272,6 +749,76 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -293,6 +840,48 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -314,6 +903,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -321,6 +931,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -328,6 +945,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -335,6 +1008,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -342,6 +1022,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -349,6 +1043,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -356,6 +1071,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -363,6 +1134,62 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -384,6 +1211,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -391,6 +1239,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -398,6 +1260,97 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -405,6 +1358,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -412,6 +1386,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -419,6 +1421,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -426,6 +1442,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -433,6 +1456,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -440,6 +1477,41 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -447,6 +1519,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -454,6 +1533,48 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
@@ -468,6 +1589,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
@@ -475,6 +1610,69 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -482,6 +1680,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -489,6 +1701,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -496,6 +1722,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -503,6 +1736,55 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -510,6 +1792,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -517,14 +1813,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -553,391 +1856,6 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4648,27 +5566,27 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:G8 O1:U8 V1:XFD49 H2:N8 A9:U49 A50:XFD1048576">
-    <cfRule type="expression" dxfId="144" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="275" priority="4" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="143" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="274" priority="5" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="273" priority="6" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="272" priority="7" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="140" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="270" priority="2" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="269" priority="3" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10814,33 +11732,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="137" priority="1">
+    <cfRule type="expression" dxfId="268" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="2">
+    <cfRule type="expression" dxfId="267" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="3">
+    <cfRule type="expression" dxfId="266" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="265" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="264" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO16 K16:P16 Q16:AE34 A17:P23 AE17:AO33 A24:K26 L24:P34 K27:K34 A27:J49 AF34:AO49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="132" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="263" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="131" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="262" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="261" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="260" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13979,33 +14897,33 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="128" priority="1">
+    <cfRule type="expression" dxfId="259" priority="1">
       <formula>A1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="2">
+    <cfRule type="expression" dxfId="258" priority="2">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="3">
+    <cfRule type="expression" dxfId="257" priority="3">
       <formula>A1=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="256" priority="4" stopIfTrue="1">
       <formula>AND(A1&gt;=90, A1&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="255" priority="5" stopIfTrue="1">
       <formula>A1=100</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:Q8 Y1:AO8 A1:J16 AP1:XFD49 R2:X8 K9:AE15 AF9:AO49 K16:P16 Q16:AE34 A17:P23 A24:K26 L24:P34 K27:K34 A27:J49 K35:AE45 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AF50:XFD1048576">
-    <cfRule type="expression" dxfId="123" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="254" priority="6" stopIfTrue="1">
       <formula>A1=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="253" priority="7" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="252" priority="8" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="251" priority="9" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19769,388 +20687,6679 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:X4 I1:T5 A1:H37 U5:Y5 S6:AE10 AG6:AQ10 I6:R20 AK6:AQ27 N11:AL11 S11:AQ12 A11:L15 O12:AL12 AE12:AL15 S13:AM19 N13:N23 I16:I21 T16:AF25 R18:S20 AH18:AH20 J18:M21 S20:X20 Y20:AM27 I21:X27 A23:L28 R26:AI26 M27:AL27 U27:AE32 T28:X34 V28:AE35 AG33:AQ37 T34:AE35 U34:X37 S35:AE37 K38:AE45 A38:J49 AF38:XFD1048576 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576 AL6:AY6 AR1:XFD37 AK33:AY33 A28:T37 A5:T10">
-    <cfRule type="expression" dxfId="119" priority="120" stopIfTrue="1">
+  <conditionalFormatting sqref="A5:N6">
+    <cfRule type="expression" dxfId="250" priority="1">
+      <formula>A5=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="249" priority="2">
+      <formula>A5=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="248" priority="3">
+      <formula>A5=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="247" priority="4" stopIfTrue="1">
+      <formula>AND(A5&gt;=90, A5&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="246" priority="5" stopIfTrue="1">
+      <formula>A5=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="245" priority="6" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="244" priority="7" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="243" priority="8" stopIfTrue="1">
+      <formula>A5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="242" priority="9" stopIfTrue="1">
+      <formula>A5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="241" priority="10" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="240" priority="11" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="239" priority="12" stopIfTrue="1">
+      <formula>A5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="238" priority="13" stopIfTrue="1">
+      <formula>A5=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:N33">
+    <cfRule type="expression" dxfId="237" priority="14">
+      <formula>A32=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="236" priority="15">
+      <formula>A32=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="235" priority="16">
+      <formula>A32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="234" priority="17" stopIfTrue="1">
+      <formula>AND(A32&gt;=90, A32&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="233" priority="18" stopIfTrue="1">
+      <formula>A32=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="232" priority="19" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="231" priority="20" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="230" priority="21" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="229" priority="22" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="228" priority="23" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="227" priority="24" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="226" priority="25" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="225" priority="26" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:X4 I1:T5 A1:H37 AR1:XFD37 U5:Y5 A5:T10 AL6:AY6 S6:AE10 AG6:AQ10 I6:R20 AK6:AQ27 N11:AL11 S11:AQ12 A11:L15 O12:AL12 AE12:AL15 S13:AM19 N13:N23 I16:I21 T16:AF25 R18:S20 AH18:AH20 J18:M21 S20:X20 Y20:AM27 I21:X27 A23:L28 R26:AI26 M27:AL27 U27:AE32 T28:X34 V28:AE35 A28:T37 AK33:AY33 AG33:AQ37 T34:AE35 U34:X37 S35:AE37 K38:AE45 A38:J49 AF38:XFD1048576 R46:AE48 K46:Q49 R49:X49 Y49:AE1048576 A50:X1048576">
+    <cfRule type="expression" dxfId="224" priority="117" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="223" priority="120" stopIfTrue="1">
       <formula>A1=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="119" stopIfTrue="1">
+    <cfRule type="expression" dxfId="222" priority="119" stopIfTrue="1">
       <formula>A1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="118" stopIfTrue="1">
+    <cfRule type="expression" dxfId="221" priority="118" stopIfTrue="1">
       <formula>A1=11</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="117" stopIfTrue="1">
-      <formula>A1=20</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:X4 I1:T5 O1:P10 AF1:AQ10 A1:H37 AR1:XFD37 U5:AE5 I6:AE10 A11:L15 I11:AQ37 A23:L28 A38:XFD1048576 AB1:AE4 AL5:AY6 AK32:AY33 A28:T37 A5:T10">
-    <cfRule type="expression" dxfId="115" priority="113">
+  <conditionalFormatting sqref="A1:X4 AB1:AE4 I1:T5 O1:P10 AF1:AQ10 A1:H37 AR1:XFD37 U5:AE5 AL5:AY6 A5:T10 I6:AE10 A11:L15 I11:AQ37 A23:L28 A28:T37 AK32:AY33 A38:XFD1048576">
+    <cfRule type="expression" dxfId="220" priority="116" stopIfTrue="1">
+      <formula>A1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="219" priority="115" stopIfTrue="1">
+      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="218" priority="114">
+      <formula>A1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="217" priority="113">
       <formula>A1=71</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="112">
+    <cfRule type="expression" dxfId="216" priority="112">
       <formula>A1=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="116" stopIfTrue="1">
-      <formula>A1=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="112" priority="115" stopIfTrue="1">
-      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="111" priority="114">
-      <formula>A1=80</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="110" priority="111">
+    <cfRule type="expression" dxfId="215" priority="111">
       <formula>A1=101</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="110">
+    <cfRule type="expression" dxfId="214" priority="110">
       <formula>A1=102</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:P10">
-    <cfRule type="expression" dxfId="108" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="213" priority="65" stopIfTrue="1">
+      <formula>O1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="212" priority="64" stopIfTrue="1">
       <formula>O1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="211" priority="62" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="210" priority="57" stopIfTrue="1">
+      <formula>O1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="209" priority="58" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="208" priority="59" stopIfTrue="1">
+      <formula>O1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="207" priority="60" stopIfTrue="1">
       <formula>O1=10</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="206" priority="63" stopIfTrue="1">
+      <formula>O1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="205" priority="54">
+      <formula>O1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="204" priority="61" stopIfTrue="1">
       <formula>O1=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="53">
+    <cfRule type="expression" dxfId="203" priority="55">
+      <formula>O1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="202" priority="56" stopIfTrue="1">
+      <formula>AND(O1&gt;=90, O1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="201" priority="53">
       <formula>O1=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="54">
-      <formula>O1=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="55">
-      <formula>O1=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="56" stopIfTrue="1">
-      <formula>AND(O1&gt;=90, O1&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="57" stopIfTrue="1">
-      <formula>O1=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="58" stopIfTrue="1">
-      <formula>O1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="59" stopIfTrue="1">
-      <formula>O1=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="61" stopIfTrue="1">
-      <formula>O1=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="62" stopIfTrue="1">
-      <formula>O1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="63" stopIfTrue="1">
-      <formula>O1=11</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:P37">
-    <cfRule type="expression" dxfId="95" priority="41">
+    <cfRule type="expression" dxfId="200" priority="42">
+      <formula>O28=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="199" priority="43" stopIfTrue="1">
+      <formula>AND(O28&gt;=90, O28&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="198" priority="44" stopIfTrue="1">
+      <formula>O28=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="197" priority="45" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="196" priority="47" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="48" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="194" priority="49" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="193" priority="50" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="192" priority="51" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="191" priority="52" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="190" priority="46" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="189" priority="40">
+      <formula>O28=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="188" priority="41">
       <formula>O28=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="42">
-      <formula>O28=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="43" stopIfTrue="1">
-      <formula>AND(O28&gt;=90, O28&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="92" priority="44" stopIfTrue="1">
-      <formula>O28=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="45" stopIfTrue="1">
-      <formula>O28=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="46" stopIfTrue="1">
-      <formula>O28=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="47" stopIfTrue="1">
-      <formula>O28=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="48" stopIfTrue="1">
-      <formula>O28=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="49" stopIfTrue="1">
-      <formula>O28=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="51" stopIfTrue="1">
-      <formula>O28=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="52" stopIfTrue="1">
-      <formula>O28=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="50" stopIfTrue="1">
-      <formula>O28=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="40">
-      <formula>O28=72</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AA4">
-    <cfRule type="expression" dxfId="82" priority="109" stopIfTrue="1">
+    <cfRule type="expression" dxfId="187" priority="104" stopIfTrue="1">
+      <formula>AND(Y1&gt;=90, Y1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="186" priority="107" stopIfTrue="1">
+      <formula>Y1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="185" priority="103">
+      <formula>Y1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="184" priority="102">
+      <formula>Y1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="183" priority="101">
+      <formula>Y1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="182" priority="106" stopIfTrue="1">
+      <formula>Y1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="181" priority="105" stopIfTrue="1">
+      <formula>Y1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="180" priority="108" stopIfTrue="1">
+      <formula>Y1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="179" priority="109" stopIfTrue="1">
       <formula>Y1=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="108" stopIfTrue="1">
-      <formula>Y1=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="107" stopIfTrue="1">
-      <formula>Y1=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="106" stopIfTrue="1">
-      <formula>Y1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="105" stopIfTrue="1">
-      <formula>Y1=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="103">
-      <formula>Y1=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="102">
-      <formula>Y1=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="101">
-      <formula>Y1=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="104" stopIfTrue="1">
-      <formula>AND(Y1&gt;=90, Y1&lt;100)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y34:AA37">
-    <cfRule type="expression" dxfId="73" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="178" priority="100" stopIfTrue="1">
+      <formula>Y34=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="177" priority="92">
+      <formula>Y34=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="176" priority="99" stopIfTrue="1">
+      <formula>Y34=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="175" priority="98" stopIfTrue="1">
+      <formula>Y34=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="97" stopIfTrue="1">
+      <formula>Y34=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="173" priority="96" stopIfTrue="1">
+      <formula>Y34=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="172" priority="95" stopIfTrue="1">
       <formula>AND(Y34&gt;=90, Y34&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="96" stopIfTrue="1">
-      <formula>Y34=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="97" stopIfTrue="1">
-      <formula>Y34=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="98" stopIfTrue="1">
-      <formula>Y34=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="100" stopIfTrue="1">
-      <formula>Y34=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="94">
+    <cfRule type="expression" dxfId="171" priority="94">
       <formula>Y34=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="99" stopIfTrue="1">
-      <formula>Y34=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="92">
-      <formula>Y34=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="93">
+    <cfRule type="expression" dxfId="170" priority="93">
       <formula>Y34=71</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ1:AK10 AL5:AY6">
-    <cfRule type="expression" dxfId="64" priority="66">
+    <cfRule type="expression" dxfId="169" priority="67">
+      <formula>AJ1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="168" priority="68">
+      <formula>AJ1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="167" priority="69" stopIfTrue="1">
+      <formula>AND(AJ1&gt;=90, AJ1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="70" stopIfTrue="1">
+      <formula>AJ1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="165" priority="72" stopIfTrue="1">
+      <formula>AJ1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="73" stopIfTrue="1">
+      <formula>AJ1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="163" priority="74" stopIfTrue="1">
+      <formula>AJ1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="162" priority="75" stopIfTrue="1">
+      <formula>AJ1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="161" priority="76" stopIfTrue="1">
+      <formula>AJ1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="160" priority="77" stopIfTrue="1">
+      <formula>AJ1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="78" stopIfTrue="1">
+      <formula>AJ1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="158" priority="71" stopIfTrue="1">
+      <formula>AJ1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="157" priority="66">
       <formula>AJ1=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="67">
-      <formula>AJ1=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="68">
-      <formula>AJ1=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="69" stopIfTrue="1">
-      <formula>AND(AJ1&gt;=90, AJ1&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="74" stopIfTrue="1">
-      <formula>AJ1=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="78" stopIfTrue="1">
-      <formula>AJ1=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="77" stopIfTrue="1">
-      <formula>AJ1=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="76" stopIfTrue="1">
-      <formula>AJ1=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="75" stopIfTrue="1">
-      <formula>AJ1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="73" stopIfTrue="1">
-      <formula>AJ1=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="72" stopIfTrue="1">
-      <formula>AJ1=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="71" stopIfTrue="1">
-      <formula>AJ1=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="70" stopIfTrue="1">
-      <formula>AJ1=100</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ32:AK37 AJ28:AL31">
+    <cfRule type="expression" dxfId="156" priority="80">
+      <formula>AJ28=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="155" priority="79">
+      <formula>AJ28=72</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ28:AL31 AJ32:AK37">
-    <cfRule type="expression" dxfId="51" priority="84" stopIfTrue="1">
+    <cfRule type="expression" dxfId="154" priority="89" stopIfTrue="1">
+      <formula>AJ28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="153" priority="88" stopIfTrue="1">
       <formula>AJ28=20</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="83" stopIfTrue="1">
+    <cfRule type="expression" dxfId="152" priority="87" stopIfTrue="1">
+      <formula>AJ28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="151" priority="86" stopIfTrue="1">
+      <formula>AJ28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="150" priority="85" stopIfTrue="1">
+      <formula>AJ28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="84" stopIfTrue="1">
+      <formula>AJ28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="148" priority="83" stopIfTrue="1">
       <formula>AJ28=100</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="81">
+    <cfRule type="expression" dxfId="147" priority="82" stopIfTrue="1">
+      <formula>AND(AJ28&gt;=90, AJ28&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="81">
       <formula>AJ28=80</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="79">
-      <formula>AJ28=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="145" priority="91" stopIfTrue="1">
       <formula>AJ28=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="144" priority="90" stopIfTrue="1">
       <formula>AJ28=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="89" stopIfTrue="1">
-      <formula>AJ28=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="82" stopIfTrue="1">
-      <formula>AND(AJ28&gt;=90, AJ28&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="88" stopIfTrue="1">
-      <formula>AJ28=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="87" stopIfTrue="1">
-      <formula>AJ28=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="86" stopIfTrue="1">
-      <formula>AJ28=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="85" stopIfTrue="1">
-      <formula>AJ28=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="80">
-      <formula>AJ28=71</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK32:AY33">
-    <cfRule type="expression" dxfId="38" priority="27">
+    <cfRule type="expression" dxfId="143" priority="37" stopIfTrue="1">
+      <formula>AK32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="142" priority="36" stopIfTrue="1">
+      <formula>AK32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="141" priority="35" stopIfTrue="1">
+      <formula>AK32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="140" priority="34" stopIfTrue="1">
+      <formula>AK32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="139" priority="33" stopIfTrue="1">
+      <formula>AK32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="32" stopIfTrue="1">
+      <formula>AK32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="137" priority="30" stopIfTrue="1">
+      <formula>AND(AK32&gt;=90, AK32&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="29">
+      <formula>AK32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="135" priority="28">
+      <formula>AK32=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="27">
       <formula>AK32=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="28">
-      <formula>AK32=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="29">
-      <formula>AK32=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="30" stopIfTrue="1">
-      <formula>AND(AK32&gt;=90, AK32&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="133" priority="39" stopIfTrue="1">
+      <formula>AK32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="38" stopIfTrue="1">
+      <formula>AK32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="31" stopIfTrue="1">
       <formula>AK32=100</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="32" stopIfTrue="1">
-      <formula>AK32=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="33" stopIfTrue="1">
-      <formula>AK32=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="34" stopIfTrue="1">
-      <formula>AK32=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
-      <formula>AK32=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="36" stopIfTrue="1">
-      <formula>AK32=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="37" stopIfTrue="1">
-      <formula>AK32=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="38" stopIfTrue="1">
-      <formula>AK32=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="39" stopIfTrue="1">
-      <formula>AK32=0</formula>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BEFBC4B-02AF-4B44-83D7-B4780A41A994}">
+  <dimension ref="A1:AZ37"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="21" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.3984375" customWidth="1"/>
+    <col min="23" max="52" width="4.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A1">
+        <v>102</v>
+      </c>
+      <c r="B1">
+        <v>102</v>
+      </c>
+      <c r="C1">
+        <v>102</v>
+      </c>
+      <c r="D1">
+        <v>102</v>
+      </c>
+      <c r="E1">
+        <v>102</v>
+      </c>
+      <c r="F1">
+        <v>102</v>
+      </c>
+      <c r="G1">
+        <v>102</v>
+      </c>
+      <c r="H1">
+        <v>102</v>
+      </c>
+      <c r="I1">
+        <v>102</v>
+      </c>
+      <c r="J1">
+        <v>102</v>
+      </c>
+      <c r="K1">
+        <v>102</v>
+      </c>
+      <c r="L1">
+        <v>102</v>
+      </c>
+      <c r="M1">
+        <v>102</v>
+      </c>
+      <c r="N1">
+        <v>102</v>
+      </c>
+      <c r="O1">
+        <v>100</v>
+      </c>
+      <c r="P1">
+        <v>100</v>
+      </c>
+      <c r="Q1">
+        <v>102</v>
+      </c>
+      <c r="R1">
+        <v>102</v>
+      </c>
+      <c r="S1">
+        <v>102</v>
+      </c>
+      <c r="T1">
+        <v>102</v>
+      </c>
+      <c r="U1">
+        <v>102</v>
+      </c>
+      <c r="V1">
+        <v>102</v>
+      </c>
+      <c r="W1">
+        <v>102</v>
+      </c>
+      <c r="X1">
+        <v>102</v>
+      </c>
+      <c r="Y1">
+        <v>102</v>
+      </c>
+      <c r="Z1">
+        <v>100</v>
+      </c>
+      <c r="AA1">
+        <v>100</v>
+      </c>
+      <c r="AB1">
+        <v>100</v>
+      </c>
+      <c r="AC1">
+        <v>101</v>
+      </c>
+      <c r="AD1">
+        <v>101</v>
+      </c>
+      <c r="AE1">
+        <v>101</v>
+      </c>
+      <c r="AF1">
+        <v>101</v>
+      </c>
+      <c r="AG1">
+        <v>101</v>
+      </c>
+      <c r="AH1">
+        <v>101</v>
+      </c>
+      <c r="AI1">
+        <v>101</v>
+      </c>
+      <c r="AJ1">
+        <v>101</v>
+      </c>
+      <c r="AK1">
+        <v>100</v>
+      </c>
+      <c r="AL1">
+        <v>100</v>
+      </c>
+      <c r="AM1">
+        <v>101</v>
+      </c>
+      <c r="AN1">
+        <v>101</v>
+      </c>
+      <c r="AO1">
+        <v>101</v>
+      </c>
+      <c r="AP1">
+        <v>101</v>
+      </c>
+      <c r="AQ1">
+        <v>101</v>
+      </c>
+      <c r="AR1">
+        <v>101</v>
+      </c>
+      <c r="AS1">
+        <v>101</v>
+      </c>
+      <c r="AT1">
+        <v>101</v>
+      </c>
+      <c r="AU1">
+        <v>101</v>
+      </c>
+      <c r="AV1">
+        <v>101</v>
+      </c>
+      <c r="AW1">
+        <v>101</v>
+      </c>
+      <c r="AX1">
+        <v>101</v>
+      </c>
+      <c r="AY1">
+        <v>101</v>
+      </c>
+      <c r="AZ1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>102</v>
+      </c>
+      <c r="B2">
+        <v>102</v>
+      </c>
+      <c r="C2">
+        <v>102</v>
+      </c>
+      <c r="D2">
+        <v>102</v>
+      </c>
+      <c r="E2">
+        <v>102</v>
+      </c>
+      <c r="F2">
+        <v>102</v>
+      </c>
+      <c r="G2">
+        <v>102</v>
+      </c>
+      <c r="H2">
+        <v>102</v>
+      </c>
+      <c r="I2">
+        <v>102</v>
+      </c>
+      <c r="J2">
+        <v>102</v>
+      </c>
+      <c r="K2">
+        <v>102</v>
+      </c>
+      <c r="L2">
+        <v>102</v>
+      </c>
+      <c r="M2">
+        <v>102</v>
+      </c>
+      <c r="N2">
+        <v>102</v>
+      </c>
+      <c r="O2">
+        <v>100</v>
+      </c>
+      <c r="P2">
+        <v>100</v>
+      </c>
+      <c r="Q2">
+        <v>102</v>
+      </c>
+      <c r="R2">
+        <v>102</v>
+      </c>
+      <c r="S2">
+        <v>102</v>
+      </c>
+      <c r="T2">
+        <v>102</v>
+      </c>
+      <c r="U2">
+        <v>102</v>
+      </c>
+      <c r="V2">
+        <v>102</v>
+      </c>
+      <c r="W2">
+        <v>102</v>
+      </c>
+      <c r="X2">
+        <v>102</v>
+      </c>
+      <c r="Y2">
+        <v>102</v>
+      </c>
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>100</v>
+      </c>
+      <c r="AC2">
+        <v>101</v>
+      </c>
+      <c r="AD2">
+        <v>101</v>
+      </c>
+      <c r="AE2">
+        <v>101</v>
+      </c>
+      <c r="AF2">
+        <v>101</v>
+      </c>
+      <c r="AG2">
+        <v>101</v>
+      </c>
+      <c r="AH2">
+        <v>101</v>
+      </c>
+      <c r="AI2">
+        <v>101</v>
+      </c>
+      <c r="AJ2">
+        <v>101</v>
+      </c>
+      <c r="AK2">
+        <v>100</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>101</v>
+      </c>
+      <c r="AN2">
+        <v>101</v>
+      </c>
+      <c r="AO2">
+        <v>101</v>
+      </c>
+      <c r="AP2">
+        <v>101</v>
+      </c>
+      <c r="AQ2">
+        <v>101</v>
+      </c>
+      <c r="AR2">
+        <v>101</v>
+      </c>
+      <c r="AS2">
+        <v>101</v>
+      </c>
+      <c r="AT2">
+        <v>101</v>
+      </c>
+      <c r="AU2">
+        <v>101</v>
+      </c>
+      <c r="AV2">
+        <v>101</v>
+      </c>
+      <c r="AW2">
+        <v>101</v>
+      </c>
+      <c r="AX2">
+        <v>101</v>
+      </c>
+      <c r="AY2">
+        <v>101</v>
+      </c>
+      <c r="AZ2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3">
+        <v>102</v>
+      </c>
+      <c r="D3">
+        <v>102</v>
+      </c>
+      <c r="E3">
+        <v>102</v>
+      </c>
+      <c r="F3">
+        <v>102</v>
+      </c>
+      <c r="G3">
+        <v>102</v>
+      </c>
+      <c r="H3">
+        <v>102</v>
+      </c>
+      <c r="I3">
+        <v>102</v>
+      </c>
+      <c r="J3">
+        <v>102</v>
+      </c>
+      <c r="K3">
+        <v>102</v>
+      </c>
+      <c r="L3">
+        <v>102</v>
+      </c>
+      <c r="M3">
+        <v>102</v>
+      </c>
+      <c r="N3">
+        <v>102</v>
+      </c>
+      <c r="O3">
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
+      </c>
+      <c r="Q3">
+        <v>102</v>
+      </c>
+      <c r="R3">
+        <v>102</v>
+      </c>
+      <c r="S3">
+        <v>102</v>
+      </c>
+      <c r="T3">
+        <v>102</v>
+      </c>
+      <c r="U3">
+        <v>102</v>
+      </c>
+      <c r="V3">
+        <v>102</v>
+      </c>
+      <c r="W3">
+        <v>102</v>
+      </c>
+      <c r="X3">
+        <v>102</v>
+      </c>
+      <c r="Y3">
+        <v>102</v>
+      </c>
+      <c r="Z3">
+        <v>100</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>100</v>
+      </c>
+      <c r="AC3">
+        <v>101</v>
+      </c>
+      <c r="AD3">
+        <v>101</v>
+      </c>
+      <c r="AE3">
+        <v>101</v>
+      </c>
+      <c r="AF3">
+        <v>101</v>
+      </c>
+      <c r="AG3">
+        <v>101</v>
+      </c>
+      <c r="AH3">
+        <v>101</v>
+      </c>
+      <c r="AI3">
+        <v>101</v>
+      </c>
+      <c r="AJ3">
+        <v>101</v>
+      </c>
+      <c r="AK3">
+        <v>100</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>101</v>
+      </c>
+      <c r="AN3">
+        <v>101</v>
+      </c>
+      <c r="AO3">
+        <v>101</v>
+      </c>
+      <c r="AP3">
+        <v>101</v>
+      </c>
+      <c r="AQ3">
+        <v>101</v>
+      </c>
+      <c r="AR3">
+        <v>101</v>
+      </c>
+      <c r="AS3">
+        <v>101</v>
+      </c>
+      <c r="AT3">
+        <v>101</v>
+      </c>
+      <c r="AU3">
+        <v>101</v>
+      </c>
+      <c r="AV3">
+        <v>101</v>
+      </c>
+      <c r="AW3">
+        <v>101</v>
+      </c>
+      <c r="AX3">
+        <v>101</v>
+      </c>
+      <c r="AY3">
+        <v>101</v>
+      </c>
+      <c r="AZ3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>102</v>
+      </c>
+      <c r="B4">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>102</v>
+      </c>
+      <c r="D4">
+        <v>102</v>
+      </c>
+      <c r="E4">
+        <v>102</v>
+      </c>
+      <c r="F4">
+        <v>102</v>
+      </c>
+      <c r="G4">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>102</v>
+      </c>
+      <c r="I4">
+        <v>102</v>
+      </c>
+      <c r="J4">
+        <v>102</v>
+      </c>
+      <c r="K4">
+        <v>102</v>
+      </c>
+      <c r="L4">
+        <v>102</v>
+      </c>
+      <c r="M4">
+        <v>102</v>
+      </c>
+      <c r="N4">
+        <v>102</v>
+      </c>
+      <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>102</v>
+      </c>
+      <c r="R4">
+        <v>102</v>
+      </c>
+      <c r="S4">
+        <v>102</v>
+      </c>
+      <c r="T4">
+        <v>102</v>
+      </c>
+      <c r="U4">
+        <v>102</v>
+      </c>
+      <c r="V4">
+        <v>102</v>
+      </c>
+      <c r="W4">
+        <v>102</v>
+      </c>
+      <c r="X4">
+        <v>102</v>
+      </c>
+      <c r="Y4">
+        <v>102</v>
+      </c>
+      <c r="Z4">
+        <v>100</v>
+      </c>
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AB4">
+        <v>100</v>
+      </c>
+      <c r="AC4">
+        <v>101</v>
+      </c>
+      <c r="AD4">
+        <v>101</v>
+      </c>
+      <c r="AE4">
+        <v>101</v>
+      </c>
+      <c r="AF4">
+        <v>101</v>
+      </c>
+      <c r="AG4">
+        <v>101</v>
+      </c>
+      <c r="AH4">
+        <v>101</v>
+      </c>
+      <c r="AI4">
+        <v>101</v>
+      </c>
+      <c r="AJ4">
+        <v>101</v>
+      </c>
+      <c r="AK4">
+        <v>100</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>101</v>
+      </c>
+      <c r="AN4">
+        <v>101</v>
+      </c>
+      <c r="AO4">
+        <v>101</v>
+      </c>
+      <c r="AP4">
+        <v>101</v>
+      </c>
+      <c r="AQ4">
+        <v>101</v>
+      </c>
+      <c r="AR4">
+        <v>101</v>
+      </c>
+      <c r="AS4">
+        <v>101</v>
+      </c>
+      <c r="AT4">
+        <v>101</v>
+      </c>
+      <c r="AU4">
+        <v>101</v>
+      </c>
+      <c r="AV4">
+        <v>101</v>
+      </c>
+      <c r="AW4">
+        <v>101</v>
+      </c>
+      <c r="AX4">
+        <v>101</v>
+      </c>
+      <c r="AY4">
+        <v>101</v>
+      </c>
+      <c r="AZ4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>102</v>
+      </c>
+      <c r="M5">
+        <v>102</v>
+      </c>
+      <c r="N5">
+        <v>102</v>
+      </c>
+      <c r="O5">
+        <v>102</v>
+      </c>
+      <c r="P5">
+        <v>102</v>
+      </c>
+      <c r="Q5">
+        <v>102</v>
+      </c>
+      <c r="R5">
+        <v>102</v>
+      </c>
+      <c r="S5">
+        <v>102</v>
+      </c>
+      <c r="T5">
+        <v>102</v>
+      </c>
+      <c r="U5">
+        <v>102</v>
+      </c>
+      <c r="V5">
+        <v>102</v>
+      </c>
+      <c r="W5">
+        <v>102</v>
+      </c>
+      <c r="X5">
+        <v>102</v>
+      </c>
+      <c r="Y5">
+        <v>102</v>
+      </c>
+      <c r="Z5">
+        <v>102</v>
+      </c>
+      <c r="AA5">
+        <v>102</v>
+      </c>
+      <c r="AB5">
+        <v>102</v>
+      </c>
+      <c r="AC5">
+        <v>102</v>
+      </c>
+      <c r="AD5">
+        <v>102</v>
+      </c>
+      <c r="AE5">
+        <v>102</v>
+      </c>
+      <c r="AF5">
+        <v>102</v>
+      </c>
+      <c r="AG5">
+        <v>102</v>
+      </c>
+      <c r="AH5">
+        <v>102</v>
+      </c>
+      <c r="AI5">
+        <v>102</v>
+      </c>
+      <c r="AJ5">
+        <v>102</v>
+      </c>
+      <c r="AK5">
+        <v>102</v>
+      </c>
+      <c r="AL5">
+        <v>102</v>
+      </c>
+      <c r="AM5">
+        <v>102</v>
+      </c>
+      <c r="AN5">
+        <v>102</v>
+      </c>
+      <c r="AO5">
+        <v>100</v>
+      </c>
+      <c r="AP5">
+        <v>100</v>
+      </c>
+      <c r="AQ5">
+        <v>100</v>
+      </c>
+      <c r="AR5">
+        <v>100</v>
+      </c>
+      <c r="AS5">
+        <v>100</v>
+      </c>
+      <c r="AT5">
+        <v>100</v>
+      </c>
+      <c r="AU5">
+        <v>100</v>
+      </c>
+      <c r="AV5">
+        <v>100</v>
+      </c>
+      <c r="AW5">
+        <v>100</v>
+      </c>
+      <c r="AX5">
+        <v>100</v>
+      </c>
+      <c r="AY5">
+        <v>100</v>
+      </c>
+      <c r="AZ5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>102</v>
+      </c>
+      <c r="M6">
+        <v>102</v>
+      </c>
+      <c r="N6">
+        <v>102</v>
+      </c>
+      <c r="O6">
+        <v>102</v>
+      </c>
+      <c r="P6">
+        <v>102</v>
+      </c>
+      <c r="Q6">
+        <v>102</v>
+      </c>
+      <c r="R6">
+        <v>102</v>
+      </c>
+      <c r="S6">
+        <v>102</v>
+      </c>
+      <c r="T6">
+        <v>102</v>
+      </c>
+      <c r="U6">
+        <v>102</v>
+      </c>
+      <c r="V6">
+        <v>102</v>
+      </c>
+      <c r="W6">
+        <v>102</v>
+      </c>
+      <c r="X6">
+        <v>102</v>
+      </c>
+      <c r="Y6">
+        <v>102</v>
+      </c>
+      <c r="Z6">
+        <v>102</v>
+      </c>
+      <c r="AA6">
+        <v>102</v>
+      </c>
+      <c r="AB6">
+        <v>102</v>
+      </c>
+      <c r="AC6">
+        <v>102</v>
+      </c>
+      <c r="AD6">
+        <v>102</v>
+      </c>
+      <c r="AE6">
+        <v>102</v>
+      </c>
+      <c r="AF6">
+        <v>102</v>
+      </c>
+      <c r="AG6">
+        <v>102</v>
+      </c>
+      <c r="AH6">
+        <v>102</v>
+      </c>
+      <c r="AI6">
+        <v>102</v>
+      </c>
+      <c r="AJ6">
+        <v>102</v>
+      </c>
+      <c r="AK6">
+        <v>102</v>
+      </c>
+      <c r="AL6">
+        <v>102</v>
+      </c>
+      <c r="AM6">
+        <v>102</v>
+      </c>
+      <c r="AN6">
+        <v>102</v>
+      </c>
+      <c r="AO6">
+        <v>100</v>
+      </c>
+      <c r="AP6">
+        <v>100</v>
+      </c>
+      <c r="AQ6">
+        <v>100</v>
+      </c>
+      <c r="AR6">
+        <v>100</v>
+      </c>
+      <c r="AS6">
+        <v>100</v>
+      </c>
+      <c r="AT6">
+        <v>100</v>
+      </c>
+      <c r="AU6">
+        <v>100</v>
+      </c>
+      <c r="AV6">
+        <v>100</v>
+      </c>
+      <c r="AW6">
+        <v>100</v>
+      </c>
+      <c r="AX6">
+        <v>100</v>
+      </c>
+      <c r="AY6">
+        <v>100</v>
+      </c>
+      <c r="AZ6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>102</v>
+      </c>
+      <c r="B7">
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>102</v>
+      </c>
+      <c r="D7">
+        <v>102</v>
+      </c>
+      <c r="E7">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>102</v>
+      </c>
+      <c r="G7">
+        <v>102</v>
+      </c>
+      <c r="H7">
+        <v>102</v>
+      </c>
+      <c r="I7">
+        <v>102</v>
+      </c>
+      <c r="J7">
+        <v>102</v>
+      </c>
+      <c r="K7">
+        <v>102</v>
+      </c>
+      <c r="L7">
+        <v>102</v>
+      </c>
+      <c r="M7">
+        <v>102</v>
+      </c>
+      <c r="N7">
+        <v>102</v>
+      </c>
+      <c r="O7">
+        <v>102</v>
+      </c>
+      <c r="P7">
+        <v>102</v>
+      </c>
+      <c r="Q7">
+        <v>102</v>
+      </c>
+      <c r="R7">
+        <v>102</v>
+      </c>
+      <c r="S7">
+        <v>102</v>
+      </c>
+      <c r="T7">
+        <v>102</v>
+      </c>
+      <c r="U7">
+        <v>102</v>
+      </c>
+      <c r="V7">
+        <v>102</v>
+      </c>
+      <c r="W7">
+        <v>102</v>
+      </c>
+      <c r="X7">
+        <v>102</v>
+      </c>
+      <c r="Y7">
+        <v>102</v>
+      </c>
+      <c r="Z7">
+        <v>102</v>
+      </c>
+      <c r="AA7">
+        <v>102</v>
+      </c>
+      <c r="AB7">
+        <v>102</v>
+      </c>
+      <c r="AC7">
+        <v>102</v>
+      </c>
+      <c r="AD7">
+        <v>102</v>
+      </c>
+      <c r="AE7">
+        <v>102</v>
+      </c>
+      <c r="AF7">
+        <v>102</v>
+      </c>
+      <c r="AG7">
+        <v>102</v>
+      </c>
+      <c r="AH7">
+        <v>102</v>
+      </c>
+      <c r="AI7">
+        <v>102</v>
+      </c>
+      <c r="AJ7">
+        <v>102</v>
+      </c>
+      <c r="AK7">
+        <v>102</v>
+      </c>
+      <c r="AL7">
+        <v>102</v>
+      </c>
+      <c r="AM7">
+        <v>102</v>
+      </c>
+      <c r="AN7">
+        <v>102</v>
+      </c>
+      <c r="AO7">
+        <v>101</v>
+      </c>
+      <c r="AP7">
+        <v>101</v>
+      </c>
+      <c r="AQ7">
+        <v>101</v>
+      </c>
+      <c r="AR7">
+        <v>101</v>
+      </c>
+      <c r="AS7">
+        <v>101</v>
+      </c>
+      <c r="AT7">
+        <v>101</v>
+      </c>
+      <c r="AU7">
+        <v>101</v>
+      </c>
+      <c r="AV7">
+        <v>101</v>
+      </c>
+      <c r="AW7">
+        <v>101</v>
+      </c>
+      <c r="AX7">
+        <v>101</v>
+      </c>
+      <c r="AY7">
+        <v>101</v>
+      </c>
+      <c r="AZ7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>102</v>
+      </c>
+      <c r="B8">
+        <v>102</v>
+      </c>
+      <c r="C8">
+        <v>102</v>
+      </c>
+      <c r="D8">
+        <v>102</v>
+      </c>
+      <c r="E8">
+        <v>102</v>
+      </c>
+      <c r="F8">
+        <v>102</v>
+      </c>
+      <c r="G8">
+        <v>102</v>
+      </c>
+      <c r="H8">
+        <v>102</v>
+      </c>
+      <c r="I8">
+        <v>102</v>
+      </c>
+      <c r="J8">
+        <v>102</v>
+      </c>
+      <c r="K8">
+        <v>102</v>
+      </c>
+      <c r="L8">
+        <v>102</v>
+      </c>
+      <c r="M8">
+        <v>102</v>
+      </c>
+      <c r="N8">
+        <v>102</v>
+      </c>
+      <c r="O8">
+        <v>102</v>
+      </c>
+      <c r="P8">
+        <v>102</v>
+      </c>
+      <c r="Q8">
+        <v>102</v>
+      </c>
+      <c r="R8">
+        <v>102</v>
+      </c>
+      <c r="S8">
+        <v>102</v>
+      </c>
+      <c r="T8">
+        <v>102</v>
+      </c>
+      <c r="U8">
+        <v>102</v>
+      </c>
+      <c r="V8">
+        <v>102</v>
+      </c>
+      <c r="W8">
+        <v>102</v>
+      </c>
+      <c r="X8">
+        <v>102</v>
+      </c>
+      <c r="Y8">
+        <v>102</v>
+      </c>
+      <c r="Z8">
+        <v>102</v>
+      </c>
+      <c r="AA8">
+        <v>102</v>
+      </c>
+      <c r="AB8">
+        <v>102</v>
+      </c>
+      <c r="AC8">
+        <v>102</v>
+      </c>
+      <c r="AD8">
+        <v>102</v>
+      </c>
+      <c r="AE8">
+        <v>102</v>
+      </c>
+      <c r="AF8">
+        <v>102</v>
+      </c>
+      <c r="AG8">
+        <v>102</v>
+      </c>
+      <c r="AH8">
+        <v>102</v>
+      </c>
+      <c r="AI8">
+        <v>102</v>
+      </c>
+      <c r="AJ8">
+        <v>102</v>
+      </c>
+      <c r="AK8">
+        <v>102</v>
+      </c>
+      <c r="AL8">
+        <v>102</v>
+      </c>
+      <c r="AM8">
+        <v>102</v>
+      </c>
+      <c r="AN8">
+        <v>102</v>
+      </c>
+      <c r="AO8">
+        <v>101</v>
+      </c>
+      <c r="AP8">
+        <v>101</v>
+      </c>
+      <c r="AQ8">
+        <v>101</v>
+      </c>
+      <c r="AR8">
+        <v>101</v>
+      </c>
+      <c r="AS8">
+        <v>101</v>
+      </c>
+      <c r="AT8">
+        <v>101</v>
+      </c>
+      <c r="AU8">
+        <v>101</v>
+      </c>
+      <c r="AV8">
+        <v>101</v>
+      </c>
+      <c r="AW8">
+        <v>101</v>
+      </c>
+      <c r="AX8">
+        <v>101</v>
+      </c>
+      <c r="AY8">
+        <v>101</v>
+      </c>
+      <c r="AZ8">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>102</v>
+      </c>
+      <c r="B9">
+        <v>102</v>
+      </c>
+      <c r="C9">
+        <v>102</v>
+      </c>
+      <c r="D9">
+        <v>102</v>
+      </c>
+      <c r="E9">
+        <v>102</v>
+      </c>
+      <c r="F9">
+        <v>102</v>
+      </c>
+      <c r="G9">
+        <v>102</v>
+      </c>
+      <c r="H9">
+        <v>102</v>
+      </c>
+      <c r="I9">
+        <v>102</v>
+      </c>
+      <c r="J9">
+        <v>102</v>
+      </c>
+      <c r="K9">
+        <v>102</v>
+      </c>
+      <c r="L9">
+        <v>102</v>
+      </c>
+      <c r="M9">
+        <v>102</v>
+      </c>
+      <c r="N9">
+        <v>102</v>
+      </c>
+      <c r="O9">
+        <v>102</v>
+      </c>
+      <c r="P9">
+        <v>102</v>
+      </c>
+      <c r="Q9">
+        <v>102</v>
+      </c>
+      <c r="R9">
+        <v>102</v>
+      </c>
+      <c r="S9">
+        <v>102</v>
+      </c>
+      <c r="T9">
+        <v>102</v>
+      </c>
+      <c r="U9">
+        <v>102</v>
+      </c>
+      <c r="V9">
+        <v>102</v>
+      </c>
+      <c r="W9">
+        <v>102</v>
+      </c>
+      <c r="X9">
+        <v>102</v>
+      </c>
+      <c r="Y9">
+        <v>102</v>
+      </c>
+      <c r="Z9">
+        <v>102</v>
+      </c>
+      <c r="AA9">
+        <v>102</v>
+      </c>
+      <c r="AB9">
+        <v>102</v>
+      </c>
+      <c r="AC9">
+        <v>102</v>
+      </c>
+      <c r="AD9">
+        <v>102</v>
+      </c>
+      <c r="AE9">
+        <v>102</v>
+      </c>
+      <c r="AF9">
+        <v>102</v>
+      </c>
+      <c r="AG9">
+        <v>102</v>
+      </c>
+      <c r="AH9">
+        <v>102</v>
+      </c>
+      <c r="AI9">
+        <v>102</v>
+      </c>
+      <c r="AJ9">
+        <v>102</v>
+      </c>
+      <c r="AK9">
+        <v>102</v>
+      </c>
+      <c r="AL9">
+        <v>102</v>
+      </c>
+      <c r="AM9">
+        <v>102</v>
+      </c>
+      <c r="AN9">
+        <v>102</v>
+      </c>
+      <c r="AO9">
+        <v>101</v>
+      </c>
+      <c r="AP9">
+        <v>101</v>
+      </c>
+      <c r="AQ9">
+        <v>101</v>
+      </c>
+      <c r="AR9">
+        <v>101</v>
+      </c>
+      <c r="AS9">
+        <v>101</v>
+      </c>
+      <c r="AT9">
+        <v>101</v>
+      </c>
+      <c r="AU9">
+        <v>101</v>
+      </c>
+      <c r="AV9">
+        <v>101</v>
+      </c>
+      <c r="AW9">
+        <v>101</v>
+      </c>
+      <c r="AX9">
+        <v>101</v>
+      </c>
+      <c r="AY9">
+        <v>101</v>
+      </c>
+      <c r="AZ9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>102</v>
+      </c>
+      <c r="B10">
+        <v>102</v>
+      </c>
+      <c r="C10">
+        <v>102</v>
+      </c>
+      <c r="D10">
+        <v>102</v>
+      </c>
+      <c r="E10">
+        <v>102</v>
+      </c>
+      <c r="F10">
+        <v>102</v>
+      </c>
+      <c r="G10">
+        <v>102</v>
+      </c>
+      <c r="H10">
+        <v>102</v>
+      </c>
+      <c r="I10">
+        <v>102</v>
+      </c>
+      <c r="J10">
+        <v>102</v>
+      </c>
+      <c r="K10">
+        <v>102</v>
+      </c>
+      <c r="L10">
+        <v>102</v>
+      </c>
+      <c r="M10">
+        <v>102</v>
+      </c>
+      <c r="N10">
+        <v>102</v>
+      </c>
+      <c r="O10">
+        <v>102</v>
+      </c>
+      <c r="P10">
+        <v>102</v>
+      </c>
+      <c r="Q10">
+        <v>102</v>
+      </c>
+      <c r="R10">
+        <v>102</v>
+      </c>
+      <c r="S10">
+        <v>102</v>
+      </c>
+      <c r="T10">
+        <v>102</v>
+      </c>
+      <c r="U10">
+        <v>102</v>
+      </c>
+      <c r="V10">
+        <v>102</v>
+      </c>
+      <c r="W10">
+        <v>102</v>
+      </c>
+      <c r="X10">
+        <v>102</v>
+      </c>
+      <c r="Y10">
+        <v>102</v>
+      </c>
+      <c r="Z10">
+        <v>102</v>
+      </c>
+      <c r="AA10">
+        <v>102</v>
+      </c>
+      <c r="AB10">
+        <v>102</v>
+      </c>
+      <c r="AC10">
+        <v>102</v>
+      </c>
+      <c r="AD10">
+        <v>102</v>
+      </c>
+      <c r="AE10">
+        <v>102</v>
+      </c>
+      <c r="AF10">
+        <v>102</v>
+      </c>
+      <c r="AG10">
+        <v>102</v>
+      </c>
+      <c r="AH10">
+        <v>102</v>
+      </c>
+      <c r="AI10">
+        <v>102</v>
+      </c>
+      <c r="AJ10">
+        <v>102</v>
+      </c>
+      <c r="AK10">
+        <v>102</v>
+      </c>
+      <c r="AL10">
+        <v>102</v>
+      </c>
+      <c r="AM10">
+        <v>102</v>
+      </c>
+      <c r="AN10">
+        <v>102</v>
+      </c>
+      <c r="AO10">
+        <v>101</v>
+      </c>
+      <c r="AP10">
+        <v>101</v>
+      </c>
+      <c r="AQ10">
+        <v>101</v>
+      </c>
+      <c r="AR10">
+        <v>101</v>
+      </c>
+      <c r="AS10">
+        <v>101</v>
+      </c>
+      <c r="AT10">
+        <v>101</v>
+      </c>
+      <c r="AU10">
+        <v>101</v>
+      </c>
+      <c r="AV10">
+        <v>101</v>
+      </c>
+      <c r="AW10">
+        <v>101</v>
+      </c>
+      <c r="AX10">
+        <v>101</v>
+      </c>
+      <c r="AY10">
+        <v>101</v>
+      </c>
+      <c r="AZ10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>102</v>
+      </c>
+      <c r="B11">
+        <v>102</v>
+      </c>
+      <c r="C11">
+        <v>102</v>
+      </c>
+      <c r="D11">
+        <v>102</v>
+      </c>
+      <c r="E11">
+        <v>102</v>
+      </c>
+      <c r="F11">
+        <v>102</v>
+      </c>
+      <c r="G11">
+        <v>102</v>
+      </c>
+      <c r="H11">
+        <v>102</v>
+      </c>
+      <c r="I11">
+        <v>102</v>
+      </c>
+      <c r="J11">
+        <v>102</v>
+      </c>
+      <c r="K11">
+        <v>102</v>
+      </c>
+      <c r="L11">
+        <v>102</v>
+      </c>
+      <c r="M11">
+        <v>102</v>
+      </c>
+      <c r="N11">
+        <v>102</v>
+      </c>
+      <c r="O11">
+        <v>102</v>
+      </c>
+      <c r="P11">
+        <v>102</v>
+      </c>
+      <c r="Q11">
+        <v>102</v>
+      </c>
+      <c r="R11">
+        <v>102</v>
+      </c>
+      <c r="S11">
+        <v>102</v>
+      </c>
+      <c r="T11">
+        <v>102</v>
+      </c>
+      <c r="U11">
+        <v>102</v>
+      </c>
+      <c r="V11">
+        <v>102</v>
+      </c>
+      <c r="W11">
+        <v>102</v>
+      </c>
+      <c r="X11">
+        <v>102</v>
+      </c>
+      <c r="Y11">
+        <v>102</v>
+      </c>
+      <c r="Z11">
+        <v>102</v>
+      </c>
+      <c r="AA11">
+        <v>102</v>
+      </c>
+      <c r="AB11">
+        <v>102</v>
+      </c>
+      <c r="AC11">
+        <v>102</v>
+      </c>
+      <c r="AD11">
+        <v>102</v>
+      </c>
+      <c r="AE11">
+        <v>102</v>
+      </c>
+      <c r="AF11">
+        <v>102</v>
+      </c>
+      <c r="AG11">
+        <v>102</v>
+      </c>
+      <c r="AH11">
+        <v>102</v>
+      </c>
+      <c r="AI11">
+        <v>102</v>
+      </c>
+      <c r="AJ11">
+        <v>102</v>
+      </c>
+      <c r="AK11">
+        <v>102</v>
+      </c>
+      <c r="AL11">
+        <v>102</v>
+      </c>
+      <c r="AM11">
+        <v>102</v>
+      </c>
+      <c r="AN11">
+        <v>102</v>
+      </c>
+      <c r="AO11">
+        <v>101</v>
+      </c>
+      <c r="AP11">
+        <v>101</v>
+      </c>
+      <c r="AQ11">
+        <v>101</v>
+      </c>
+      <c r="AR11">
+        <v>101</v>
+      </c>
+      <c r="AS11">
+        <v>101</v>
+      </c>
+      <c r="AT11">
+        <v>101</v>
+      </c>
+      <c r="AU11">
+        <v>101</v>
+      </c>
+      <c r="AV11">
+        <v>101</v>
+      </c>
+      <c r="AW11">
+        <v>101</v>
+      </c>
+      <c r="AX11">
+        <v>101</v>
+      </c>
+      <c r="AY11">
+        <v>101</v>
+      </c>
+      <c r="AZ11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>102</v>
+      </c>
+      <c r="B12">
+        <v>102</v>
+      </c>
+      <c r="C12">
+        <v>102</v>
+      </c>
+      <c r="D12">
+        <v>102</v>
+      </c>
+      <c r="E12">
+        <v>102</v>
+      </c>
+      <c r="F12">
+        <v>102</v>
+      </c>
+      <c r="G12">
+        <v>102</v>
+      </c>
+      <c r="H12">
+        <v>102</v>
+      </c>
+      <c r="I12">
+        <v>102</v>
+      </c>
+      <c r="J12">
+        <v>102</v>
+      </c>
+      <c r="K12">
+        <v>102</v>
+      </c>
+      <c r="L12">
+        <v>102</v>
+      </c>
+      <c r="M12">
+        <v>102</v>
+      </c>
+      <c r="N12">
+        <v>102</v>
+      </c>
+      <c r="O12">
+        <v>102</v>
+      </c>
+      <c r="P12">
+        <v>102</v>
+      </c>
+      <c r="Q12">
+        <v>102</v>
+      </c>
+      <c r="R12">
+        <v>102</v>
+      </c>
+      <c r="S12">
+        <v>102</v>
+      </c>
+      <c r="T12">
+        <v>102</v>
+      </c>
+      <c r="U12">
+        <v>102</v>
+      </c>
+      <c r="V12">
+        <v>102</v>
+      </c>
+      <c r="W12">
+        <v>102</v>
+      </c>
+      <c r="X12">
+        <v>102</v>
+      </c>
+      <c r="Y12">
+        <v>102</v>
+      </c>
+      <c r="Z12">
+        <v>102</v>
+      </c>
+      <c r="AA12">
+        <v>102</v>
+      </c>
+      <c r="AB12">
+        <v>102</v>
+      </c>
+      <c r="AC12">
+        <v>102</v>
+      </c>
+      <c r="AD12">
+        <v>102</v>
+      </c>
+      <c r="AE12">
+        <v>102</v>
+      </c>
+      <c r="AF12">
+        <v>102</v>
+      </c>
+      <c r="AG12">
+        <v>102</v>
+      </c>
+      <c r="AH12">
+        <v>102</v>
+      </c>
+      <c r="AI12">
+        <v>102</v>
+      </c>
+      <c r="AJ12">
+        <v>102</v>
+      </c>
+      <c r="AK12">
+        <v>102</v>
+      </c>
+      <c r="AL12">
+        <v>102</v>
+      </c>
+      <c r="AM12">
+        <v>102</v>
+      </c>
+      <c r="AN12">
+        <v>102</v>
+      </c>
+      <c r="AO12">
+        <v>101</v>
+      </c>
+      <c r="AP12">
+        <v>101</v>
+      </c>
+      <c r="AQ12">
+        <v>101</v>
+      </c>
+      <c r="AR12">
+        <v>101</v>
+      </c>
+      <c r="AS12">
+        <v>101</v>
+      </c>
+      <c r="AT12">
+        <v>101</v>
+      </c>
+      <c r="AU12">
+        <v>101</v>
+      </c>
+      <c r="AV12">
+        <v>101</v>
+      </c>
+      <c r="AW12">
+        <v>101</v>
+      </c>
+      <c r="AX12">
+        <v>101</v>
+      </c>
+      <c r="AY12">
+        <v>101</v>
+      </c>
+      <c r="AZ12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>102</v>
+      </c>
+      <c r="B13">
+        <v>102</v>
+      </c>
+      <c r="C13">
+        <v>102</v>
+      </c>
+      <c r="D13">
+        <v>102</v>
+      </c>
+      <c r="E13">
+        <v>102</v>
+      </c>
+      <c r="F13">
+        <v>102</v>
+      </c>
+      <c r="G13">
+        <v>102</v>
+      </c>
+      <c r="H13">
+        <v>102</v>
+      </c>
+      <c r="I13">
+        <v>102</v>
+      </c>
+      <c r="J13">
+        <v>102</v>
+      </c>
+      <c r="K13">
+        <v>102</v>
+      </c>
+      <c r="L13">
+        <v>102</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>10</v>
+      </c>
+      <c r="P13">
+        <v>10</v>
+      </c>
+      <c r="Q13">
+        <v>10</v>
+      </c>
+      <c r="R13">
+        <v>10</v>
+      </c>
+      <c r="S13">
+        <v>10</v>
+      </c>
+      <c r="T13">
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <v>10</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13">
+        <v>10</v>
+      </c>
+      <c r="Y13">
+        <v>10</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
+        <v>10</v>
+      </c>
+      <c r="AE13">
+        <v>10</v>
+      </c>
+      <c r="AF13">
+        <v>10</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+      <c r="AH13">
+        <v>10</v>
+      </c>
+      <c r="AI13">
+        <v>10</v>
+      </c>
+      <c r="AJ13">
+        <v>10</v>
+      </c>
+      <c r="AK13">
+        <v>10</v>
+      </c>
+      <c r="AL13">
+        <v>10</v>
+      </c>
+      <c r="AM13">
+        <v>10</v>
+      </c>
+      <c r="AN13">
+        <v>10</v>
+      </c>
+      <c r="AO13">
+        <v>101</v>
+      </c>
+      <c r="AP13">
+        <v>101</v>
+      </c>
+      <c r="AQ13">
+        <v>101</v>
+      </c>
+      <c r="AR13">
+        <v>101</v>
+      </c>
+      <c r="AS13">
+        <v>101</v>
+      </c>
+      <c r="AT13">
+        <v>101</v>
+      </c>
+      <c r="AU13">
+        <v>101</v>
+      </c>
+      <c r="AV13">
+        <v>101</v>
+      </c>
+      <c r="AW13">
+        <v>101</v>
+      </c>
+      <c r="AX13">
+        <v>101</v>
+      </c>
+      <c r="AY13">
+        <v>101</v>
+      </c>
+      <c r="AZ13">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>102</v>
+      </c>
+      <c r="B14">
+        <v>102</v>
+      </c>
+      <c r="C14">
+        <v>102</v>
+      </c>
+      <c r="D14">
+        <v>102</v>
+      </c>
+      <c r="E14">
+        <v>102</v>
+      </c>
+      <c r="F14">
+        <v>102</v>
+      </c>
+      <c r="G14">
+        <v>102</v>
+      </c>
+      <c r="H14">
+        <v>102</v>
+      </c>
+      <c r="I14">
+        <v>102</v>
+      </c>
+      <c r="J14">
+        <v>102</v>
+      </c>
+      <c r="K14">
+        <v>102</v>
+      </c>
+      <c r="L14">
+        <v>102</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>20</v>
+      </c>
+      <c r="O14">
+        <v>20</v>
+      </c>
+      <c r="P14">
+        <v>20</v>
+      </c>
+      <c r="Q14">
+        <v>20</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>20</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>20</v>
+      </c>
+      <c r="Z14">
+        <v>20</v>
+      </c>
+      <c r="AA14">
+        <v>20</v>
+      </c>
+      <c r="AB14">
+        <v>20</v>
+      </c>
+      <c r="AC14">
+        <v>20</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>20</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>20</v>
+      </c>
+      <c r="AL14">
+        <v>20</v>
+      </c>
+      <c r="AM14">
+        <v>20</v>
+      </c>
+      <c r="AN14">
+        <v>10</v>
+      </c>
+      <c r="AO14">
+        <v>101</v>
+      </c>
+      <c r="AP14">
+        <v>101</v>
+      </c>
+      <c r="AQ14">
+        <v>101</v>
+      </c>
+      <c r="AR14">
+        <v>101</v>
+      </c>
+      <c r="AS14">
+        <v>101</v>
+      </c>
+      <c r="AT14">
+        <v>101</v>
+      </c>
+      <c r="AU14">
+        <v>101</v>
+      </c>
+      <c r="AV14">
+        <v>101</v>
+      </c>
+      <c r="AW14">
+        <v>101</v>
+      </c>
+      <c r="AX14">
+        <v>101</v>
+      </c>
+      <c r="AY14">
+        <v>101</v>
+      </c>
+      <c r="AZ14">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>102</v>
+      </c>
+      <c r="B15">
+        <v>102</v>
+      </c>
+      <c r="C15">
+        <v>102</v>
+      </c>
+      <c r="D15">
+        <v>102</v>
+      </c>
+      <c r="E15">
+        <v>102</v>
+      </c>
+      <c r="F15">
+        <v>102</v>
+      </c>
+      <c r="G15">
+        <v>102</v>
+      </c>
+      <c r="H15">
+        <v>102</v>
+      </c>
+      <c r="I15">
+        <v>102</v>
+      </c>
+      <c r="J15">
+        <v>102</v>
+      </c>
+      <c r="K15">
+        <v>102</v>
+      </c>
+      <c r="L15">
+        <v>102</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>20</v>
+      </c>
+      <c r="O15">
+        <v>10</v>
+      </c>
+      <c r="P15">
+        <v>20</v>
+      </c>
+      <c r="Q15">
+        <v>10</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>10</v>
+      </c>
+      <c r="T15">
+        <v>10</v>
+      </c>
+      <c r="U15">
+        <v>10</v>
+      </c>
+      <c r="V15">
+        <v>10</v>
+      </c>
+      <c r="W15">
+        <v>10</v>
+      </c>
+      <c r="X15">
+        <v>10</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>20</v>
+      </c>
+      <c r="AA15">
+        <v>20</v>
+      </c>
+      <c r="AB15">
+        <v>20</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>10</v>
+      </c>
+      <c r="AE15">
+        <v>10</v>
+      </c>
+      <c r="AF15">
+        <v>10</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+      <c r="AH15">
+        <v>10</v>
+      </c>
+      <c r="AI15">
+        <v>20</v>
+      </c>
+      <c r="AJ15">
+        <v>10</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>10</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>10</v>
+      </c>
+      <c r="AO15">
+        <v>101</v>
+      </c>
+      <c r="AP15">
+        <v>101</v>
+      </c>
+      <c r="AQ15">
+        <v>101</v>
+      </c>
+      <c r="AR15">
+        <v>101</v>
+      </c>
+      <c r="AS15">
+        <v>101</v>
+      </c>
+      <c r="AT15">
+        <v>101</v>
+      </c>
+      <c r="AU15">
+        <v>101</v>
+      </c>
+      <c r="AV15">
+        <v>101</v>
+      </c>
+      <c r="AW15">
+        <v>101</v>
+      </c>
+      <c r="AX15">
+        <v>101</v>
+      </c>
+      <c r="AY15">
+        <v>101</v>
+      </c>
+      <c r="AZ15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>102</v>
+      </c>
+      <c r="B16">
+        <v>102</v>
+      </c>
+      <c r="C16">
+        <v>102</v>
+      </c>
+      <c r="D16">
+        <v>102</v>
+      </c>
+      <c r="E16">
+        <v>102</v>
+      </c>
+      <c r="F16">
+        <v>102</v>
+      </c>
+      <c r="G16">
+        <v>102</v>
+      </c>
+      <c r="H16">
+        <v>102</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>20</v>
+      </c>
+      <c r="O16">
+        <v>80</v>
+      </c>
+      <c r="P16">
+        <v>80</v>
+      </c>
+      <c r="Q16">
+        <v>80</v>
+      </c>
+      <c r="R16">
+        <v>80</v>
+      </c>
+      <c r="S16">
+        <v>80</v>
+      </c>
+      <c r="T16">
+        <v>80</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>81</v>
+      </c>
+      <c r="Y16">
+        <v>81</v>
+      </c>
+      <c r="Z16">
+        <v>81</v>
+      </c>
+      <c r="AA16">
+        <v>81</v>
+      </c>
+      <c r="AB16">
+        <v>81</v>
+      </c>
+      <c r="AC16">
+        <v>81</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>82</v>
+      </c>
+      <c r="AH16">
+        <v>82</v>
+      </c>
+      <c r="AI16">
+        <v>82</v>
+      </c>
+      <c r="AJ16">
+        <v>82</v>
+      </c>
+      <c r="AK16">
+        <v>82</v>
+      </c>
+      <c r="AL16">
+        <v>82</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>10</v>
+      </c>
+      <c r="AO16">
+        <v>10</v>
+      </c>
+      <c r="AP16">
+        <v>10</v>
+      </c>
+      <c r="AQ16">
+        <v>10</v>
+      </c>
+      <c r="AR16">
+        <v>10</v>
+      </c>
+      <c r="AS16">
+        <v>101</v>
+      </c>
+      <c r="AT16">
+        <v>101</v>
+      </c>
+      <c r="AU16">
+        <v>101</v>
+      </c>
+      <c r="AV16">
+        <v>101</v>
+      </c>
+      <c r="AW16">
+        <v>101</v>
+      </c>
+      <c r="AX16">
+        <v>101</v>
+      </c>
+      <c r="AY16">
+        <v>101</v>
+      </c>
+      <c r="AZ16">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>102</v>
+      </c>
+      <c r="B17">
+        <v>102</v>
+      </c>
+      <c r="C17">
+        <v>102</v>
+      </c>
+      <c r="D17">
+        <v>102</v>
+      </c>
+      <c r="E17">
+        <v>102</v>
+      </c>
+      <c r="F17">
+        <v>102</v>
+      </c>
+      <c r="G17">
+        <v>102</v>
+      </c>
+      <c r="H17">
+        <v>102</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>99</v>
+      </c>
+      <c r="K17">
+        <v>99</v>
+      </c>
+      <c r="L17">
+        <v>99</v>
+      </c>
+      <c r="M17">
+        <v>95</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>80</v>
+      </c>
+      <c r="P17">
+        <v>80</v>
+      </c>
+      <c r="Q17">
+        <v>80</v>
+      </c>
+      <c r="R17">
+        <v>80</v>
+      </c>
+      <c r="S17">
+        <v>80</v>
+      </c>
+      <c r="T17">
+        <v>80</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>81</v>
+      </c>
+      <c r="Y17">
+        <v>81</v>
+      </c>
+      <c r="Z17">
+        <v>81</v>
+      </c>
+      <c r="AA17">
+        <v>81</v>
+      </c>
+      <c r="AB17">
+        <v>81</v>
+      </c>
+      <c r="AC17">
+        <v>81</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>82</v>
+      </c>
+      <c r="AH17">
+        <v>82</v>
+      </c>
+      <c r="AI17">
+        <v>82</v>
+      </c>
+      <c r="AJ17">
+        <v>82</v>
+      </c>
+      <c r="AK17">
+        <v>82</v>
+      </c>
+      <c r="AL17">
+        <v>82</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>95</v>
+      </c>
+      <c r="AO17">
+        <v>99</v>
+      </c>
+      <c r="AP17">
+        <v>99</v>
+      </c>
+      <c r="AQ17">
+        <v>99</v>
+      </c>
+      <c r="AR17">
+        <v>10</v>
+      </c>
+      <c r="AS17">
+        <v>101</v>
+      </c>
+      <c r="AT17">
+        <v>101</v>
+      </c>
+      <c r="AU17">
+        <v>101</v>
+      </c>
+      <c r="AV17">
+        <v>101</v>
+      </c>
+      <c r="AW17">
+        <v>101</v>
+      </c>
+      <c r="AX17">
+        <v>101</v>
+      </c>
+      <c r="AY17">
+        <v>101</v>
+      </c>
+      <c r="AZ17">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>102</v>
+      </c>
+      <c r="B18">
+        <v>102</v>
+      </c>
+      <c r="C18">
+        <v>102</v>
+      </c>
+      <c r="D18">
+        <v>102</v>
+      </c>
+      <c r="E18">
+        <v>102</v>
+      </c>
+      <c r="F18">
+        <v>102</v>
+      </c>
+      <c r="G18">
+        <v>102</v>
+      </c>
+      <c r="H18">
+        <v>102</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>99</v>
+      </c>
+      <c r="K18">
+        <v>93</v>
+      </c>
+      <c r="L18">
+        <v>99</v>
+      </c>
+      <c r="M18">
+        <v>95</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>80</v>
+      </c>
+      <c r="P18">
+        <v>80</v>
+      </c>
+      <c r="Q18">
+        <v>80</v>
+      </c>
+      <c r="R18">
+        <v>80</v>
+      </c>
+      <c r="S18">
+        <v>80</v>
+      </c>
+      <c r="T18">
+        <v>80</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>81</v>
+      </c>
+      <c r="Y18">
+        <v>81</v>
+      </c>
+      <c r="Z18">
+        <v>81</v>
+      </c>
+      <c r="AA18">
+        <v>81</v>
+      </c>
+      <c r="AB18">
+        <v>81</v>
+      </c>
+      <c r="AC18">
+        <v>81</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>82</v>
+      </c>
+      <c r="AH18">
+        <v>82</v>
+      </c>
+      <c r="AI18">
+        <v>82</v>
+      </c>
+      <c r="AJ18">
+        <v>82</v>
+      </c>
+      <c r="AK18">
+        <v>82</v>
+      </c>
+      <c r="AL18">
+        <v>82</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>95</v>
+      </c>
+      <c r="AO18">
+        <v>99</v>
+      </c>
+      <c r="AP18">
+        <v>91</v>
+      </c>
+      <c r="AQ18">
+        <v>99</v>
+      </c>
+      <c r="AR18">
+        <v>10</v>
+      </c>
+      <c r="AS18">
+        <v>101</v>
+      </c>
+      <c r="AT18">
+        <v>101</v>
+      </c>
+      <c r="AU18">
+        <v>101</v>
+      </c>
+      <c r="AV18">
+        <v>101</v>
+      </c>
+      <c r="AW18">
+        <v>101</v>
+      </c>
+      <c r="AX18">
+        <v>101</v>
+      </c>
+      <c r="AY18">
+        <v>101</v>
+      </c>
+      <c r="AZ18">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>102</v>
+      </c>
+      <c r="B19">
+        <v>102</v>
+      </c>
+      <c r="C19">
+        <v>102</v>
+      </c>
+      <c r="D19">
+        <v>102</v>
+      </c>
+      <c r="E19">
+        <v>102</v>
+      </c>
+      <c r="F19">
+        <v>102</v>
+      </c>
+      <c r="G19">
+        <v>102</v>
+      </c>
+      <c r="H19">
+        <v>102</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>99</v>
+      </c>
+      <c r="K19">
+        <v>99</v>
+      </c>
+      <c r="L19">
+        <v>99</v>
+      </c>
+      <c r="M19">
+        <v>95</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>80</v>
+      </c>
+      <c r="P19">
+        <v>80</v>
+      </c>
+      <c r="Q19">
+        <v>80</v>
+      </c>
+      <c r="R19">
+        <v>80</v>
+      </c>
+      <c r="S19">
+        <v>80</v>
+      </c>
+      <c r="T19">
+        <v>80</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>81</v>
+      </c>
+      <c r="Y19">
+        <v>81</v>
+      </c>
+      <c r="Z19">
+        <v>81</v>
+      </c>
+      <c r="AA19">
+        <v>81</v>
+      </c>
+      <c r="AB19">
+        <v>81</v>
+      </c>
+      <c r="AC19">
+        <v>81</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>82</v>
+      </c>
+      <c r="AH19">
+        <v>82</v>
+      </c>
+      <c r="AI19">
+        <v>82</v>
+      </c>
+      <c r="AJ19">
+        <v>82</v>
+      </c>
+      <c r="AK19">
+        <v>82</v>
+      </c>
+      <c r="AL19">
+        <v>82</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>95</v>
+      </c>
+      <c r="AO19">
+        <v>99</v>
+      </c>
+      <c r="AP19">
+        <v>99</v>
+      </c>
+      <c r="AQ19">
+        <v>99</v>
+      </c>
+      <c r="AR19">
+        <v>10</v>
+      </c>
+      <c r="AS19">
+        <v>101</v>
+      </c>
+      <c r="AT19">
+        <v>101</v>
+      </c>
+      <c r="AU19">
+        <v>101</v>
+      </c>
+      <c r="AV19">
+        <v>101</v>
+      </c>
+      <c r="AW19">
+        <v>101</v>
+      </c>
+      <c r="AX19">
+        <v>101</v>
+      </c>
+      <c r="AY19">
+        <v>101</v>
+      </c>
+      <c r="AZ19">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>102</v>
+      </c>
+      <c r="B20">
+        <v>102</v>
+      </c>
+      <c r="C20">
+        <v>102</v>
+      </c>
+      <c r="D20">
+        <v>102</v>
+      </c>
+      <c r="E20">
+        <v>102</v>
+      </c>
+      <c r="F20">
+        <v>102</v>
+      </c>
+      <c r="G20">
+        <v>102</v>
+      </c>
+      <c r="H20">
+        <v>102</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>99</v>
+      </c>
+      <c r="K20">
+        <v>94</v>
+      </c>
+      <c r="L20">
+        <v>99</v>
+      </c>
+      <c r="M20">
+        <v>95</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>80</v>
+      </c>
+      <c r="P20">
+        <v>80</v>
+      </c>
+      <c r="Q20">
+        <v>80</v>
+      </c>
+      <c r="R20">
+        <v>80</v>
+      </c>
+      <c r="S20">
+        <v>80</v>
+      </c>
+      <c r="T20">
+        <v>80</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>81</v>
+      </c>
+      <c r="Y20">
+        <v>81</v>
+      </c>
+      <c r="Z20">
+        <v>81</v>
+      </c>
+      <c r="AA20">
+        <v>81</v>
+      </c>
+      <c r="AB20">
+        <v>81</v>
+      </c>
+      <c r="AC20">
+        <v>81</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>82</v>
+      </c>
+      <c r="AH20">
+        <v>82</v>
+      </c>
+      <c r="AI20">
+        <v>82</v>
+      </c>
+      <c r="AJ20">
+        <v>82</v>
+      </c>
+      <c r="AK20">
+        <v>82</v>
+      </c>
+      <c r="AL20">
+        <v>82</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>95</v>
+      </c>
+      <c r="AO20">
+        <v>99</v>
+      </c>
+      <c r="AP20">
+        <v>92</v>
+      </c>
+      <c r="AQ20">
+        <v>99</v>
+      </c>
+      <c r="AR20">
+        <v>10</v>
+      </c>
+      <c r="AS20">
+        <v>101</v>
+      </c>
+      <c r="AT20">
+        <v>101</v>
+      </c>
+      <c r="AU20">
+        <v>101</v>
+      </c>
+      <c r="AV20">
+        <v>101</v>
+      </c>
+      <c r="AW20">
+        <v>101</v>
+      </c>
+      <c r="AX20">
+        <v>101</v>
+      </c>
+      <c r="AY20">
+        <v>101</v>
+      </c>
+      <c r="AZ20">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>102</v>
+      </c>
+      <c r="B21">
+        <v>102</v>
+      </c>
+      <c r="C21">
+        <v>102</v>
+      </c>
+      <c r="D21">
+        <v>102</v>
+      </c>
+      <c r="E21">
+        <v>102</v>
+      </c>
+      <c r="F21">
+        <v>102</v>
+      </c>
+      <c r="G21">
+        <v>102</v>
+      </c>
+      <c r="H21">
+        <v>102</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>99</v>
+      </c>
+      <c r="K21">
+        <v>99</v>
+      </c>
+      <c r="L21">
+        <v>99</v>
+      </c>
+      <c r="M21">
+        <v>95</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>80</v>
+      </c>
+      <c r="P21">
+        <v>80</v>
+      </c>
+      <c r="Q21">
+        <v>80</v>
+      </c>
+      <c r="R21">
+        <v>80</v>
+      </c>
+      <c r="S21">
+        <v>80</v>
+      </c>
+      <c r="T21">
+        <v>80</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>81</v>
+      </c>
+      <c r="Y21">
+        <v>81</v>
+      </c>
+      <c r="Z21">
+        <v>81</v>
+      </c>
+      <c r="AA21">
+        <v>81</v>
+      </c>
+      <c r="AB21">
+        <v>81</v>
+      </c>
+      <c r="AC21">
+        <v>81</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>82</v>
+      </c>
+      <c r="AH21">
+        <v>82</v>
+      </c>
+      <c r="AI21">
+        <v>82</v>
+      </c>
+      <c r="AJ21">
+        <v>82</v>
+      </c>
+      <c r="AK21">
+        <v>82</v>
+      </c>
+      <c r="AL21">
+        <v>82</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>95</v>
+      </c>
+      <c r="AO21">
+        <v>99</v>
+      </c>
+      <c r="AP21">
+        <v>99</v>
+      </c>
+      <c r="AQ21">
+        <v>99</v>
+      </c>
+      <c r="AR21">
+        <v>10</v>
+      </c>
+      <c r="AS21">
+        <v>101</v>
+      </c>
+      <c r="AT21">
+        <v>101</v>
+      </c>
+      <c r="AU21">
+        <v>101</v>
+      </c>
+      <c r="AV21">
+        <v>101</v>
+      </c>
+      <c r="AW21">
+        <v>101</v>
+      </c>
+      <c r="AX21">
+        <v>101</v>
+      </c>
+      <c r="AY21">
+        <v>101</v>
+      </c>
+      <c r="AZ21">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>102</v>
+      </c>
+      <c r="B22">
+        <v>102</v>
+      </c>
+      <c r="C22">
+        <v>102</v>
+      </c>
+      <c r="D22">
+        <v>102</v>
+      </c>
+      <c r="E22">
+        <v>102</v>
+      </c>
+      <c r="F22">
+        <v>102</v>
+      </c>
+      <c r="G22">
+        <v>102</v>
+      </c>
+      <c r="H22">
+        <v>102</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>80</v>
+      </c>
+      <c r="P22">
+        <v>80</v>
+      </c>
+      <c r="Q22">
+        <v>80</v>
+      </c>
+      <c r="R22">
+        <v>80</v>
+      </c>
+      <c r="S22">
+        <v>80</v>
+      </c>
+      <c r="T22">
+        <v>80</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>81</v>
+      </c>
+      <c r="Y22">
+        <v>81</v>
+      </c>
+      <c r="Z22">
+        <v>81</v>
+      </c>
+      <c r="AA22">
+        <v>81</v>
+      </c>
+      <c r="AB22">
+        <v>81</v>
+      </c>
+      <c r="AC22">
+        <v>81</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>82</v>
+      </c>
+      <c r="AH22">
+        <v>82</v>
+      </c>
+      <c r="AI22">
+        <v>82</v>
+      </c>
+      <c r="AJ22">
+        <v>82</v>
+      </c>
+      <c r="AK22">
+        <v>82</v>
+      </c>
+      <c r="AL22">
+        <v>82</v>
+      </c>
+      <c r="AM22">
+        <v>20</v>
+      </c>
+      <c r="AN22">
+        <v>10</v>
+      </c>
+      <c r="AO22">
+        <v>10</v>
+      </c>
+      <c r="AP22">
+        <v>10</v>
+      </c>
+      <c r="AQ22">
+        <v>10</v>
+      </c>
+      <c r="AR22">
+        <v>10</v>
+      </c>
+      <c r="AS22">
+        <v>101</v>
+      </c>
+      <c r="AT22">
+        <v>101</v>
+      </c>
+      <c r="AU22">
+        <v>101</v>
+      </c>
+      <c r="AV22">
+        <v>101</v>
+      </c>
+      <c r="AW22">
+        <v>101</v>
+      </c>
+      <c r="AX22">
+        <v>101</v>
+      </c>
+      <c r="AY22">
+        <v>101</v>
+      </c>
+      <c r="AZ22">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>102</v>
+      </c>
+      <c r="B23">
+        <v>102</v>
+      </c>
+      <c r="C23">
+        <v>102</v>
+      </c>
+      <c r="D23">
+        <v>102</v>
+      </c>
+      <c r="E23">
+        <v>102</v>
+      </c>
+      <c r="F23">
+        <v>102</v>
+      </c>
+      <c r="G23">
+        <v>102</v>
+      </c>
+      <c r="H23">
+        <v>102</v>
+      </c>
+      <c r="I23">
+        <v>102</v>
+      </c>
+      <c r="J23">
+        <v>102</v>
+      </c>
+      <c r="K23">
+        <v>102</v>
+      </c>
+      <c r="L23">
+        <v>102</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>10</v>
+      </c>
+      <c r="R23">
+        <v>20</v>
+      </c>
+      <c r="S23">
+        <v>10</v>
+      </c>
+      <c r="T23">
+        <v>10</v>
+      </c>
+      <c r="U23">
+        <v>10</v>
+      </c>
+      <c r="V23">
+        <v>10</v>
+      </c>
+      <c r="W23">
+        <v>10</v>
+      </c>
+      <c r="X23">
+        <v>10</v>
+      </c>
+      <c r="Y23">
+        <v>10</v>
+      </c>
+      <c r="Z23">
+        <v>20</v>
+      </c>
+      <c r="AA23">
+        <v>20</v>
+      </c>
+      <c r="AB23">
+        <v>20</v>
+      </c>
+      <c r="AC23">
+        <v>10</v>
+      </c>
+      <c r="AD23">
+        <v>10</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>10</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+      <c r="AH23">
+        <v>10</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>10</v>
+      </c>
+      <c r="AK23">
+        <v>20</v>
+      </c>
+      <c r="AL23">
+        <v>10</v>
+      </c>
+      <c r="AM23">
+        <v>20</v>
+      </c>
+      <c r="AN23">
+        <v>10</v>
+      </c>
+      <c r="AO23">
+        <v>101</v>
+      </c>
+      <c r="AP23">
+        <v>101</v>
+      </c>
+      <c r="AQ23">
+        <v>101</v>
+      </c>
+      <c r="AR23">
+        <v>101</v>
+      </c>
+      <c r="AS23">
+        <v>101</v>
+      </c>
+      <c r="AT23">
+        <v>101</v>
+      </c>
+      <c r="AU23">
+        <v>101</v>
+      </c>
+      <c r="AV23">
+        <v>101</v>
+      </c>
+      <c r="AW23">
+        <v>101</v>
+      </c>
+      <c r="AX23">
+        <v>101</v>
+      </c>
+      <c r="AY23">
+        <v>101</v>
+      </c>
+      <c r="AZ23">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>102</v>
+      </c>
+      <c r="B24">
+        <v>102</v>
+      </c>
+      <c r="C24">
+        <v>102</v>
+      </c>
+      <c r="D24">
+        <v>102</v>
+      </c>
+      <c r="E24">
+        <v>102</v>
+      </c>
+      <c r="F24">
+        <v>102</v>
+      </c>
+      <c r="G24">
+        <v>102</v>
+      </c>
+      <c r="H24">
+        <v>102</v>
+      </c>
+      <c r="I24">
+        <v>102</v>
+      </c>
+      <c r="J24">
+        <v>102</v>
+      </c>
+      <c r="K24">
+        <v>102</v>
+      </c>
+      <c r="L24">
+        <v>102</v>
+      </c>
+      <c r="M24">
+        <v>10</v>
+      </c>
+      <c r="N24">
+        <v>20</v>
+      </c>
+      <c r="O24">
+        <v>20</v>
+      </c>
+      <c r="P24">
+        <v>20</v>
+      </c>
+      <c r="Q24">
+        <v>10</v>
+      </c>
+      <c r="R24">
+        <v>20</v>
+      </c>
+      <c r="S24">
+        <v>20</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>20</v>
+      </c>
+      <c r="Z24">
+        <v>20</v>
+      </c>
+      <c r="AA24">
+        <v>20</v>
+      </c>
+      <c r="AB24">
+        <v>20</v>
+      </c>
+      <c r="AC24">
+        <v>20</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>20</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>20</v>
+      </c>
+      <c r="AK24">
+        <v>20</v>
+      </c>
+      <c r="AL24">
+        <v>20</v>
+      </c>
+      <c r="AM24">
+        <v>20</v>
+      </c>
+      <c r="AN24">
+        <v>10</v>
+      </c>
+      <c r="AO24">
+        <v>101</v>
+      </c>
+      <c r="AP24">
+        <v>101</v>
+      </c>
+      <c r="AQ24">
+        <v>101</v>
+      </c>
+      <c r="AR24">
+        <v>101</v>
+      </c>
+      <c r="AS24">
+        <v>101</v>
+      </c>
+      <c r="AT24">
+        <v>101</v>
+      </c>
+      <c r="AU24">
+        <v>101</v>
+      </c>
+      <c r="AV24">
+        <v>101</v>
+      </c>
+      <c r="AW24">
+        <v>101</v>
+      </c>
+      <c r="AX24">
+        <v>101</v>
+      </c>
+      <c r="AY24">
+        <v>101</v>
+      </c>
+      <c r="AZ24">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>102</v>
+      </c>
+      <c r="B25">
+        <v>102</v>
+      </c>
+      <c r="C25">
+        <v>102</v>
+      </c>
+      <c r="D25">
+        <v>102</v>
+      </c>
+      <c r="E25">
+        <v>102</v>
+      </c>
+      <c r="F25">
+        <v>102</v>
+      </c>
+      <c r="G25">
+        <v>102</v>
+      </c>
+      <c r="H25">
+        <v>102</v>
+      </c>
+      <c r="I25">
+        <v>102</v>
+      </c>
+      <c r="J25">
+        <v>102</v>
+      </c>
+      <c r="K25">
+        <v>102</v>
+      </c>
+      <c r="L25">
+        <v>102</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>10</v>
+      </c>
+      <c r="O25">
+        <v>10</v>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
+        <v>10</v>
+      </c>
+      <c r="S25">
+        <v>10</v>
+      </c>
+      <c r="T25">
+        <v>10</v>
+      </c>
+      <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25">
+        <v>10</v>
+      </c>
+      <c r="W25">
+        <v>10</v>
+      </c>
+      <c r="X25">
+        <v>10</v>
+      </c>
+      <c r="Y25">
+        <v>10</v>
+      </c>
+      <c r="Z25">
+        <v>10</v>
+      </c>
+      <c r="AA25">
+        <v>10</v>
+      </c>
+      <c r="AB25">
+        <v>10</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>10</v>
+      </c>
+      <c r="AE25">
+        <v>10</v>
+      </c>
+      <c r="AF25">
+        <v>10</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+      <c r="AH25">
+        <v>10</v>
+      </c>
+      <c r="AI25">
+        <v>10</v>
+      </c>
+      <c r="AJ25">
+        <v>10</v>
+      </c>
+      <c r="AK25">
+        <v>10</v>
+      </c>
+      <c r="AL25">
+        <v>10</v>
+      </c>
+      <c r="AM25">
+        <v>10</v>
+      </c>
+      <c r="AN25">
+        <v>10</v>
+      </c>
+      <c r="AO25">
+        <v>101</v>
+      </c>
+      <c r="AP25">
+        <v>101</v>
+      </c>
+      <c r="AQ25">
+        <v>101</v>
+      </c>
+      <c r="AR25">
+        <v>101</v>
+      </c>
+      <c r="AS25">
+        <v>101</v>
+      </c>
+      <c r="AT25">
+        <v>101</v>
+      </c>
+      <c r="AU25">
+        <v>101</v>
+      </c>
+      <c r="AV25">
+        <v>101</v>
+      </c>
+      <c r="AW25">
+        <v>101</v>
+      </c>
+      <c r="AX25">
+        <v>101</v>
+      </c>
+      <c r="AY25">
+        <v>101</v>
+      </c>
+      <c r="AZ25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>102</v>
+      </c>
+      <c r="B26">
+        <v>102</v>
+      </c>
+      <c r="C26">
+        <v>102</v>
+      </c>
+      <c r="D26">
+        <v>102</v>
+      </c>
+      <c r="E26">
+        <v>102</v>
+      </c>
+      <c r="F26">
+        <v>102</v>
+      </c>
+      <c r="G26">
+        <v>102</v>
+      </c>
+      <c r="H26">
+        <v>102</v>
+      </c>
+      <c r="I26">
+        <v>102</v>
+      </c>
+      <c r="J26">
+        <v>102</v>
+      </c>
+      <c r="K26">
+        <v>102</v>
+      </c>
+      <c r="L26">
+        <v>102</v>
+      </c>
+      <c r="M26">
+        <v>102</v>
+      </c>
+      <c r="N26">
+        <v>102</v>
+      </c>
+      <c r="O26">
+        <v>102</v>
+      </c>
+      <c r="P26">
+        <v>102</v>
+      </c>
+      <c r="Q26">
+        <v>102</v>
+      </c>
+      <c r="R26">
+        <v>102</v>
+      </c>
+      <c r="S26">
+        <v>102</v>
+      </c>
+      <c r="T26">
+        <v>102</v>
+      </c>
+      <c r="U26">
+        <v>102</v>
+      </c>
+      <c r="V26">
+        <v>102</v>
+      </c>
+      <c r="W26">
+        <v>102</v>
+      </c>
+      <c r="X26">
+        <v>102</v>
+      </c>
+      <c r="Y26">
+        <v>102</v>
+      </c>
+      <c r="Z26">
+        <v>102</v>
+      </c>
+      <c r="AA26">
+        <v>102</v>
+      </c>
+      <c r="AB26">
+        <v>102</v>
+      </c>
+      <c r="AC26">
+        <v>102</v>
+      </c>
+      <c r="AD26">
+        <v>102</v>
+      </c>
+      <c r="AE26">
+        <v>102</v>
+      </c>
+      <c r="AF26">
+        <v>102</v>
+      </c>
+      <c r="AG26">
+        <v>102</v>
+      </c>
+      <c r="AH26">
+        <v>102</v>
+      </c>
+      <c r="AI26">
+        <v>102</v>
+      </c>
+      <c r="AJ26">
+        <v>102</v>
+      </c>
+      <c r="AK26">
+        <v>102</v>
+      </c>
+      <c r="AL26">
+        <v>102</v>
+      </c>
+      <c r="AM26">
+        <v>102</v>
+      </c>
+      <c r="AN26">
+        <v>102</v>
+      </c>
+      <c r="AO26">
+        <v>101</v>
+      </c>
+      <c r="AP26">
+        <v>101</v>
+      </c>
+      <c r="AQ26">
+        <v>101</v>
+      </c>
+      <c r="AR26">
+        <v>101</v>
+      </c>
+      <c r="AS26">
+        <v>101</v>
+      </c>
+      <c r="AT26">
+        <v>101</v>
+      </c>
+      <c r="AU26">
+        <v>101</v>
+      </c>
+      <c r="AV26">
+        <v>101</v>
+      </c>
+      <c r="AW26">
+        <v>101</v>
+      </c>
+      <c r="AX26">
+        <v>101</v>
+      </c>
+      <c r="AY26">
+        <v>101</v>
+      </c>
+      <c r="AZ26">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>102</v>
+      </c>
+      <c r="B27">
+        <v>102</v>
+      </c>
+      <c r="C27">
+        <v>102</v>
+      </c>
+      <c r="D27">
+        <v>102</v>
+      </c>
+      <c r="E27">
+        <v>102</v>
+      </c>
+      <c r="F27">
+        <v>102</v>
+      </c>
+      <c r="G27">
+        <v>102</v>
+      </c>
+      <c r="H27">
+        <v>102</v>
+      </c>
+      <c r="I27">
+        <v>102</v>
+      </c>
+      <c r="J27">
+        <v>102</v>
+      </c>
+      <c r="K27">
+        <v>102</v>
+      </c>
+      <c r="L27">
+        <v>102</v>
+      </c>
+      <c r="M27">
+        <v>102</v>
+      </c>
+      <c r="N27">
+        <v>102</v>
+      </c>
+      <c r="O27">
+        <v>102</v>
+      </c>
+      <c r="P27">
+        <v>102</v>
+      </c>
+      <c r="Q27">
+        <v>102</v>
+      </c>
+      <c r="R27">
+        <v>102</v>
+      </c>
+      <c r="S27">
+        <v>102</v>
+      </c>
+      <c r="T27">
+        <v>102</v>
+      </c>
+      <c r="U27">
+        <v>102</v>
+      </c>
+      <c r="V27">
+        <v>102</v>
+      </c>
+      <c r="W27">
+        <v>102</v>
+      </c>
+      <c r="X27">
+        <v>102</v>
+      </c>
+      <c r="Y27">
+        <v>102</v>
+      </c>
+      <c r="Z27">
+        <v>102</v>
+      </c>
+      <c r="AA27">
+        <v>102</v>
+      </c>
+      <c r="AB27">
+        <v>102</v>
+      </c>
+      <c r="AC27">
+        <v>102</v>
+      </c>
+      <c r="AD27">
+        <v>102</v>
+      </c>
+      <c r="AE27">
+        <v>102</v>
+      </c>
+      <c r="AF27">
+        <v>102</v>
+      </c>
+      <c r="AG27">
+        <v>102</v>
+      </c>
+      <c r="AH27">
+        <v>102</v>
+      </c>
+      <c r="AI27">
+        <v>102</v>
+      </c>
+      <c r="AJ27">
+        <v>102</v>
+      </c>
+      <c r="AK27">
+        <v>102</v>
+      </c>
+      <c r="AL27">
+        <v>102</v>
+      </c>
+      <c r="AM27">
+        <v>102</v>
+      </c>
+      <c r="AN27">
+        <v>102</v>
+      </c>
+      <c r="AO27">
+        <v>101</v>
+      </c>
+      <c r="AP27">
+        <v>101</v>
+      </c>
+      <c r="AQ27">
+        <v>101</v>
+      </c>
+      <c r="AR27">
+        <v>101</v>
+      </c>
+      <c r="AS27">
+        <v>101</v>
+      </c>
+      <c r="AT27">
+        <v>101</v>
+      </c>
+      <c r="AU27">
+        <v>101</v>
+      </c>
+      <c r="AV27">
+        <v>101</v>
+      </c>
+      <c r="AW27">
+        <v>101</v>
+      </c>
+      <c r="AX27">
+        <v>101</v>
+      </c>
+      <c r="AY27">
+        <v>101</v>
+      </c>
+      <c r="AZ27">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>102</v>
+      </c>
+      <c r="B28">
+        <v>102</v>
+      </c>
+      <c r="C28">
+        <v>102</v>
+      </c>
+      <c r="D28">
+        <v>102</v>
+      </c>
+      <c r="E28">
+        <v>102</v>
+      </c>
+      <c r="F28">
+        <v>102</v>
+      </c>
+      <c r="G28">
+        <v>102</v>
+      </c>
+      <c r="H28">
+        <v>102</v>
+      </c>
+      <c r="I28">
+        <v>102</v>
+      </c>
+      <c r="J28">
+        <v>102</v>
+      </c>
+      <c r="K28">
+        <v>102</v>
+      </c>
+      <c r="L28">
+        <v>102</v>
+      </c>
+      <c r="M28">
+        <v>102</v>
+      </c>
+      <c r="N28">
+        <v>102</v>
+      </c>
+      <c r="O28">
+        <v>102</v>
+      </c>
+      <c r="P28">
+        <v>102</v>
+      </c>
+      <c r="Q28">
+        <v>102</v>
+      </c>
+      <c r="R28">
+        <v>102</v>
+      </c>
+      <c r="S28">
+        <v>102</v>
+      </c>
+      <c r="T28">
+        <v>102</v>
+      </c>
+      <c r="U28">
+        <v>102</v>
+      </c>
+      <c r="V28">
+        <v>102</v>
+      </c>
+      <c r="W28">
+        <v>102</v>
+      </c>
+      <c r="X28">
+        <v>102</v>
+      </c>
+      <c r="Y28">
+        <v>102</v>
+      </c>
+      <c r="Z28">
+        <v>102</v>
+      </c>
+      <c r="AA28">
+        <v>102</v>
+      </c>
+      <c r="AB28">
+        <v>102</v>
+      </c>
+      <c r="AC28">
+        <v>102</v>
+      </c>
+      <c r="AD28">
+        <v>102</v>
+      </c>
+      <c r="AE28">
+        <v>102</v>
+      </c>
+      <c r="AF28">
+        <v>102</v>
+      </c>
+      <c r="AG28">
+        <v>102</v>
+      </c>
+      <c r="AH28">
+        <v>102</v>
+      </c>
+      <c r="AI28">
+        <v>102</v>
+      </c>
+      <c r="AJ28">
+        <v>102</v>
+      </c>
+      <c r="AK28">
+        <v>102</v>
+      </c>
+      <c r="AL28">
+        <v>102</v>
+      </c>
+      <c r="AM28">
+        <v>102</v>
+      </c>
+      <c r="AN28">
+        <v>102</v>
+      </c>
+      <c r="AO28">
+        <v>101</v>
+      </c>
+      <c r="AP28">
+        <v>101</v>
+      </c>
+      <c r="AQ28">
+        <v>101</v>
+      </c>
+      <c r="AR28">
+        <v>101</v>
+      </c>
+      <c r="AS28">
+        <v>101</v>
+      </c>
+      <c r="AT28">
+        <v>101</v>
+      </c>
+      <c r="AU28">
+        <v>101</v>
+      </c>
+      <c r="AV28">
+        <v>101</v>
+      </c>
+      <c r="AW28">
+        <v>101</v>
+      </c>
+      <c r="AX28">
+        <v>101</v>
+      </c>
+      <c r="AY28">
+        <v>101</v>
+      </c>
+      <c r="AZ28">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>102</v>
+      </c>
+      <c r="B29">
+        <v>102</v>
+      </c>
+      <c r="C29">
+        <v>102</v>
+      </c>
+      <c r="D29">
+        <v>102</v>
+      </c>
+      <c r="E29">
+        <v>102</v>
+      </c>
+      <c r="F29">
+        <v>102</v>
+      </c>
+      <c r="G29">
+        <v>102</v>
+      </c>
+      <c r="H29">
+        <v>102</v>
+      </c>
+      <c r="I29">
+        <v>102</v>
+      </c>
+      <c r="J29">
+        <v>102</v>
+      </c>
+      <c r="K29">
+        <v>102</v>
+      </c>
+      <c r="L29">
+        <v>102</v>
+      </c>
+      <c r="M29">
+        <v>102</v>
+      </c>
+      <c r="N29">
+        <v>102</v>
+      </c>
+      <c r="O29">
+        <v>102</v>
+      </c>
+      <c r="P29">
+        <v>102</v>
+      </c>
+      <c r="Q29">
+        <v>102</v>
+      </c>
+      <c r="R29">
+        <v>102</v>
+      </c>
+      <c r="S29">
+        <v>102</v>
+      </c>
+      <c r="T29">
+        <v>102</v>
+      </c>
+      <c r="U29">
+        <v>102</v>
+      </c>
+      <c r="V29">
+        <v>102</v>
+      </c>
+      <c r="W29">
+        <v>102</v>
+      </c>
+      <c r="X29">
+        <v>102</v>
+      </c>
+      <c r="Y29">
+        <v>102</v>
+      </c>
+      <c r="Z29">
+        <v>102</v>
+      </c>
+      <c r="AA29">
+        <v>102</v>
+      </c>
+      <c r="AB29">
+        <v>102</v>
+      </c>
+      <c r="AC29">
+        <v>102</v>
+      </c>
+      <c r="AD29">
+        <v>102</v>
+      </c>
+      <c r="AE29">
+        <v>102</v>
+      </c>
+      <c r="AF29">
+        <v>102</v>
+      </c>
+      <c r="AG29">
+        <v>102</v>
+      </c>
+      <c r="AH29">
+        <v>102</v>
+      </c>
+      <c r="AI29">
+        <v>102</v>
+      </c>
+      <c r="AJ29">
+        <v>102</v>
+      </c>
+      <c r="AK29">
+        <v>102</v>
+      </c>
+      <c r="AL29">
+        <v>102</v>
+      </c>
+      <c r="AM29">
+        <v>102</v>
+      </c>
+      <c r="AN29">
+        <v>102</v>
+      </c>
+      <c r="AO29">
+        <v>101</v>
+      </c>
+      <c r="AP29">
+        <v>101</v>
+      </c>
+      <c r="AQ29">
+        <v>101</v>
+      </c>
+      <c r="AR29">
+        <v>101</v>
+      </c>
+      <c r="AS29">
+        <v>101</v>
+      </c>
+      <c r="AT29">
+        <v>101</v>
+      </c>
+      <c r="AU29">
+        <v>101</v>
+      </c>
+      <c r="AV29">
+        <v>101</v>
+      </c>
+      <c r="AW29">
+        <v>101</v>
+      </c>
+      <c r="AX29">
+        <v>101</v>
+      </c>
+      <c r="AY29">
+        <v>101</v>
+      </c>
+      <c r="AZ29">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>102</v>
+      </c>
+      <c r="B30">
+        <v>102</v>
+      </c>
+      <c r="C30">
+        <v>102</v>
+      </c>
+      <c r="D30">
+        <v>102</v>
+      </c>
+      <c r="E30">
+        <v>102</v>
+      </c>
+      <c r="F30">
+        <v>102</v>
+      </c>
+      <c r="G30">
+        <v>102</v>
+      </c>
+      <c r="H30">
+        <v>102</v>
+      </c>
+      <c r="I30">
+        <v>102</v>
+      </c>
+      <c r="J30">
+        <v>102</v>
+      </c>
+      <c r="K30">
+        <v>102</v>
+      </c>
+      <c r="L30">
+        <v>102</v>
+      </c>
+      <c r="M30">
+        <v>102</v>
+      </c>
+      <c r="N30">
+        <v>102</v>
+      </c>
+      <c r="O30">
+        <v>102</v>
+      </c>
+      <c r="P30">
+        <v>102</v>
+      </c>
+      <c r="Q30">
+        <v>102</v>
+      </c>
+      <c r="R30">
+        <v>102</v>
+      </c>
+      <c r="S30">
+        <v>102</v>
+      </c>
+      <c r="T30">
+        <v>102</v>
+      </c>
+      <c r="U30">
+        <v>102</v>
+      </c>
+      <c r="V30">
+        <v>102</v>
+      </c>
+      <c r="W30">
+        <v>102</v>
+      </c>
+      <c r="X30">
+        <v>102</v>
+      </c>
+      <c r="Y30">
+        <v>102</v>
+      </c>
+      <c r="Z30">
+        <v>102</v>
+      </c>
+      <c r="AA30">
+        <v>102</v>
+      </c>
+      <c r="AB30">
+        <v>102</v>
+      </c>
+      <c r="AC30">
+        <v>102</v>
+      </c>
+      <c r="AD30">
+        <v>102</v>
+      </c>
+      <c r="AE30">
+        <v>102</v>
+      </c>
+      <c r="AF30">
+        <v>102</v>
+      </c>
+      <c r="AG30">
+        <v>102</v>
+      </c>
+      <c r="AH30">
+        <v>102</v>
+      </c>
+      <c r="AI30">
+        <v>102</v>
+      </c>
+      <c r="AJ30">
+        <v>102</v>
+      </c>
+      <c r="AK30">
+        <v>102</v>
+      </c>
+      <c r="AL30">
+        <v>102</v>
+      </c>
+      <c r="AM30">
+        <v>102</v>
+      </c>
+      <c r="AN30">
+        <v>102</v>
+      </c>
+      <c r="AO30">
+        <v>101</v>
+      </c>
+      <c r="AP30">
+        <v>101</v>
+      </c>
+      <c r="AQ30">
+        <v>101</v>
+      </c>
+      <c r="AR30">
+        <v>101</v>
+      </c>
+      <c r="AS30">
+        <v>101</v>
+      </c>
+      <c r="AT30">
+        <v>101</v>
+      </c>
+      <c r="AU30">
+        <v>101</v>
+      </c>
+      <c r="AV30">
+        <v>101</v>
+      </c>
+      <c r="AW30">
+        <v>101</v>
+      </c>
+      <c r="AX30">
+        <v>101</v>
+      </c>
+      <c r="AY30">
+        <v>101</v>
+      </c>
+      <c r="AZ30">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>102</v>
+      </c>
+      <c r="B31">
+        <v>102</v>
+      </c>
+      <c r="C31">
+        <v>102</v>
+      </c>
+      <c r="D31">
+        <v>102</v>
+      </c>
+      <c r="E31">
+        <v>102</v>
+      </c>
+      <c r="F31">
+        <v>102</v>
+      </c>
+      <c r="G31">
+        <v>102</v>
+      </c>
+      <c r="H31">
+        <v>102</v>
+      </c>
+      <c r="I31">
+        <v>102</v>
+      </c>
+      <c r="J31">
+        <v>102</v>
+      </c>
+      <c r="K31">
+        <v>102</v>
+      </c>
+      <c r="L31">
+        <v>102</v>
+      </c>
+      <c r="M31">
+        <v>102</v>
+      </c>
+      <c r="N31">
+        <v>102</v>
+      </c>
+      <c r="O31">
+        <v>102</v>
+      </c>
+      <c r="P31">
+        <v>102</v>
+      </c>
+      <c r="Q31">
+        <v>102</v>
+      </c>
+      <c r="R31">
+        <v>102</v>
+      </c>
+      <c r="S31">
+        <v>102</v>
+      </c>
+      <c r="T31">
+        <v>102</v>
+      </c>
+      <c r="U31">
+        <v>102</v>
+      </c>
+      <c r="V31">
+        <v>102</v>
+      </c>
+      <c r="W31">
+        <v>102</v>
+      </c>
+      <c r="X31">
+        <v>102</v>
+      </c>
+      <c r="Y31">
+        <v>102</v>
+      </c>
+      <c r="Z31">
+        <v>102</v>
+      </c>
+      <c r="AA31">
+        <v>102</v>
+      </c>
+      <c r="AB31">
+        <v>102</v>
+      </c>
+      <c r="AC31">
+        <v>102</v>
+      </c>
+      <c r="AD31">
+        <v>102</v>
+      </c>
+      <c r="AE31">
+        <v>102</v>
+      </c>
+      <c r="AF31">
+        <v>102</v>
+      </c>
+      <c r="AG31">
+        <v>102</v>
+      </c>
+      <c r="AH31">
+        <v>102</v>
+      </c>
+      <c r="AI31">
+        <v>102</v>
+      </c>
+      <c r="AJ31">
+        <v>102</v>
+      </c>
+      <c r="AK31">
+        <v>102</v>
+      </c>
+      <c r="AL31">
+        <v>102</v>
+      </c>
+      <c r="AM31">
+        <v>102</v>
+      </c>
+      <c r="AN31">
+        <v>102</v>
+      </c>
+      <c r="AO31">
+        <v>101</v>
+      </c>
+      <c r="AP31">
+        <v>101</v>
+      </c>
+      <c r="AQ31">
+        <v>101</v>
+      </c>
+      <c r="AR31">
+        <v>101</v>
+      </c>
+      <c r="AS31">
+        <v>101</v>
+      </c>
+      <c r="AT31">
+        <v>101</v>
+      </c>
+      <c r="AU31">
+        <v>101</v>
+      </c>
+      <c r="AV31">
+        <v>101</v>
+      </c>
+      <c r="AW31">
+        <v>101</v>
+      </c>
+      <c r="AX31">
+        <v>101</v>
+      </c>
+      <c r="AY31">
+        <v>101</v>
+      </c>
+      <c r="AZ31">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>100</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>102</v>
+      </c>
+      <c r="M32">
+        <v>102</v>
+      </c>
+      <c r="N32">
+        <v>102</v>
+      </c>
+      <c r="O32">
+        <v>102</v>
+      </c>
+      <c r="P32">
+        <v>102</v>
+      </c>
+      <c r="Q32">
+        <v>102</v>
+      </c>
+      <c r="R32">
+        <v>102</v>
+      </c>
+      <c r="S32">
+        <v>102</v>
+      </c>
+      <c r="T32">
+        <v>102</v>
+      </c>
+      <c r="U32">
+        <v>102</v>
+      </c>
+      <c r="V32">
+        <v>102</v>
+      </c>
+      <c r="W32">
+        <v>102</v>
+      </c>
+      <c r="X32">
+        <v>102</v>
+      </c>
+      <c r="Y32">
+        <v>102</v>
+      </c>
+      <c r="Z32">
+        <v>102</v>
+      </c>
+      <c r="AA32">
+        <v>102</v>
+      </c>
+      <c r="AB32">
+        <v>102</v>
+      </c>
+      <c r="AC32">
+        <v>102</v>
+      </c>
+      <c r="AD32">
+        <v>102</v>
+      </c>
+      <c r="AE32">
+        <v>102</v>
+      </c>
+      <c r="AF32">
+        <v>102</v>
+      </c>
+      <c r="AG32">
+        <v>102</v>
+      </c>
+      <c r="AH32">
+        <v>102</v>
+      </c>
+      <c r="AI32">
+        <v>102</v>
+      </c>
+      <c r="AJ32">
+        <v>102</v>
+      </c>
+      <c r="AK32">
+        <v>102</v>
+      </c>
+      <c r="AL32">
+        <v>102</v>
+      </c>
+      <c r="AM32">
+        <v>102</v>
+      </c>
+      <c r="AN32">
+        <v>102</v>
+      </c>
+      <c r="AO32">
+        <v>100</v>
+      </c>
+      <c r="AP32">
+        <v>100</v>
+      </c>
+      <c r="AQ32">
+        <v>100</v>
+      </c>
+      <c r="AR32">
+        <v>100</v>
+      </c>
+      <c r="AS32">
+        <v>100</v>
+      </c>
+      <c r="AT32">
+        <v>100</v>
+      </c>
+      <c r="AU32">
+        <v>100</v>
+      </c>
+      <c r="AV32">
+        <v>100</v>
+      </c>
+      <c r="AW32">
+        <v>100</v>
+      </c>
+      <c r="AX32">
+        <v>100</v>
+      </c>
+      <c r="AY32">
+        <v>100</v>
+      </c>
+      <c r="AZ32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>100</v>
+      </c>
+      <c r="B33">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>102</v>
+      </c>
+      <c r="M33">
+        <v>102</v>
+      </c>
+      <c r="N33">
+        <v>102</v>
+      </c>
+      <c r="O33">
+        <v>102</v>
+      </c>
+      <c r="P33">
+        <v>102</v>
+      </c>
+      <c r="Q33">
+        <v>102</v>
+      </c>
+      <c r="R33">
+        <v>102</v>
+      </c>
+      <c r="S33">
+        <v>102</v>
+      </c>
+      <c r="T33">
+        <v>102</v>
+      </c>
+      <c r="U33">
+        <v>102</v>
+      </c>
+      <c r="V33">
+        <v>102</v>
+      </c>
+      <c r="W33">
+        <v>102</v>
+      </c>
+      <c r="X33">
+        <v>102</v>
+      </c>
+      <c r="Y33">
+        <v>102</v>
+      </c>
+      <c r="Z33">
+        <v>102</v>
+      </c>
+      <c r="AA33">
+        <v>102</v>
+      </c>
+      <c r="AB33">
+        <v>102</v>
+      </c>
+      <c r="AC33">
+        <v>102</v>
+      </c>
+      <c r="AD33">
+        <v>102</v>
+      </c>
+      <c r="AE33">
+        <v>102</v>
+      </c>
+      <c r="AF33">
+        <v>102</v>
+      </c>
+      <c r="AG33">
+        <v>102</v>
+      </c>
+      <c r="AH33">
+        <v>102</v>
+      </c>
+      <c r="AI33">
+        <v>102</v>
+      </c>
+      <c r="AJ33">
+        <v>102</v>
+      </c>
+      <c r="AK33">
+        <v>102</v>
+      </c>
+      <c r="AL33">
+        <v>102</v>
+      </c>
+      <c r="AM33">
+        <v>102</v>
+      </c>
+      <c r="AN33">
+        <v>102</v>
+      </c>
+      <c r="AO33">
+        <v>100</v>
+      </c>
+      <c r="AP33">
+        <v>100</v>
+      </c>
+      <c r="AQ33">
+        <v>100</v>
+      </c>
+      <c r="AR33">
+        <v>100</v>
+      </c>
+      <c r="AS33">
+        <v>100</v>
+      </c>
+      <c r="AT33">
+        <v>100</v>
+      </c>
+      <c r="AU33">
+        <v>100</v>
+      </c>
+      <c r="AV33">
+        <v>100</v>
+      </c>
+      <c r="AW33">
+        <v>100</v>
+      </c>
+      <c r="AX33">
+        <v>100</v>
+      </c>
+      <c r="AY33">
+        <v>100</v>
+      </c>
+      <c r="AZ33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>102</v>
+      </c>
+      <c r="B34">
+        <v>102</v>
+      </c>
+      <c r="C34">
+        <v>102</v>
+      </c>
+      <c r="D34">
+        <v>102</v>
+      </c>
+      <c r="E34">
+        <v>102</v>
+      </c>
+      <c r="F34">
+        <v>102</v>
+      </c>
+      <c r="G34">
+        <v>102</v>
+      </c>
+      <c r="H34">
+        <v>102</v>
+      </c>
+      <c r="I34">
+        <v>102</v>
+      </c>
+      <c r="J34">
+        <v>102</v>
+      </c>
+      <c r="K34">
+        <v>102</v>
+      </c>
+      <c r="L34">
+        <v>102</v>
+      </c>
+      <c r="M34">
+        <v>102</v>
+      </c>
+      <c r="N34">
+        <v>102</v>
+      </c>
+      <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="P34">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <v>102</v>
+      </c>
+      <c r="R34">
+        <v>102</v>
+      </c>
+      <c r="S34">
+        <v>102</v>
+      </c>
+      <c r="T34">
+        <v>102</v>
+      </c>
+      <c r="U34">
+        <v>100</v>
+      </c>
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
+        <v>100</v>
+      </c>
+      <c r="X34">
+        <v>100</v>
+      </c>
+      <c r="Y34">
+        <v>100</v>
+      </c>
+      <c r="Z34">
+        <v>100</v>
+      </c>
+      <c r="AA34">
+        <v>100</v>
+      </c>
+      <c r="AB34">
+        <v>100</v>
+      </c>
+      <c r="AC34">
+        <v>101</v>
+      </c>
+      <c r="AD34">
+        <v>101</v>
+      </c>
+      <c r="AE34">
+        <v>101</v>
+      </c>
+      <c r="AF34">
+        <v>101</v>
+      </c>
+      <c r="AG34">
+        <v>101</v>
+      </c>
+      <c r="AH34">
+        <v>101</v>
+      </c>
+      <c r="AI34">
+        <v>101</v>
+      </c>
+      <c r="AJ34">
+        <v>101</v>
+      </c>
+      <c r="AK34">
+        <v>100</v>
+      </c>
+      <c r="AL34">
+        <v>100</v>
+      </c>
+      <c r="AM34">
+        <v>101</v>
+      </c>
+      <c r="AN34">
+        <v>101</v>
+      </c>
+      <c r="AO34">
+        <v>101</v>
+      </c>
+      <c r="AP34">
+        <v>101</v>
+      </c>
+      <c r="AQ34">
+        <v>101</v>
+      </c>
+      <c r="AR34">
+        <v>101</v>
+      </c>
+      <c r="AS34">
+        <v>101</v>
+      </c>
+      <c r="AT34">
+        <v>101</v>
+      </c>
+      <c r="AU34">
+        <v>101</v>
+      </c>
+      <c r="AV34">
+        <v>101</v>
+      </c>
+      <c r="AW34">
+        <v>101</v>
+      </c>
+      <c r="AX34">
+        <v>101</v>
+      </c>
+      <c r="AY34">
+        <v>101</v>
+      </c>
+      <c r="AZ34">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>102</v>
+      </c>
+      <c r="B35">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>102</v>
+      </c>
+      <c r="D35">
+        <v>102</v>
+      </c>
+      <c r="E35">
+        <v>102</v>
+      </c>
+      <c r="F35">
+        <v>102</v>
+      </c>
+      <c r="G35">
+        <v>102</v>
+      </c>
+      <c r="H35">
+        <v>102</v>
+      </c>
+      <c r="I35">
+        <v>102</v>
+      </c>
+      <c r="J35">
+        <v>102</v>
+      </c>
+      <c r="K35">
+        <v>102</v>
+      </c>
+      <c r="L35">
+        <v>102</v>
+      </c>
+      <c r="M35">
+        <v>102</v>
+      </c>
+      <c r="N35">
+        <v>102</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>102</v>
+      </c>
+      <c r="R35">
+        <v>102</v>
+      </c>
+      <c r="S35">
+        <v>102</v>
+      </c>
+      <c r="T35">
+        <v>102</v>
+      </c>
+      <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+      <c r="Z35">
+        <v>100</v>
+      </c>
+      <c r="AA35">
+        <v>100</v>
+      </c>
+      <c r="AB35">
+        <v>100</v>
+      </c>
+      <c r="AC35">
+        <v>101</v>
+      </c>
+      <c r="AD35">
+        <v>101</v>
+      </c>
+      <c r="AE35">
+        <v>101</v>
+      </c>
+      <c r="AF35">
+        <v>101</v>
+      </c>
+      <c r="AG35">
+        <v>101</v>
+      </c>
+      <c r="AH35">
+        <v>101</v>
+      </c>
+      <c r="AI35">
+        <v>101</v>
+      </c>
+      <c r="AJ35">
+        <v>101</v>
+      </c>
+      <c r="AK35">
+        <v>100</v>
+      </c>
+      <c r="AL35">
+        <v>100</v>
+      </c>
+      <c r="AM35">
+        <v>101</v>
+      </c>
+      <c r="AN35">
+        <v>101</v>
+      </c>
+      <c r="AO35">
+        <v>101</v>
+      </c>
+      <c r="AP35">
+        <v>101</v>
+      </c>
+      <c r="AQ35">
+        <v>101</v>
+      </c>
+      <c r="AR35">
+        <v>101</v>
+      </c>
+      <c r="AS35">
+        <v>101</v>
+      </c>
+      <c r="AT35">
+        <v>101</v>
+      </c>
+      <c r="AU35">
+        <v>101</v>
+      </c>
+      <c r="AV35">
+        <v>101</v>
+      </c>
+      <c r="AW35">
+        <v>101</v>
+      </c>
+      <c r="AX35">
+        <v>101</v>
+      </c>
+      <c r="AY35">
+        <v>101</v>
+      </c>
+      <c r="AZ35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>102</v>
+      </c>
+      <c r="B36">
+        <v>102</v>
+      </c>
+      <c r="C36">
+        <v>102</v>
+      </c>
+      <c r="D36">
+        <v>102</v>
+      </c>
+      <c r="E36">
+        <v>102</v>
+      </c>
+      <c r="F36">
+        <v>102</v>
+      </c>
+      <c r="G36">
+        <v>102</v>
+      </c>
+      <c r="H36">
+        <v>102</v>
+      </c>
+      <c r="I36">
+        <v>102</v>
+      </c>
+      <c r="J36">
+        <v>102</v>
+      </c>
+      <c r="K36">
+        <v>102</v>
+      </c>
+      <c r="L36">
+        <v>102</v>
+      </c>
+      <c r="M36">
+        <v>102</v>
+      </c>
+      <c r="N36">
+        <v>102</v>
+      </c>
+      <c r="O36">
+        <v>100</v>
+      </c>
+      <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
+        <v>102</v>
+      </c>
+      <c r="R36">
+        <v>102</v>
+      </c>
+      <c r="S36">
+        <v>102</v>
+      </c>
+      <c r="T36">
+        <v>102</v>
+      </c>
+      <c r="U36">
+        <v>100</v>
+      </c>
+      <c r="V36">
+        <v>100</v>
+      </c>
+      <c r="W36">
+        <v>100</v>
+      </c>
+      <c r="X36">
+        <v>100</v>
+      </c>
+      <c r="Y36">
+        <v>100</v>
+      </c>
+      <c r="Z36">
+        <v>100</v>
+      </c>
+      <c r="AA36">
+        <v>100</v>
+      </c>
+      <c r="AB36">
+        <v>100</v>
+      </c>
+      <c r="AC36">
+        <v>101</v>
+      </c>
+      <c r="AD36">
+        <v>101</v>
+      </c>
+      <c r="AE36">
+        <v>101</v>
+      </c>
+      <c r="AF36">
+        <v>101</v>
+      </c>
+      <c r="AG36">
+        <v>101</v>
+      </c>
+      <c r="AH36">
+        <v>101</v>
+      </c>
+      <c r="AI36">
+        <v>101</v>
+      </c>
+      <c r="AJ36">
+        <v>101</v>
+      </c>
+      <c r="AK36">
+        <v>100</v>
+      </c>
+      <c r="AL36">
+        <v>100</v>
+      </c>
+      <c r="AM36">
+        <v>101</v>
+      </c>
+      <c r="AN36">
+        <v>101</v>
+      </c>
+      <c r="AO36">
+        <v>101</v>
+      </c>
+      <c r="AP36">
+        <v>101</v>
+      </c>
+      <c r="AQ36">
+        <v>101</v>
+      </c>
+      <c r="AR36">
+        <v>101</v>
+      </c>
+      <c r="AS36">
+        <v>101</v>
+      </c>
+      <c r="AT36">
+        <v>101</v>
+      </c>
+      <c r="AU36">
+        <v>101</v>
+      </c>
+      <c r="AV36">
+        <v>101</v>
+      </c>
+      <c r="AW36">
+        <v>101</v>
+      </c>
+      <c r="AX36">
+        <v>101</v>
+      </c>
+      <c r="AY36">
+        <v>101</v>
+      </c>
+      <c r="AZ36">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>102</v>
+      </c>
+      <c r="B37">
+        <v>102</v>
+      </c>
+      <c r="C37">
+        <v>102</v>
+      </c>
+      <c r="D37">
+        <v>102</v>
+      </c>
+      <c r="E37">
+        <v>102</v>
+      </c>
+      <c r="F37">
+        <v>102</v>
+      </c>
+      <c r="G37">
+        <v>102</v>
+      </c>
+      <c r="H37">
+        <v>102</v>
+      </c>
+      <c r="I37">
+        <v>102</v>
+      </c>
+      <c r="J37">
+        <v>102</v>
+      </c>
+      <c r="K37">
+        <v>102</v>
+      </c>
+      <c r="L37">
+        <v>102</v>
+      </c>
+      <c r="M37">
+        <v>102</v>
+      </c>
+      <c r="N37">
+        <v>102</v>
+      </c>
+      <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>102</v>
+      </c>
+      <c r="R37">
+        <v>102</v>
+      </c>
+      <c r="S37">
+        <v>102</v>
+      </c>
+      <c r="T37">
+        <v>102</v>
+      </c>
+      <c r="U37">
+        <v>100</v>
+      </c>
+      <c r="V37">
+        <v>100</v>
+      </c>
+      <c r="W37">
+        <v>100</v>
+      </c>
+      <c r="X37">
+        <v>100</v>
+      </c>
+      <c r="Y37">
+        <v>100</v>
+      </c>
+      <c r="Z37">
+        <v>100</v>
+      </c>
+      <c r="AA37">
+        <v>100</v>
+      </c>
+      <c r="AB37">
+        <v>100</v>
+      </c>
+      <c r="AC37">
+        <v>101</v>
+      </c>
+      <c r="AD37">
+        <v>101</v>
+      </c>
+      <c r="AE37">
+        <v>101</v>
+      </c>
+      <c r="AF37">
+        <v>101</v>
+      </c>
+      <c r="AG37">
+        <v>101</v>
+      </c>
+      <c r="AH37">
+        <v>101</v>
+      </c>
+      <c r="AI37">
+        <v>101</v>
+      </c>
+      <c r="AJ37">
+        <v>101</v>
+      </c>
+      <c r="AK37">
+        <v>100</v>
+      </c>
+      <c r="AL37">
+        <v>100</v>
+      </c>
+      <c r="AM37">
+        <v>101</v>
+      </c>
+      <c r="AN37">
+        <v>101</v>
+      </c>
+      <c r="AO37">
+        <v>101</v>
+      </c>
+      <c r="AP37">
+        <v>101</v>
+      </c>
+      <c r="AQ37">
+        <v>101</v>
+      </c>
+      <c r="AR37">
+        <v>101</v>
+      </c>
+      <c r="AS37">
+        <v>101</v>
+      </c>
+      <c r="AT37">
+        <v>101</v>
+      </c>
+      <c r="AU37">
+        <v>101</v>
+      </c>
+      <c r="AV37">
+        <v>101</v>
+      </c>
+      <c r="AW37">
+        <v>101</v>
+      </c>
+      <c r="AX37">
+        <v>101</v>
+      </c>
+      <c r="AY37">
+        <v>101</v>
+      </c>
+      <c r="AZ37">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A5:N6">
+    <cfRule type="expression" dxfId="130" priority="35" stopIfTrue="1">
+      <formula>A5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="129" priority="24">
+      <formula>A5=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="30" stopIfTrue="1">
+      <formula>A5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="127" priority="29" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="28" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="125" priority="23">
+      <formula>A5=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="124" priority="27" stopIfTrue="1">
+      <formula>A5=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="123" priority="26" stopIfTrue="1">
+      <formula>AND(A5&gt;=90, A5&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="25">
+      <formula>A5=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="121" priority="31" stopIfTrue="1">
+      <formula>A5=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="120" priority="32" stopIfTrue="1">
+      <formula>A5=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="119" priority="33" stopIfTrue="1">
+      <formula>A5=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="34" stopIfTrue="1">
+      <formula>A5=10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:N33">
-    <cfRule type="expression" dxfId="25" priority="14">
+    <cfRule type="expression" dxfId="117" priority="45" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="38">
+      <formula>A32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="115" priority="44" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="114" priority="37">
+      <formula>A32=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="113" priority="43" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="42" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="111" priority="41" stopIfTrue="1">
+      <formula>A32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="40" stopIfTrue="1">
+      <formula>A32=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="109" priority="36">
       <formula>A32=72</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="15">
-      <formula>A32=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="16">
-      <formula>A32=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="48" stopIfTrue="1">
+      <formula>A32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="107" priority="47" stopIfTrue="1">
+      <formula>A32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="106" priority="46" stopIfTrue="1">
+      <formula>A32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="39" stopIfTrue="1">
       <formula>AND(A32&gt;=90, A32&lt;100)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="18" stopIfTrue="1">
-      <formula>A32=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="19" stopIfTrue="1">
-      <formula>A32=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="20" stopIfTrue="1">
-      <formula>A32=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
-      <formula>A32=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="22" stopIfTrue="1">
-      <formula>A32=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="23" stopIfTrue="1">
-      <formula>A32=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
-      <formula>A32=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
-      <formula>A32=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
-      <formula>A32=0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:N6">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>A5=72</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>A5=71</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
-      <formula>A5=80</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="4" stopIfTrue="1">
-      <formula>AND(A5&gt;=90, A5&lt;100)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="5" stopIfTrue="1">
-      <formula>A5=100</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
-      <formula>A5=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
-      <formula>A5=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
-      <formula>A5=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="9" stopIfTrue="1">
-      <formula>A5=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="10" stopIfTrue="1">
-      <formula>A5=20</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="11" stopIfTrue="1">
-      <formula>A5=11</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="12" stopIfTrue="1">
-      <formula>A5=10</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="13" stopIfTrue="1">
-      <formula>A5=0</formula>
+  <conditionalFormatting sqref="A1:Y4 AC1:AF4 AG1:AR10 AS1:AZ37 I5:AN10 A5:H37 I11:AR15 I23:AR37 V1:V12">
+    <cfRule type="expression" dxfId="104" priority="138" stopIfTrue="1">
+      <formula>A1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="134">
+      <formula>A1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="135">
+      <formula>A1=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="136">
+      <formula>A1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="137" stopIfTrue="1">
+      <formula>AND(A1&gt;=90, A1&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:Y4 AS1:AZ37 I5:Z5 L5:R10 M5:AN12 A5:H37 I6:AF10 AH6:AR10 I11:R20 AL11:AR27 M13:U13 W13:AN13 V13:AK15 S14:U15 I21:S27 T23:U24 V23:AK25 M25:U25 W25:AN25 M26:AN33 V26:V37 I28:AF37 AH33:AR37 V1:V5">
+    <cfRule type="expression" dxfId="99" priority="139" stopIfTrue="1">
+      <formula>A1=20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:Y4 AS1:AZ37 I5:Z5 L5:R10 M5:AN12 A5:H37 I6:AF10 AH6:AR10 I11:R20 AL11:AR27 M13:U13 W13:AN13 V13:AK15 S14:U15 O16:T22 AG16:AL22 I21:S27 T23:U24 V23:AK25 M25:U25 W25:AN25 M26:AN33 V26:V37 I28:AF37 AH33:AR37 V1:V5">
+    <cfRule type="expression" dxfId="98" priority="141" stopIfTrue="1">
+      <formula>A1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="97" priority="140" stopIfTrue="1">
+      <formula>A1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="142" stopIfTrue="1">
+      <formula>A1=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23:AZ37 A1:AZ15">
+    <cfRule type="expression" dxfId="95" priority="132">
+      <formula>A1=102</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="133">
+      <formula>A1=101</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16:AZ22">
+    <cfRule type="expression" dxfId="93" priority="2">
+      <formula>A16=101</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="92" priority="1">
+      <formula>A16=102</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:AR22">
+    <cfRule type="expression" dxfId="91" priority="5">
+      <formula>I16=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="4">
+      <formula>I16=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="7" stopIfTrue="1">
+      <formula>I16=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="6" stopIfTrue="1">
+      <formula>AND(I16&gt;=90, I16&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="87" priority="3">
+      <formula>I16=72</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:P10">
+    <cfRule type="expression" dxfId="86" priority="85" stopIfTrue="1">
+      <formula>O1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="86" stopIfTrue="1">
+      <formula>O1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="87" stopIfTrue="1">
+      <formula>O1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="84" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="83" stopIfTrue="1">
+      <formula>O1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="82" stopIfTrue="1">
+      <formula>O1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="81" stopIfTrue="1">
+      <formula>O1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="80" stopIfTrue="1">
+      <formula>O1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="79" stopIfTrue="1">
+      <formula>O1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="75">
+      <formula>O1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="78" stopIfTrue="1">
+      <formula>AND(O1&gt;=90, O1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="77">
+      <formula>O1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="76">
+      <formula>O1=71</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O28:P37">
+    <cfRule type="expression" dxfId="73" priority="72" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="74" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="73" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="62">
+      <formula>O28=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="63">
+      <formula>O28=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="64">
+      <formula>O28=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="66" stopIfTrue="1">
+      <formula>O28=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="67" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="68" stopIfTrue="1">
+      <formula>O28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="69" stopIfTrue="1">
+      <formula>O28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="70" stopIfTrue="1">
+      <formula>O28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="71" stopIfTrue="1">
+      <formula>O28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="65" stopIfTrue="1">
+      <formula>AND(O28&gt;=90, O28&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O16:AL22">
+    <cfRule type="expression" dxfId="60" priority="8" stopIfTrue="1">
+      <formula>O16=20</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U16:AF22">
+    <cfRule type="expression" dxfId="59" priority="10" stopIfTrue="1">
+      <formula>U16=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="11" stopIfTrue="1">
+      <formula>U16=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="9" stopIfTrue="1">
+      <formula>U16=11</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1:AB4">
+    <cfRule type="expression" dxfId="56" priority="126" stopIfTrue="1">
+      <formula>AND(Z1&gt;=90, Z1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="127" stopIfTrue="1">
+      <formula>Z1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="128" stopIfTrue="1">
+      <formula>Z1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="129" stopIfTrue="1">
+      <formula>Z1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="130" stopIfTrue="1">
+      <formula>Z1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="131" stopIfTrue="1">
+      <formula>Z1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="125">
+      <formula>Z1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="123">
+      <formula>Z1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="124">
+      <formula>Z1=71</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z34:AB37">
+    <cfRule type="expression" dxfId="47" priority="119" stopIfTrue="1">
+      <formula>Z34=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="118" stopIfTrue="1">
+      <formula>Z34=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="117" stopIfTrue="1">
+      <formula>AND(Z34&gt;=90, Z34&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="116">
+      <formula>Z34=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="115">
+      <formula>Z34=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="114">
+      <formula>Z34=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="120" stopIfTrue="1">
+      <formula>Z34=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="121" stopIfTrue="1">
+      <formula>Z34=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="122" stopIfTrue="1">
+      <formula>Z34=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK1:AL10 AM5:AZ6">
+    <cfRule type="expression" dxfId="38" priority="91" stopIfTrue="1">
+      <formula>AND(AK1&gt;=90, AK1&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="88">
+      <formula>AK1=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="90">
+      <formula>AK1=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="98" stopIfTrue="1">
+      <formula>AK1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="92" stopIfTrue="1">
+      <formula>AK1=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="93" stopIfTrue="1">
+      <formula>AK1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="94" stopIfTrue="1">
+      <formula>AK1=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="95" stopIfTrue="1">
+      <formula>AK1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="96" stopIfTrue="1">
+      <formula>AK1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="97" stopIfTrue="1">
+      <formula>AK1=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="99" stopIfTrue="1">
+      <formula>AK1=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="100" stopIfTrue="1">
+      <formula>AK1=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="89">
+      <formula>AK1=71</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK28:AM32 AK32:AL37">
+    <cfRule type="expression" dxfId="25" priority="104" stopIfTrue="1">
+      <formula>AND(AK28&gt;=90, AK28&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="105" stopIfTrue="1">
+      <formula>AK28=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="107" stopIfTrue="1">
+      <formula>AK28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="109" stopIfTrue="1">
+      <formula>AK28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="110" stopIfTrue="1">
+      <formula>AK28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="111" stopIfTrue="1">
+      <formula>AK28=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="112" stopIfTrue="1">
+      <formula>AK28=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="106" stopIfTrue="1">
+      <formula>AK28=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="113" stopIfTrue="1">
+      <formula>AK28=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="101">
+      <formula>AK28=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="102">
+      <formula>AK28=71</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="103">
+      <formula>AK28=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="108" stopIfTrue="1">
+      <formula>AK28=10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL32:AZ33">
+    <cfRule type="expression" dxfId="12" priority="49">
+      <formula>AL32=72</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="55" stopIfTrue="1">
+      <formula>AL32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="61" stopIfTrue="1">
+      <formula>AL32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="60" stopIfTrue="1">
+      <formula>AL32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="59" stopIfTrue="1">
+      <formula>AL32=11</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="58" stopIfTrue="1">
+      <formula>AL32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="56" stopIfTrue="1">
+      <formula>AL32=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="54" stopIfTrue="1">
+      <formula>AL32=20</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="53" stopIfTrue="1">
+      <formula>AL32=100</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="57" stopIfTrue="1">
+      <formula>AL32=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="52" stopIfTrue="1">
+      <formula>AND(AL32&gt;=90, AL32&lt;100)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="51">
+      <formula>AL32=80</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="50">
+      <formula>AL32=71</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/StageExcel.xlsx
+++ b/Assets/Resources/StageExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hotat\OneDrive\デスクトップ\GCP\DecoBom\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4989F2F-286A-491C-97BD-752D445B2562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB56697-3F65-41B7-91F0-A5FE152E45E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{1AEF912E-AD76-439A-9847-D359AAF86FF7}"/>
   </bookViews>
@@ -30241,7 +30241,7 @@
         <v>100</v>
       </c>
       <c r="Z4">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -30396,7 +30396,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -31290,7 +31290,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -32515,7 +32515,7 @@
         <v>102</v>
       </c>
       <c r="I19">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>99</v>
@@ -32617,7 +32617,7 @@
         <v>99</v>
       </c>
       <c r="AQ19">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AR19">
         <v>101</v>
@@ -33770,7 +33770,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -34736,7 +34736,7 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -34891,7 +34891,7 @@
         <v>100</v>
       </c>
       <c r="Z34">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AA34">
         <v>100</v>
@@ -37814,10 +37814,10 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -38243,7 +38243,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -38336,7 +38336,7 @@
         <v>10</v>
       </c>
       <c r="AP16">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
         <v>10</v>
@@ -38595,7 +38595,7 @@
         <v>20</v>
       </c>
       <c r="W18">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="X18">
         <v>84</v>
@@ -38616,7 +38616,7 @@
         <v>84</v>
       </c>
       <c r="AD18">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AE18">
         <v>20</v>
@@ -38711,7 +38711,7 @@
         <v>102</v>
       </c>
       <c r="I19">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>99</v>
@@ -38753,7 +38753,7 @@
         <v>20</v>
       </c>
       <c r="W19">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="X19">
         <v>84</v>
@@ -38774,7 +38774,7 @@
         <v>84</v>
       </c>
       <c r="AD19">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="AE19">
         <v>20</v>
@@ -38816,7 +38816,7 @@
         <v>99</v>
       </c>
       <c r="AR19">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="AS19">
         <v>101</v>
@@ -38911,7 +38911,7 @@
         <v>20</v>
       </c>
       <c r="W20">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="X20">
         <v>84</v>
@@ -38932,7 +38932,7 @@
         <v>84</v>
       </c>
       <c r="AD20">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AE20">
         <v>20</v>
@@ -39191,7 +39191,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -39284,7 +39284,7 @@
         <v>10</v>
       </c>
       <c r="AP22">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
         <v>10</v>
@@ -39710,10 +39710,10 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AB25">
         <v>10</v>
